--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D22066-7CD3-0E48-AAE1-F4412F667F50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08B9BB7-057E-8D43-B7A2-73B4A012A50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
-    <sheet name="Foglio1" sheetId="2" r:id="rId2"/>
+    <sheet name="Foglio1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registro!$C$1:$C$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registro!$F$1:$F$59</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="151">
   <si>
     <t>Anagrafica</t>
   </si>
@@ -475,6 +475,24 @@
   </si>
   <si>
     <t>Claudia</t>
+  </si>
+  <si>
+    <t>Gennaro</t>
+  </si>
+  <si>
+    <t>Agliottone</t>
+  </si>
+  <si>
+    <t>Imperatore</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Senza rimorso</t>
+  </si>
+  <si>
+    <t>Marcello</t>
   </si>
 </sst>
 </file>
@@ -651,6 +669,18 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -662,18 +692,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -695,9 +713,9 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46103.477192824073" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="43" xr:uid="{2A87FEF4-A6FE-0342-A972-B8E55F08E641}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46110.424964351849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A2:S45" sheet="Registro"/>
+    <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
   <cacheFields count="19">
     <cacheField name="Cognome" numFmtId="0">
@@ -707,26 +725,28 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="Azienda" numFmtId="0">
-      <sharedItems count="6">
+      <sharedItems count="8">
         <s v="AmorSì"/>
+        <s v="Draft8"/>
         <s v="Maccarò Lab"/>
         <s v="Partenope Food Innovation"/>
         <s v="ReFood-Lab"/>
+        <s v="Senza rimorso"/>
         <s v="Socialbite!"/>
         <s v="VivaFruit"/>
       </sharedItems>
     </cacheField>
     <cacheField name="L1 Presenza" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L1 XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="150"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="150"/>
     </cacheField>
     <cacheField name="L2 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L2 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="100"/>
     </cacheField>
     <cacheField name="L3 Presenza" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -759,10 +779,15 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.14285714285714285"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.2857142857142857"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="150"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="150" count="4">
+        <n v="65"/>
+        <n v="50"/>
+        <n v="150"/>
+        <n v="0"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -774,27 +799,27 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="43">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="61">
   <r>
     <s v="Cinieri"/>
     <s v="Giuseppe"/>
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -802,20 +827,20 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -823,20 +848,20 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -844,20 +869,20 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -865,20 +890,20 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -886,20 +911,20 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -907,8 +932,71 @@
     <x v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Cuomo"/>
+    <s v="Davide"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Ercolano"/>
+    <s v="Anna"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Forte"/>
+    <s v="Giusi"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -920,121 +1008,205 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Gallo"/>
+    <s v="Francesca"/>
+    <x v="1"/>
+    <n v="1"/>
     <n v="50"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Paone"/>
+    <s v="Davide"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Petrone"/>
+    <s v="Claudia"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Preteverde"/>
+    <s v="Simona"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Baudrand"/>
     <s v="Iris"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Borreca"/>
     <s v="Paolo"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Borrione"/>
     <s v="Carlotta"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Cappelluccio"/>
     <s v="Mario"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Casale"/>
     <s v="Alessandro"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Marrazzo"/>
     <s v="Alessia"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="15"/>
     <m/>
     <m/>
     <m/>
@@ -1046,331 +1218,331 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Miles"/>
     <s v="Eva"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Parente"/>
     <s v="Maria"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Pietropaolo"/>
     <s v="Sara"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Rispoli"/>
     <s v="Marco"/>
-    <x v="1"/>
+    <x v="2"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Maione"/>
     <s v="Barbara"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Nasti"/>
     <s v="Francesca"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Noviello"/>
     <s v="Martina"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Pepe"/>
     <s v="Lorenzo"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Tartaro"/>
     <s v="Ilaria"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Versi"/>
     <s v="Giuseppina"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="150"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
     <x v="2"/>
-    <n v="1"/>
-    <n v="150"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="150"/>
   </r>
   <r>
     <s v="Borrelli"/>
     <s v="Nunzia"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Canzolino"/>
     <s v="Carlo"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="De Siena"/>
     <s v="Daniele Gennaro"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Di Meglio"/>
     <s v="Francesco"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Esposito"/>
     <s v="Melissa"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Ferrante"/>
     <s v="Rosanna"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1382,79 +1554,121 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Maglietta"/>
     <s v="Giuseppe"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Patroni Griffi"/>
     <s v="Niccolò"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Semioli"/>
     <s v="Stella"/>
-    <x v="3"/>
+    <x v="4"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="Siano"/>
     <s v="Gaetano"/>
+    <x v="4"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <s v="Agliottone"/>
+    <s v="Davide"/>
+    <x v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
     <x v="3"/>
-    <n v="1"/>
-    <n v="50"/>
-    <m/>
-    <m/>
+  </r>
+  <r>
+    <s v="Gallo"/>
+    <s v="Gennaro"/>
+    <x v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1466,235 +1680,426 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="Imperatore"/>
+    <s v="Luca"/>
+    <x v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <s v="Monaco"/>
+    <s v="Marcello"/>
+    <x v="5"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.14285714285714285"/>
+    <x v="3"/>
   </r>
   <r>
     <s v="Cerundolo"/>
     <s v="Anna"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Chieti"/>
     <s v="Simona"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Coda"/>
     <s v="Roberta"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Dibartolomeo"/>
     <s v="Elisa Diana"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Raduazzo"/>
     <s v="Letizia"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Vable"/>
     <s v="Vittoria"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Zito"/>
     <s v="Michelangelo"/>
-    <x v="4"/>
+    <x v="6"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="100"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="Antico"/>
     <s v="Giorgia"/>
-    <x v="5"/>
+    <x v="7"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="D'Acunto"/>
     <s v="Luca"/>
-    <x v="5"/>
+    <x v="7"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="Di Fiore"/>
     <s v="Manila"/>
-    <x v="5"/>
+    <x v="7"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Ditri"/>
+    <s v="Martina"/>
+    <x v="7"/>
+    <n v="1"/>
     <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Fraddanno"/>
+    <s v="Filippo"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Marciello"/>
+    <s v="Miriam"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Miranda"/>
+    <s v="Sara"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Rolletta"/>
+    <s v="Christian"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Soriano"/>
+    <s v="Leandro"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <s v="Vitale"/>
+    <s v="Marco"/>
+    <x v="7"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="15"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7CF1CC40-347B-D040-837C-FA6C3BFCDD38}" name="Tabella pivot1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:C10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="ascending">
-      <items count="7">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="9">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
         <item x="4"/>
         <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1718,7 +2123,7 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="9">
     <i>
       <x/>
     </i>
@@ -1737,6 +2142,12 @@
     <i>
       <x v="5"/>
     </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -1753,8 +2164,8 @@
     </i>
   </colItems>
   <dataFields count="2">
+    <dataField name="Media di XP" fld="18" subtotal="average" baseField="0" baseItem="0"/>
     <dataField name="Media di Presenza" fld="17" subtotal="average" baseField="0" baseItem="0" numFmtId="9"/>
-    <dataField name="Media di XP" fld="18" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -2053,7 +2464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:S63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2062,7 +2473,7 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8" style="19" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
@@ -2077,43 +2488,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="18" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="21"/>
+      <c r="F1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="16" t="s">
+      <c r="G1" s="21"/>
+      <c r="H1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="17"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="21"/>
+      <c r="J1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="16" t="s">
+      <c r="K1" s="21"/>
+      <c r="L1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="18" t="s">
+      <c r="M1" s="21"/>
+      <c r="N1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="O1" s="17"/>
-      <c r="P1" s="16" t="s">
+      <c r="O1" s="21"/>
+      <c r="P1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="19" t="s">
+      <c r="Q1" s="21"/>
+      <c r="R1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="19"/>
+      <c r="S1" s="23"/>
     </row>
     <row r="2" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2190,8 +2601,12 @@
       <c r="E3" s="9">
         <v>50</v>
       </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="F3" s="16">
+        <v>1</v>
+      </c>
+      <c r="G3" s="18">
+        <v>15</v>
+      </c>
       <c r="H3" s="13"/>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
@@ -2203,12 +2618,12 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="4">
-        <f>(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.14285714285714285</v>
+        <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S3" s="3">
-        <f>E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>50</v>
+        <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2227,8 +2642,12 @@
       <c r="E4" s="9">
         <v>50</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="F4" s="16">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18">
+        <v>15</v>
+      </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="13"/>
@@ -2240,12 +2659,12 @@
       <c r="P4" s="13"/>
       <c r="Q4" s="13"/>
       <c r="R4" s="4">
-        <f t="shared" ref="R4:R59" si="0">(D4+F4+H4+J4+L4+N4+P4)/7</f>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="0"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S4" s="3">
-        <f t="shared" ref="S4:S16" si="1">E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2264,8 +2683,12 @@
       <c r="E5" s="9">
         <v>50</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="F5" s="16">
+        <v>1</v>
+      </c>
+      <c r="G5" s="18">
+        <v>15</v>
+      </c>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
       <c r="J5" s="13"/>
@@ -2278,11 +2701,11 @@
       <c r="Q5" s="13"/>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2301,8 +2724,12 @@
       <c r="E6" s="9">
         <v>50</v>
       </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="F6" s="16">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18">
+        <v>15</v>
+      </c>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
@@ -2315,11 +2742,11 @@
       <c r="Q6" s="13"/>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2338,8 +2765,12 @@
       <c r="E7" s="9">
         <v>50</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="F7" s="16">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18">
+        <v>15</v>
+      </c>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -2352,11 +2783,11 @@
       <c r="Q7" s="13"/>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2375,8 +2806,12 @@
       <c r="E8" s="9">
         <v>50</v>
       </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="F8" s="16">
+        <v>1</v>
+      </c>
+      <c r="G8" s="18">
+        <v>15</v>
+      </c>
       <c r="H8" s="13"/>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
@@ -2389,11 +2824,11 @@
       <c r="Q8" s="13"/>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2412,8 +2847,12 @@
       <c r="E9" s="9">
         <v>50</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="18">
+        <v>15</v>
+      </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
@@ -2426,31 +2865,35 @@
       <c r="Q9" s="13"/>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="23">
-        <v>1</v>
-      </c>
-      <c r="E10" s="23">
-        <v>50</v>
-      </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9">
+        <v>50</v>
+      </c>
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
+      <c r="G10" s="18">
+        <v>0</v>
+      </c>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -2463,7 +2906,7 @@
       <c r="Q10" s="13"/>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
@@ -2471,23 +2914,27 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D11" s="23">
-        <v>1</v>
-      </c>
-      <c r="E11" s="23">
-        <v>50</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9">
+        <v>50</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18">
+        <v>0</v>
+      </c>
       <c r="H11" s="13"/>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -2500,7 +2947,7 @@
       <c r="Q11" s="13"/>
       <c r="R11" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S11" s="3">
         <f t="shared" si="1"/>
@@ -2508,23 +2955,27 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D12" s="23">
-        <v>1</v>
-      </c>
-      <c r="E12" s="23">
-        <v>50</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9">
+        <v>50</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18">
+        <v>0</v>
+      </c>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
@@ -2545,23 +2996,27 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D13" s="23">
-        <v>1</v>
-      </c>
-      <c r="E13" s="23">
-        <v>50</v>
-      </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9">
+        <v>50</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <v>0</v>
+      </c>
       <c r="H13" s="13"/>
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
@@ -2582,23 +3037,27 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="23">
-        <v>1</v>
-      </c>
-      <c r="E14" s="23">
-        <v>50</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="D14" s="9">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9">
+        <v>50</v>
+      </c>
+      <c r="F14" s="16">
+        <v>1</v>
+      </c>
+      <c r="G14" s="18">
+        <v>0</v>
+      </c>
       <c r="H14" s="13"/>
       <c r="I14" s="13"/>
       <c r="J14" s="13"/>
@@ -2611,7 +3070,7 @@
       <c r="Q14" s="13"/>
       <c r="R14" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S14" s="3">
         <f t="shared" si="1"/>
@@ -2619,23 +3078,27 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D15" s="23">
-        <v>1</v>
-      </c>
-      <c r="E15" s="23">
-        <v>50</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="D15" s="9">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
+        <v>50</v>
+      </c>
+      <c r="F15" s="16">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18">
+        <v>0</v>
+      </c>
       <c r="H15" s="13"/>
       <c r="I15" s="13"/>
       <c r="J15" s="13"/>
@@ -2648,7 +3111,7 @@
       <c r="Q15" s="13"/>
       <c r="R15" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S15" s="3">
         <f t="shared" si="1"/>
@@ -2656,23 +3119,27 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D16" s="23">
-        <v>1</v>
-      </c>
-      <c r="E16" s="23">
-        <v>50</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9">
+        <v>50</v>
+      </c>
+      <c r="F16" s="16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="18">
+        <v>0</v>
+      </c>
       <c r="H16" s="13"/>
       <c r="I16" s="13"/>
       <c r="J16" s="13"/>
@@ -2685,7 +3152,7 @@
       <c r="Q16" s="13"/>
       <c r="R16" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S16" s="3">
         <f t="shared" si="1"/>
@@ -2708,8 +3175,12 @@
       <c r="E17" s="9">
         <v>50</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
+      <c r="F17" s="9">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9">
+        <v>115</v>
+      </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9"/>
@@ -2722,11 +3193,11 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S17" s="3">
-        <f>E17+G17+I17+K17+M17+O17+Q17</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
@@ -2745,8 +3216,12 @@
       <c r="E18" s="9">
         <v>50</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
+      <c r="F18" s="9">
+        <v>1</v>
+      </c>
+      <c r="G18" s="9">
+        <v>115</v>
+      </c>
       <c r="H18" s="9"/>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -2759,11 +3234,11 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S18" s="3">
-        <f>E18+G18+I18+K18+M18+O18+Q18</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -2782,8 +3257,12 @@
       <c r="E19" s="9">
         <v>50</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="F19" s="9">
+        <v>1</v>
+      </c>
+      <c r="G19" s="9">
+        <v>115</v>
+      </c>
       <c r="H19" s="9"/>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -2796,11 +3275,11 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S19" s="3">
-        <f>E19+G19+I19+K19+M19+O19+Q19</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -2819,8 +3298,12 @@
       <c r="E20" s="9">
         <v>50</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
+      <c r="F20" s="9">
+        <v>1</v>
+      </c>
+      <c r="G20" s="9">
+        <v>115</v>
+      </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -2833,11 +3316,11 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S20" s="3">
-        <f>E20+G20+I20+K20+M20+O20+Q20</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -2856,8 +3339,12 @@
       <c r="E21" s="9">
         <v>50</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
+      <c r="F21" s="9">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9">
+        <v>115</v>
+      </c>
       <c r="H21" s="9"/>
       <c r="I21" s="9"/>
       <c r="J21" s="9"/>
@@ -2870,11 +3357,11 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S21" s="3">
-        <f>E21+G21+I21+K21+M21+O21+Q21</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -2893,8 +3380,12 @@
       <c r="E22" s="9">
         <v>50</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>115</v>
+      </c>
       <c r="H22" s="9"/>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -2910,8 +3401,8 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="S22" s="3">
-        <f>E22+G22+I22+K22+M22+O22+Q22</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -2930,8 +3421,12 @@
       <c r="E23" s="9">
         <v>50</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
+      <c r="F23" s="9">
+        <v>1</v>
+      </c>
+      <c r="G23" s="9">
+        <v>115</v>
+      </c>
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
       <c r="J23" s="9"/>
@@ -2944,11 +3439,11 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S23" s="3">
-        <f>E23+G23+I23+K23+M23+O23+Q23</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -2967,8 +3462,12 @@
       <c r="E24" s="9">
         <v>50</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
+      <c r="F24" s="9">
+        <v>1</v>
+      </c>
+      <c r="G24" s="9">
+        <v>115</v>
+      </c>
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
       <c r="J24" s="9"/>
@@ -2981,11 +3480,11 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S24" s="3">
-        <f>E24+G24+I24+K24+M24+O24+Q24</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -3004,8 +3503,12 @@
       <c r="E25" s="9">
         <v>50</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
+      <c r="F25" s="9">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9">
+        <v>115</v>
+      </c>
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
       <c r="J25" s="9"/>
@@ -3018,11 +3521,11 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S25" s="3">
-        <f>E25+G25+I25+K25+M25+O25+Q25</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -3041,8 +3544,12 @@
       <c r="E26" s="9">
         <v>50</v>
       </c>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
+      <c r="F26" s="9">
+        <v>1</v>
+      </c>
+      <c r="G26" s="9">
+        <v>115</v>
+      </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
       <c r="J26" s="9"/>
@@ -3055,11 +3562,11 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S26" s="3">
-        <f>E26+G26+I26+K26+M26+O26+Q26</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -3078,8 +3585,12 @@
       <c r="E27" s="9">
         <v>150</v>
       </c>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="9">
+        <v>0</v>
+      </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
@@ -3095,7 +3606,7 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="S27" s="3">
-        <f>E27+G27+I27+K27+M27+O27+Q27</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3115,8 +3626,12 @@
       <c r="E28" s="9">
         <v>150</v>
       </c>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="F28" s="9">
+        <v>1</v>
+      </c>
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
@@ -3129,10 +3644,10 @@
       <c r="Q28" s="9"/>
       <c r="R28" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S28" s="3">
-        <f>E28+G28+I28+K28+M28+O28+Q28</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3152,8 +3667,12 @@
       <c r="E29" s="9">
         <v>150</v>
       </c>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9"/>
       <c r="J29" s="9"/>
@@ -3169,7 +3688,7 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="S29" s="3">
-        <f>E29+G29+I29+K29+M29+O29+Q29</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3189,8 +3708,12 @@
       <c r="E30" s="9">
         <v>150</v>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
+      <c r="F30" s="9">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
       <c r="J30" s="9"/>
@@ -3203,10 +3726,10 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S30" s="3">
-        <f>E30+G30+I30+K30+M30+O30+Q30</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3226,8 +3749,12 @@
       <c r="E31" s="9">
         <v>150</v>
       </c>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
+      <c r="F31" s="9">
+        <v>0</v>
+      </c>
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9"/>
       <c r="J31" s="9"/>
@@ -3243,7 +3770,7 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="S31" s="3">
-        <f>E31+G31+I31+K31+M31+O31+Q31</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3263,8 +3790,12 @@
       <c r="E32" s="9">
         <v>150</v>
       </c>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
+      <c r="F32" s="9">
+        <v>0</v>
+      </c>
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9"/>
       <c r="J32" s="9"/>
@@ -3280,7 +3811,7 @@
         <v>0.14285714285714285</v>
       </c>
       <c r="S32" s="3">
-        <f>E32+G32+I32+K32+M32+O32+Q32</f>
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
@@ -3300,8 +3831,12 @@
       <c r="E33" s="9">
         <v>50</v>
       </c>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
+      <c r="F33" s="9">
+        <v>1</v>
+      </c>
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
       <c r="H33" s="9"/>
       <c r="I33" s="9"/>
       <c r="J33" s="9"/>
@@ -3314,10 +3849,10 @@
       <c r="Q33" s="9"/>
       <c r="R33" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S33" s="3">
-        <f>E33+G33+I33+K33+M33+O33+Q33</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
@@ -3337,8 +3872,12 @@
       <c r="E34" s="9">
         <v>50</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="F34" s="9">
+        <v>1</v>
+      </c>
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
       <c r="H34" s="9"/>
       <c r="I34" s="9"/>
       <c r="J34" s="9"/>
@@ -3351,10 +3890,10 @@
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S34" s="3">
-        <f>E34+G34+I34+K34+M34+O34+Q34</f>
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
@@ -3374,8 +3913,12 @@
       <c r="E35" s="9">
         <v>50</v>
       </c>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="F35" s="9">
+        <v>1</v>
+      </c>
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9"/>
       <c r="J35" s="9"/>
@@ -3387,11 +3930,11 @@
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" ref="R35:R63" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S35" s="3">
-        <f>E35+G35+I35+K35+M35+O35+Q35</f>
+        <f t="shared" ref="S35:S63" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
         <v>50</v>
       </c>
     </row>
@@ -3411,8 +3954,12 @@
       <c r="E36" s="9">
         <v>50</v>
       </c>
-      <c r="F36" s="9"/>
-      <c r="G36" s="9"/>
+      <c r="F36" s="9">
+        <v>1</v>
+      </c>
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
       <c r="H36" s="9"/>
       <c r="I36" s="9"/>
       <c r="J36" s="9"/>
@@ -3424,11 +3971,11 @@
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S36" s="3">
-        <f>E36+G36+I36+K36+M36+O36+Q36</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3448,8 +3995,12 @@
       <c r="E37" s="9">
         <v>50</v>
       </c>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="F37" s="9">
+        <v>1</v>
+      </c>
+      <c r="G37" s="9">
+        <v>0</v>
+      </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
@@ -3461,11 +4012,11 @@
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S37" s="3">
-        <f>E37+G37+I37+K37+M37+O37+Q37</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3485,8 +4036,12 @@
       <c r="E38" s="9">
         <v>50</v>
       </c>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="F38" s="9">
+        <v>0</v>
+      </c>
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
       <c r="H38" s="9"/>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -3498,11 +4053,11 @@
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S38" s="3">
-        <f>E38+G38+I38+K38+M38+O38+Q38</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3522,8 +4077,12 @@
       <c r="E39" s="9">
         <v>50</v>
       </c>
-      <c r="F39" s="9"/>
-      <c r="G39" s="9"/>
+      <c r="F39" s="9">
+        <v>1</v>
+      </c>
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
       <c r="H39" s="9"/>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -3535,11 +4094,11 @@
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S39" s="3">
-        <f>E39+G39+I39+K39+M39+O39+Q39</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3559,8 +4118,12 @@
       <c r="E40" s="9">
         <v>50</v>
       </c>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="F40" s="9">
+        <v>1</v>
+      </c>
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
@@ -3572,11 +4135,11 @@
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S40" s="3">
-        <f>E40+G40+I40+K40+M40+O40+Q40</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3596,8 +4159,12 @@
       <c r="E41" s="9">
         <v>50</v>
       </c>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="F41" s="9">
+        <v>1</v>
+      </c>
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9"/>
       <c r="J41" s="9"/>
@@ -3609,11 +4176,11 @@
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S41" s="3">
-        <f>E41+G41+I41+K41+M41+O41+Q41</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
@@ -3633,8 +4200,12 @@
       <c r="E42" s="9">
         <v>50</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
+      <c r="F42" s="9">
+        <v>0</v>
+      </c>
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9"/>
       <c r="J42" s="9"/>
@@ -3646,168 +4217,174 @@
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S42" s="3">
-        <f>E42+G42+I42+K42+M42+O42+Q42</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" s="9">
-        <v>50</v>
-      </c>
-      <c r="F43" s="9"/>
-      <c r="G43" s="9"/>
-      <c r="H43" s="9"/>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
-      <c r="Q43" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="13"/>
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13"/>
+      <c r="P43" s="13"/>
+      <c r="Q43" s="13"/>
       <c r="R43" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S43" s="3">
-        <f>E43+G43+I43+K43+M43+O43+Q43</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D44" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>50</v>
-      </c>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-      <c r="O44" s="9"/>
-      <c r="P44" s="9"/>
-      <c r="Q44" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="9">
+        <v>1</v>
+      </c>
+      <c r="G44" s="9">
+        <v>0</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="13"/>
+      <c r="M44" s="13"/>
+      <c r="N44" s="13"/>
+      <c r="O44" s="13"/>
+      <c r="P44" s="13"/>
+      <c r="Q44" s="13"/>
       <c r="R44" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S44" s="3">
-        <f>E44+G44+I44+K44+M44+O44+Q44</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>50</v>
+        <v>147</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D45" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" s="9">
-        <v>50</v>
-      </c>
-      <c r="F45" s="9"/>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="9">
+        <v>1</v>
+      </c>
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="13"/>
+      <c r="M45" s="13"/>
+      <c r="N45" s="13"/>
+      <c r="O45" s="13"/>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="13"/>
       <c r="R45" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S45" s="3">
-        <f>E45+G45+I45+K45+M45+O45+Q45</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>54</v>
+        <v>148</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="D46" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" s="11">
-        <v>50</v>
-      </c>
-      <c r="F46" s="24"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="24"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="24"/>
-      <c r="N46" s="24"/>
-      <c r="O46" s="24"/>
-      <c r="P46" s="24"/>
-      <c r="Q46" s="24"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="9">
+        <v>1</v>
+      </c>
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
       <c r="R46" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S46" s="12">
-        <f>E46+G46+I46+K46+M46+O46+Q46</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>47</v>
@@ -3818,33 +4395,37 @@
       <c r="E47" s="11">
         <v>50</v>
       </c>
-      <c r="F47" s="24"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="24"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="24"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="24"/>
-      <c r="N47" s="24"/>
-      <c r="O47" s="24"/>
-      <c r="P47" s="24"/>
-      <c r="Q47" s="24"/>
+      <c r="F47" s="9">
+        <v>1</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
+      <c r="O47" s="14"/>
+      <c r="P47" s="14"/>
+      <c r="Q47" s="14"/>
       <c r="R47" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S47" s="12">
-        <f>E47+G47+I47+K47+M47+O47+Q47</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>47</v>
@@ -3855,33 +4436,37 @@
       <c r="E48" s="11">
         <v>50</v>
       </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="24"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
+      <c r="F48" s="9">
+        <v>1</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
+      <c r="O48" s="14"/>
+      <c r="P48" s="14"/>
+      <c r="Q48" s="14"/>
       <c r="R48" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S48" s="12">
-        <f>E48+G48+I48+K48+M48+O48+Q48</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>47</v>
@@ -3892,36 +4477,40 @@
       <c r="E49" s="11">
         <v>50</v>
       </c>
-      <c r="F49" s="24"/>
-      <c r="G49" s="24"/>
-      <c r="H49" s="24"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24"/>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
+      <c r="O49" s="14"/>
+      <c r="P49" s="14"/>
+      <c r="Q49" s="14"/>
       <c r="R49" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S49" s="12">
-        <f>E49+G49+I49+K49+M49+O49+Q49</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D50" s="11">
         <v>1</v>
@@ -3929,36 +4518,40 @@
       <c r="E50" s="11">
         <v>50</v>
       </c>
-      <c r="F50" s="24"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="24"/>
+      <c r="F50" s="9">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
+      <c r="O50" s="14"/>
+      <c r="P50" s="14"/>
+      <c r="Q50" s="14"/>
       <c r="R50" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S50" s="12">
-        <f>E50+G50+I50+K50+M50+O50+Q50</f>
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D51" s="11">
         <v>1</v>
@@ -3966,36 +4559,40 @@
       <c r="E51" s="11">
         <v>50</v>
       </c>
-      <c r="F51" s="24"/>
-      <c r="G51" s="24"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="24"/>
-      <c r="N51" s="24"/>
-      <c r="O51" s="24"/>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="24"/>
+      <c r="F51" s="9">
+        <v>1</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
+      <c r="O51" s="14"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="14"/>
       <c r="R51" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S51" s="21">
-        <f>E51+G51+I51+K51+M51+O51+Q51</f>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S51" s="15">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D52" s="11">
         <v>1</v>
@@ -4003,36 +4600,40 @@
       <c r="E52" s="11">
         <v>50</v>
       </c>
-      <c r="F52" s="24"/>
-      <c r="G52" s="24"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" s="24"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
-      <c r="N52" s="24"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
+      <c r="F52" s="9">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="14"/>
+      <c r="N52" s="14"/>
+      <c r="O52" s="14"/>
+      <c r="P52" s="14"/>
+      <c r="Q52" s="14"/>
       <c r="R52" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S52" s="21">
-        <f>E52+G52+I52+K52+M52+O52+Q52</f>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S52" s="15">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D53" s="11">
         <v>1</v>
@@ -4040,33 +4641,37 @@
       <c r="E53" s="11">
         <v>50</v>
       </c>
-      <c r="F53" s="24"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="24"/>
-      <c r="J53" s="24"/>
-      <c r="K53" s="24"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="24"/>
-      <c r="N53" s="24"/>
-      <c r="O53" s="24"/>
-      <c r="P53" s="24"/>
-      <c r="Q53" s="24"/>
+      <c r="F53" s="9">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
+      <c r="O53" s="14"/>
+      <c r="P53" s="14"/>
+      <c r="Q53" s="14"/>
       <c r="R53" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S53" s="21">
-        <f>E53+G53+I53+K53+M53+O53+Q53</f>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S53" s="15">
+        <f t="shared" si="3"/>
         <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>28</v>
@@ -4077,33 +4682,37 @@
       <c r="E54" s="11">
         <v>50</v>
       </c>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-      <c r="J54" s="24"/>
-      <c r="K54" s="24"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="24"/>
-      <c r="N54" s="24"/>
-      <c r="O54" s="24"/>
-      <c r="P54" s="24"/>
-      <c r="Q54" s="24"/>
+      <c r="F54" s="9">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14">
+        <v>15</v>
+      </c>
+      <c r="H54" s="14"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
+      <c r="O54" s="14"/>
+      <c r="P54" s="14"/>
+      <c r="Q54" s="14"/>
       <c r="R54" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S54" s="21">
-        <f>E54+G54+I54+K54+M54+O54+Q54</f>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S54" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>28</v>
@@ -4114,33 +4723,37 @@
       <c r="E55" s="11">
         <v>50</v>
       </c>
-      <c r="F55" s="24"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="24"/>
-      <c r="I55" s="24"/>
-      <c r="J55" s="24"/>
-      <c r="K55" s="24"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="24"/>
-      <c r="N55" s="24"/>
-      <c r="O55" s="24"/>
-      <c r="P55" s="24"/>
-      <c r="Q55" s="24"/>
+      <c r="F55" s="9">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14">
+        <v>15</v>
+      </c>
+      <c r="H55" s="14"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
+      <c r="O55" s="14"/>
+      <c r="P55" s="14"/>
+      <c r="Q55" s="14"/>
       <c r="R55" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S55" s="21">
-        <f>E55+G55+I55+K55+M55+O55+Q55</f>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S55" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>28</v>
@@ -4151,33 +4764,37 @@
       <c r="E56" s="11">
         <v>50</v>
       </c>
-      <c r="F56" s="24"/>
-      <c r="G56" s="24"/>
-      <c r="H56" s="24"/>
-      <c r="I56" s="24"/>
-      <c r="J56" s="24"/>
-      <c r="K56" s="24"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="24"/>
-      <c r="N56" s="24"/>
-      <c r="O56" s="24"/>
-      <c r="P56" s="24"/>
-      <c r="Q56" s="24"/>
+      <c r="F56" s="9">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14">
+        <v>15</v>
+      </c>
+      <c r="H56" s="14"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
+      <c r="O56" s="14"/>
+      <c r="P56" s="14"/>
+      <c r="Q56" s="14"/>
       <c r="R56" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S56" s="21">
-        <f>E56+G56+I56+K56+M56+O56+Q56</f>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S56" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>28</v>
@@ -4188,8 +4805,12 @@
       <c r="E57" s="11">
         <v>50</v>
       </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+      <c r="F57" s="9">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14">
+        <v>15</v>
+      </c>
       <c r="H57" s="14"/>
       <c r="I57" s="14"/>
       <c r="J57" s="14"/>
@@ -4201,20 +4822,20 @@
       <c r="P57" s="14"/>
       <c r="Q57" s="14"/>
       <c r="R57" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S57" s="21">
-        <f>E57+G57+I57+K57+M57+O57+Q57</f>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S57" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>96</v>
+        <v>61</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>28</v>
@@ -4225,8 +4846,12 @@
       <c r="E58" s="11">
         <v>50</v>
       </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+      <c r="F58" s="9">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14">
+        <v>15</v>
+      </c>
       <c r="H58" s="14"/>
       <c r="I58" s="14"/>
       <c r="J58" s="14"/>
@@ -4238,20 +4863,20 @@
       <c r="P58" s="14"/>
       <c r="Q58" s="14"/>
       <c r="R58" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S58" s="15">
-        <f>E58+G58+I58+K58+M58+O58+Q58</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>28</v>
@@ -4262,8 +4887,12 @@
       <c r="E59" s="11">
         <v>50</v>
       </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="F59" s="9">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14">
+        <v>15</v>
+      </c>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="14"/>
@@ -4275,18 +4904,182 @@
       <c r="P59" s="14"/>
       <c r="Q59" s="14"/>
       <c r="R59" s="4">
-        <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S59" s="15">
-        <f>E59+G59+I59+K59+M59+O59+Q59</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A60" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D60" s="11">
+        <v>1</v>
+      </c>
+      <c r="E60" s="11">
+        <v>50</v>
+      </c>
+      <c r="F60" s="11">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14">
+        <v>15</v>
+      </c>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="17">
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S60" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="11">
+        <v>1</v>
+      </c>
+      <c r="E61" s="11">
+        <v>50</v>
+      </c>
+      <c r="F61" s="11">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14">
+        <v>15</v>
+      </c>
+      <c r="H61" s="14"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
+      <c r="O61" s="14"/>
+      <c r="P61" s="14"/>
+      <c r="Q61" s="14"/>
+      <c r="R61" s="17">
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S61" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A62" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="11">
+        <v>1</v>
+      </c>
+      <c r="E62" s="11">
+        <v>50</v>
+      </c>
+      <c r="F62" s="11">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14">
+        <v>15</v>
+      </c>
+      <c r="H62" s="14"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
+      <c r="O62" s="14"/>
+      <c r="P62" s="14"/>
+      <c r="Q62" s="14"/>
+      <c r="R62" s="17">
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S62" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A63" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D63" s="11">
+        <v>1</v>
+      </c>
+      <c r="E63" s="11">
+        <v>50</v>
+      </c>
+      <c r="F63" s="11">
+        <v>1</v>
+      </c>
+      <c r="G63" s="14">
+        <v>15</v>
+      </c>
+      <c r="H63" s="14"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
+      <c r="O63" s="14"/>
+      <c r="P63" s="14"/>
+      <c r="Q63" s="14"/>
+      <c r="R63" s="17">
+        <f t="shared" si="2"/>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S63" s="15">
+        <f t="shared" si="3"/>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:S60">
-    <sortCondition ref="C2:C60"/>
+  <autoFilter ref="F1:F59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:S65">
+    <sortCondition ref="C2:C65"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="P1:Q1"/>
@@ -4306,13 +5099,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13379CDE-009D-7047-85BE-05DF9DB1A0A1}">
-  <dimension ref="A3:C10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA253C9-3F5D-9F42-B702-C982D2131A8F}">
+  <dimension ref="A3:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -4320,91 +5113,112 @@
         <v>116</v>
       </c>
       <c r="B3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" t="s">
         <v>119</v>
-      </c>
-      <c r="C3" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="7">
-        <v>0.14285714285714282</v>
-      </c>
-      <c r="C4">
-        <v>50</v>
+      <c r="B4">
+        <v>65</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0.28571428571428564</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="7">
-        <v>0.14285714285714282</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
+        <v>135</v>
+      </c>
+      <c r="B5">
+        <v>50</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0.24489795918367344</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" s="7">
-        <v>0.14285714285714282</v>
-      </c>
-      <c r="C6">
-        <v>150</v>
+        <v>31</v>
+      </c>
+      <c r="B6">
+        <v>65</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0.27142857142857135</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="7">
-        <v>0.14285714285714282</v>
-      </c>
-      <c r="C7">
-        <v>50</v>
+        <v>66</v>
+      </c>
+      <c r="B7">
+        <v>150</v>
+      </c>
+      <c r="C7" s="7">
+        <v>0.19047619047619047</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="7">
-        <v>0.14285714285714282</v>
-      </c>
-      <c r="C8">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="B8">
+        <v>50</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.25714285714285706</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="7">
+        <v>149</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9" s="7">
         <v>0.14285714285714285</v>
-      </c>
-      <c r="C9">
-        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10">
+        <v>150</v>
+      </c>
+      <c r="C10" s="7">
+        <v>0.28571428571428564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>65</v>
+      </c>
+      <c r="C11" s="7">
+        <v>0.28571428571428564</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7">
-        <v>0.14285714285714296</v>
-      </c>
-      <c r="C10">
-        <v>63.953488372093027</v>
+      <c r="B12">
+        <v>74.672131147540981</v>
+      </c>
+      <c r="C12" s="7">
+        <v>0.25526932084309156</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08B9BB7-057E-8D43-B7A2-73B4A012A50F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E1A4D8-2BA0-D946-AD03-D8AB09E0CE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -628,7 +628,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -662,7 +662,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -681,19 +680,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -713,7 +719,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46110.424964351849" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46124.457464467596" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -740,19 +746,19 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L1 XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="150"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="50" maxValue="150"/>
     </cacheField>
     <cacheField name="L2 Presenza" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L2 XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="100"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="115"/>
     </cacheField>
     <cacheField name="L3 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L3 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-5" maxValue="100"/>
     </cacheField>
     <cacheField name="L4 Presenza" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -779,15 +785,10 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.2857142857142857"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.42857142857142855"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="150" count="4">
-        <n v="65"/>
-        <n v="50"/>
-        <n v="150"/>
-        <n v="0"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45" maxValue="215"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -808,18 +809,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -829,18 +830,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -850,18 +851,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -871,18 +872,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -892,8 +893,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="30"/>
     <m/>
     <m/>
     <m/>
@@ -903,7 +904,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -913,18 +914,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -934,18 +935,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="30"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="95"/>
   </r>
   <r>
     <s v="Cuomo"/>
@@ -955,18 +956,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Ercolano"/>
@@ -976,18 +977,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Forte"/>
@@ -997,18 +998,18 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1018,18 +1019,18 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Paone"/>
@@ -1039,18 +1040,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Petrone"/>
@@ -1060,8 +1061,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1071,7 +1072,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Preteverde"/>
@@ -1081,18 +1082,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Baudrand"/>
@@ -1101,19 +1102,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Borreca"/>
@@ -1122,19 +1123,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Borrione"/>
@@ -1143,19 +1144,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Cappelluccio"/>
@@ -1164,19 +1165,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Casale"/>
@@ -1185,9 +1186,9 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
+    <n v="115"/>
+    <n v="0"/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
@@ -1197,7 +1198,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Marrazzo"/>
@@ -1206,19 +1207,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Miles"/>
@@ -1227,19 +1228,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Parente"/>
@@ -1248,19 +1249,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Pietropaolo"/>
@@ -1269,19 +1270,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Rispoli"/>
@@ -1290,19 +1291,19 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="115"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Maione"/>
@@ -1312,18 +1313,18 @@
     <n v="150"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Nasti"/>
@@ -1333,18 +1334,18 @@
     <n v="150"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Noviello"/>
@@ -1354,18 +1355,18 @@
     <n v="150"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Pepe"/>
@@ -1375,18 +1376,18 @@
     <n v="150"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Tartaro"/>
@@ -1396,8 +1397,8 @@
     <n v="150"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1407,7 +1408,7 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <x v="2"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Versi"/>
@@ -1417,18 +1418,18 @@
     <n v="150"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Borrelli"/>
@@ -1438,8 +1439,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1449,7 +1450,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Canzolino"/>
@@ -1459,18 +1460,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="De Siena"/>
@@ -1480,18 +1481,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Di Meglio"/>
@@ -1501,18 +1502,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Esposito"/>
@@ -1522,8 +1523,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1533,7 +1534,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Ferrante"/>
@@ -1543,18 +1544,18 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Maglietta"/>
@@ -1564,8 +1565,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1575,7 +1576,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Patroni Griffi"/>
@@ -1585,18 +1586,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Semioli"/>
@@ -1606,8 +1607,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1617,7 +1618,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Siano"/>
@@ -1627,8 +1628,8 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1638,60 +1639,60 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <x v="1"/>
+    <n v="50"/>
   </r>
   <r>
     <s v="Agliottone"/>
     <s v="Davide"/>
     <x v="5"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="3"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="-5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="45"/>
   </r>
   <r>
     <s v="Gallo"/>
     <s v="Gennaro"/>
     <x v="5"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="3"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="-5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="45"/>
   </r>
   <r>
     <s v="Imperatore"/>
     <s v="Luca"/>
     <x v="5"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
-    <m/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="-5"/>
     <m/>
     <m/>
     <m/>
@@ -1701,28 +1702,28 @@
     <m/>
     <m/>
     <n v="0.14285714285714285"/>
-    <x v="3"/>
+    <n v="45"/>
   </r>
   <r>
     <s v="Monaco"/>
     <s v="Marcello"/>
     <x v="5"/>
     <n v="0"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
-    <x v="3"/>
+    <n v="50"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="-5"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
+    <n v="45"/>
   </r>
   <r>
     <s v="Cerundolo"/>
@@ -1731,6 +1732,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1740,10 +1743,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Chieti"/>
@@ -1752,6 +1753,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1761,10 +1764,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Coda"/>
@@ -1773,6 +1774,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1782,10 +1785,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Dibartolomeo"/>
@@ -1794,6 +1795,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1803,10 +1806,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Raduazzo"/>
@@ -1815,6 +1816,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1824,10 +1827,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Vable"/>
@@ -1836,6 +1837,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1845,10 +1848,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Zito"/>
@@ -1857,6 +1858,8 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
     <n v="100"/>
     <m/>
     <m/>
@@ -1866,10 +1869,8 @@
     <m/>
     <m/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="2"/>
+    <n v="0.42857142857142855"/>
+    <n v="150"/>
   </r>
   <r>
     <s v="Antico"/>
@@ -1879,18 +1880,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="D'Acunto"/>
@@ -1900,8 +1901,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1911,7 +1912,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Di Fiore"/>
@@ -1921,8 +1922,8 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1932,7 +1933,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Ditri"/>
@@ -1942,18 +1943,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Fraddanno"/>
@@ -1963,18 +1964,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Marciello"/>
@@ -1984,18 +1985,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Miranda"/>
@@ -2005,18 +2006,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Rolletta"/>
@@ -2026,18 +2027,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Soriano"/>
@@ -2047,18 +2048,18 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Vitale"/>
@@ -2068,24 +2069,24 @@
     <n v="50"/>
     <n v="1"/>
     <n v="15"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <x v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -2473,34 +2474,34 @@
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="8" style="19" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="8" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="8" customWidth="1"/>
+    <col min="7" max="7" width="8" style="18" customWidth="1"/>
+    <col min="8" max="8" width="11" style="18" customWidth="1"/>
+    <col min="9" max="9" width="8" style="18" customWidth="1"/>
+    <col min="10" max="10" width="11" style="18" customWidth="1"/>
+    <col min="11" max="11" width="8" style="18" customWidth="1"/>
+    <col min="12" max="12" width="11" style="18" customWidth="1"/>
+    <col min="13" max="13" width="8" style="18" customWidth="1"/>
+    <col min="14" max="14" width="11" style="18" customWidth="1"/>
+    <col min="15" max="15" width="8" style="18" customWidth="1"/>
+    <col min="16" max="16" width="11" style="18" customWidth="1"/>
+    <col min="17" max="17" width="8" style="18" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
+      <c r="A1" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
       <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="21"/>
+      <c r="E1" s="23"/>
       <c r="F1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="21"/>
+      <c r="G1" s="23"/>
       <c r="H1" s="20" t="s">
         <v>3</v>
       </c>
@@ -2521,10 +2522,10 @@
         <v>7</v>
       </c>
       <c r="Q1" s="21"/>
-      <c r="R1" s="23" t="s">
+      <c r="R1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="23"/>
+      <c r="S1" s="24"/>
     </row>
     <row r="2" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2601,29 +2602,33 @@
       <c r="E3" s="9">
         <v>50</v>
       </c>
-      <c r="F3" s="16">
-        <v>1</v>
-      </c>
-      <c r="G3" s="18">
+      <c r="F3" s="15">
+        <v>1</v>
+      </c>
+      <c r="G3" s="17">
         <v>15</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
+      <c r="H3" s="17">
+        <v>1</v>
+      </c>
+      <c r="I3" s="17">
+        <v>30</v>
+      </c>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2642,29 +2647,33 @@
       <c r="E4" s="9">
         <v>50</v>
       </c>
-      <c r="F4" s="16">
-        <v>1</v>
-      </c>
-      <c r="G4" s="18">
+      <c r="F4" s="15">
+        <v>1</v>
+      </c>
+      <c r="G4" s="17">
         <v>15</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
+      <c r="H4" s="17">
+        <v>1</v>
+      </c>
+      <c r="I4" s="17">
+        <v>30</v>
+      </c>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2683,29 +2692,33 @@
       <c r="E5" s="9">
         <v>50</v>
       </c>
-      <c r="F5" s="16">
-        <v>1</v>
-      </c>
-      <c r="G5" s="18">
+      <c r="F5" s="15">
+        <v>1</v>
+      </c>
+      <c r="G5" s="17">
         <v>15</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
+      <c r="H5" s="17">
+        <v>1</v>
+      </c>
+      <c r="I5" s="17">
+        <v>30</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17"/>
+      <c r="O5" s="17"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="17"/>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2724,29 +2737,33 @@
       <c r="E6" s="9">
         <v>50</v>
       </c>
-      <c r="F6" s="16">
-        <v>1</v>
-      </c>
-      <c r="G6" s="18">
+      <c r="F6" s="15">
+        <v>1</v>
+      </c>
+      <c r="G6" s="17">
         <v>15</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
+      <c r="H6" s="17">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17">
+        <v>30</v>
+      </c>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2765,29 +2782,33 @@
       <c r="E7" s="9">
         <v>50</v>
       </c>
-      <c r="F7" s="16">
-        <v>1</v>
-      </c>
-      <c r="G7" s="18">
+      <c r="F7" s="15">
+        <v>1</v>
+      </c>
+      <c r="G7" s="17">
         <v>15</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
+      <c r="H7" s="17">
+        <v>0</v>
+      </c>
+      <c r="I7" s="17">
+        <v>30</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="Q7" s="17"/>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2806,29 +2827,33 @@
       <c r="E8" s="9">
         <v>50</v>
       </c>
-      <c r="F8" s="16">
-        <v>1</v>
-      </c>
-      <c r="G8" s="18">
+      <c r="F8" s="15">
+        <v>1</v>
+      </c>
+      <c r="G8" s="17">
         <v>15</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
+      <c r="H8" s="17">
+        <v>1</v>
+      </c>
+      <c r="I8" s="17">
+        <v>30</v>
+      </c>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2847,29 +2872,33 @@
       <c r="E9" s="9">
         <v>50</v>
       </c>
-      <c r="F9" s="16">
-        <v>1</v>
-      </c>
-      <c r="G9" s="18">
+      <c r="F9" s="15">
+        <v>1</v>
+      </c>
+      <c r="G9" s="17">
         <v>15</v>
       </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
+      <c r="H9" s="17">
+        <v>1</v>
+      </c>
+      <c r="I9" s="17">
+        <v>30</v>
+      </c>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -2888,25 +2917,29 @@
       <c r="E10" s="9">
         <v>50</v>
       </c>
-      <c r="F10" s="16">
-        <v>1</v>
-      </c>
-      <c r="G10" s="18">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
+      <c r="F10" s="15">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17">
+        <v>1</v>
+      </c>
+      <c r="I10" s="17">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
@@ -2929,25 +2962,29 @@
       <c r="E11" s="9">
         <v>50</v>
       </c>
-      <c r="F11" s="16">
-        <v>1</v>
-      </c>
-      <c r="G11" s="18">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
+      <c r="F11" s="15">
+        <v>1</v>
+      </c>
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="17">
+        <v>1</v>
+      </c>
+      <c r="I11" s="17">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+      <c r="N11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17"/>
+      <c r="Q11" s="17"/>
       <c r="R11" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S11" s="3">
         <f t="shared" si="1"/>
@@ -2970,25 +3007,29 @@
       <c r="E12" s="9">
         <v>50</v>
       </c>
-      <c r="F12" s="16">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
+      <c r="F12" s="15">
+        <v>0</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1</v>
+      </c>
+      <c r="I12" s="17">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
       <c r="R12" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S12" s="3">
         <f t="shared" si="1"/>
@@ -3011,25 +3052,29 @@
       <c r="E13" s="9">
         <v>50</v>
       </c>
-      <c r="F13" s="16">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
+      <c r="F13" s="15">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>1</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
       <c r="R13" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S13" s="3">
         <f t="shared" si="1"/>
@@ -3052,25 +3097,29 @@
       <c r="E14" s="9">
         <v>50</v>
       </c>
-      <c r="F14" s="16">
-        <v>1</v>
-      </c>
-      <c r="G14" s="18">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
+      <c r="F14" s="15">
+        <v>1</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1</v>
+      </c>
+      <c r="I14" s="17">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
       <c r="R14" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S14" s="3">
         <f t="shared" si="1"/>
@@ -3093,22 +3142,26 @@
       <c r="E15" s="9">
         <v>50</v>
       </c>
-      <c r="F15" s="16">
-        <v>1</v>
-      </c>
-      <c r="G15" s="18">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
+      <c r="F15" s="15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="17">
+        <v>0</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0</v>
+      </c>
+      <c r="I15" s="17">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
       <c r="R15" s="4">
         <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
@@ -3134,25 +3187,29 @@
       <c r="E16" s="9">
         <v>50</v>
       </c>
-      <c r="F16" s="16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="18">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
+      <c r="F16" s="15">
+        <v>1</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="17"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
       <c r="R16" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S16" s="3">
         <f t="shared" si="1"/>
@@ -3181,8 +3238,12 @@
       <c r="G17" s="9">
         <v>115</v>
       </c>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="H17" s="9">
+        <v>1</v>
+      </c>
+      <c r="I17" s="9">
+        <v>50</v>
+      </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -3193,11 +3254,11 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S17" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
@@ -3222,8 +3283,12 @@
       <c r="G18" s="9">
         <v>115</v>
       </c>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
+      <c r="H18" s="9">
+        <v>1</v>
+      </c>
+      <c r="I18" s="9">
+        <v>50</v>
+      </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
@@ -3234,11 +3299,11 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -3263,8 +3328,12 @@
       <c r="G19" s="9">
         <v>115</v>
       </c>
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
+      <c r="H19" s="9">
+        <v>1</v>
+      </c>
+      <c r="I19" s="9">
+        <v>50</v>
+      </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -3275,11 +3344,11 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -3304,8 +3373,12 @@
       <c r="G20" s="9">
         <v>115</v>
       </c>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
+      <c r="H20" s="9">
+        <v>1</v>
+      </c>
+      <c r="I20" s="9">
+        <v>50</v>
+      </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -3316,11 +3389,11 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -3345,8 +3418,12 @@
       <c r="G21" s="9">
         <v>115</v>
       </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
+      <c r="H21" s="9">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9">
+        <v>50</v>
+      </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -3361,7 +3438,7 @@
       </c>
       <c r="S21" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -3386,8 +3463,12 @@
       <c r="G22" s="9">
         <v>115</v>
       </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
+      <c r="H22" s="9">
+        <v>1</v>
+      </c>
+      <c r="I22" s="9">
+        <v>50</v>
+      </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -3398,11 +3479,11 @@
       <c r="Q22" s="9"/>
       <c r="R22" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S22" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -3427,8 +3508,12 @@
       <c r="G23" s="9">
         <v>115</v>
       </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
+      <c r="H23" s="9">
+        <v>1</v>
+      </c>
+      <c r="I23" s="9">
+        <v>50</v>
+      </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -3439,11 +3524,11 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -3468,8 +3553,12 @@
       <c r="G24" s="9">
         <v>115</v>
       </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
+      <c r="H24" s="9">
+        <v>1</v>
+      </c>
+      <c r="I24" s="9">
+        <v>50</v>
+      </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
@@ -3480,11 +3569,11 @@
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S24" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -3509,8 +3598,12 @@
       <c r="G25" s="9">
         <v>115</v>
       </c>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
+      <c r="H25" s="9">
+        <v>1</v>
+      </c>
+      <c r="I25" s="9">
+        <v>50</v>
+      </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -3521,11 +3614,11 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -3550,8 +3643,12 @@
       <c r="G26" s="9">
         <v>115</v>
       </c>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
+      <c r="H26" s="9">
+        <v>1</v>
+      </c>
+      <c r="I26" s="9">
+        <v>50</v>
+      </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
@@ -3562,11 +3659,11 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="1"/>
-        <v>165</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -3591,8 +3688,12 @@
       <c r="G27" s="9">
         <v>0</v>
       </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
+      <c r="H27" s="9">
+        <v>1</v>
+      </c>
+      <c r="I27" s="9">
+        <v>0</v>
+      </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -3603,7 +3704,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="1"/>
@@ -3632,8 +3733,12 @@
       <c r="G28" s="9">
         <v>0</v>
       </c>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
+      <c r="H28" s="9">
+        <v>1</v>
+      </c>
+      <c r="I28" s="9">
+        <v>0</v>
+      </c>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
@@ -3644,7 +3749,7 @@
       <c r="Q28" s="9"/>
       <c r="R28" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S28" s="3">
         <f t="shared" si="1"/>
@@ -3673,8 +3778,12 @@
       <c r="G29" s="9">
         <v>0</v>
       </c>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
+      <c r="H29" s="9">
+        <v>1</v>
+      </c>
+      <c r="I29" s="9">
+        <v>0</v>
+      </c>
       <c r="J29" s="9"/>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
@@ -3685,7 +3794,7 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S29" s="3">
         <f t="shared" si="1"/>
@@ -3714,8 +3823,12 @@
       <c r="G30" s="9">
         <v>0</v>
       </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
+      <c r="H30" s="9">
+        <v>1</v>
+      </c>
+      <c r="I30" s="9">
+        <v>0</v>
+      </c>
       <c r="J30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
@@ -3726,7 +3839,7 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S30" s="3">
         <f t="shared" si="1"/>
@@ -3755,8 +3868,12 @@
       <c r="G31" s="9">
         <v>0</v>
       </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
+      <c r="H31" s="9">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9">
+        <v>0</v>
+      </c>
       <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
@@ -3796,8 +3913,12 @@
       <c r="G32" s="9">
         <v>0</v>
       </c>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
+      <c r="H32" s="9">
+        <v>1</v>
+      </c>
+      <c r="I32" s="9">
+        <v>0</v>
+      </c>
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
@@ -3808,7 +3929,7 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S32" s="3">
         <f t="shared" si="1"/>
@@ -3837,8 +3958,12 @@
       <c r="G33" s="9">
         <v>0</v>
       </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
+      <c r="H33" s="9">
+        <v>0</v>
+      </c>
+      <c r="I33" s="9">
+        <v>0</v>
+      </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
@@ -3878,8 +4003,12 @@
       <c r="G34" s="9">
         <v>0</v>
       </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
+      <c r="H34" s="9">
+        <v>1</v>
+      </c>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
       <c r="J34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
@@ -3890,7 +4019,7 @@
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S34" s="3">
         <f t="shared" si="1"/>
@@ -3919,8 +4048,12 @@
       <c r="G35" s="9">
         <v>0</v>
       </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="9"/>
+      <c r="H35" s="9">
+        <v>1</v>
+      </c>
+      <c r="I35" s="9">
+        <v>0</v>
+      </c>
       <c r="J35" s="9"/>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
@@ -3931,7 +4064,7 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
         <f t="shared" ref="R35:R63" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S35" s="3">
         <f t="shared" ref="S35:S63" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
@@ -3960,8 +4093,12 @@
       <c r="G36" s="9">
         <v>0</v>
       </c>
-      <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
+      <c r="H36" s="9">
+        <v>1</v>
+      </c>
+      <c r="I36" s="9">
+        <v>0</v>
+      </c>
       <c r="J36" s="9"/>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
@@ -3972,7 +4109,7 @@
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S36" s="3">
         <f t="shared" si="3"/>
@@ -4001,8 +4138,12 @@
       <c r="G37" s="9">
         <v>0</v>
       </c>
-      <c r="H37" s="9"/>
-      <c r="I37" s="9"/>
+      <c r="H37" s="9">
+        <v>0</v>
+      </c>
+      <c r="I37" s="9">
+        <v>0</v>
+      </c>
       <c r="J37" s="9"/>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
@@ -4042,8 +4183,12 @@
       <c r="G38" s="9">
         <v>0</v>
       </c>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
+      <c r="H38" s="9">
+        <v>1</v>
+      </c>
+      <c r="I38" s="9">
+        <v>0</v>
+      </c>
       <c r="J38" s="9"/>
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
@@ -4054,7 +4199,7 @@
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S38" s="3">
         <f t="shared" si="3"/>
@@ -4083,8 +4228,12 @@
       <c r="G39" s="9">
         <v>0</v>
       </c>
-      <c r="H39" s="9"/>
-      <c r="I39" s="9"/>
+      <c r="H39" s="9">
+        <v>0</v>
+      </c>
+      <c r="I39" s="9">
+        <v>0</v>
+      </c>
       <c r="J39" s="9"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
@@ -4124,8 +4273,12 @@
       <c r="G40" s="9">
         <v>0</v>
       </c>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
+      <c r="H40" s="9">
+        <v>1</v>
+      </c>
+      <c r="I40" s="9">
+        <v>0</v>
+      </c>
       <c r="J40" s="9"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
@@ -4136,7 +4289,7 @@
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S40" s="3">
         <f t="shared" si="3"/>
@@ -4165,8 +4318,12 @@
       <c r="G41" s="9">
         <v>0</v>
       </c>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
+      <c r="H41" s="9">
+        <v>0</v>
+      </c>
+      <c r="I41" s="9">
+        <v>0</v>
+      </c>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
@@ -4206,8 +4363,12 @@
       <c r="G42" s="9">
         <v>0</v>
       </c>
-      <c r="H42" s="9"/>
-      <c r="I42" s="9"/>
+      <c r="H42" s="9">
+        <v>0</v>
+      </c>
+      <c r="I42" s="9">
+        <v>0</v>
+      </c>
       <c r="J42" s="9"/>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
@@ -4239,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F43" s="9">
         <v>1</v>
@@ -4247,23 +4408,27 @@
       <c r="G43" s="9">
         <v>0</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
+      <c r="H43" s="17">
+        <v>1</v>
+      </c>
+      <c r="I43" s="17">
+        <v>-5</v>
+      </c>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="L43" s="17"/>
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
       <c r="R43" s="4">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S43" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
@@ -4280,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F44" s="9">
         <v>1</v>
@@ -4288,23 +4453,27 @@
       <c r="G44" s="9">
         <v>0</v>
       </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13"/>
-      <c r="Q44" s="13"/>
+      <c r="H44" s="17">
+        <v>1</v>
+      </c>
+      <c r="I44" s="17">
+        <v>-5</v>
+      </c>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
       <c r="R44" s="4">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S44" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
@@ -4321,7 +4490,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F45" s="9">
         <v>1</v>
@@ -4329,23 +4498,27 @@
       <c r="G45" s="9">
         <v>0</v>
       </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
+      <c r="H45" s="17">
+        <v>0</v>
+      </c>
+      <c r="I45" s="17">
+        <v>-5</v>
+      </c>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
       <c r="R45" s="4">
         <f t="shared" si="2"/>
         <v>0.14285714285714285</v>
       </c>
       <c r="S45" s="3">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -4361,22 +4534,28 @@
       <c r="D46" s="11">
         <v>0</v>
       </c>
-      <c r="E46" s="11">
-        <v>0</v>
+      <c r="E46" s="9">
+        <v>50</v>
       </c>
       <c r="F46" s="9">
         <v>1</v>
       </c>
       <c r="G46" s="9">
         <v>0</v>
+      </c>
+      <c r="H46" s="19">
+        <v>1</v>
+      </c>
+      <c r="I46" s="17">
+        <v>-5</v>
       </c>
       <c r="R46" s="4">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -4398,26 +4577,30 @@
       <c r="F47" s="9">
         <v>1</v>
       </c>
-      <c r="G47" s="14">
-        <v>0</v>
-      </c>
-      <c r="H47" s="14"/>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
+        <v>1</v>
+      </c>
+      <c r="I47" s="13">
+        <v>100</v>
+      </c>
+      <c r="J47" s="13"/>
+      <c r="K47" s="13"/>
+      <c r="L47" s="13"/>
+      <c r="M47" s="13"/>
+      <c r="N47" s="13"/>
+      <c r="O47" s="13"/>
+      <c r="P47" s="13"/>
+      <c r="Q47" s="13"/>
       <c r="R47" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S47" s="12">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
@@ -4439,26 +4622,30 @@
       <c r="F48" s="9">
         <v>1</v>
       </c>
-      <c r="G48" s="14">
-        <v>0</v>
-      </c>
-      <c r="H48" s="14"/>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14"/>
-      <c r="Q48" s="14"/>
+      <c r="G48" s="13">
+        <v>0</v>
+      </c>
+      <c r="H48" s="13">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13">
+        <v>100</v>
+      </c>
+      <c r="J48" s="13"/>
+      <c r="K48" s="13"/>
+      <c r="L48" s="13"/>
+      <c r="M48" s="13"/>
+      <c r="N48" s="13"/>
+      <c r="O48" s="13"/>
+      <c r="P48" s="13"/>
+      <c r="Q48" s="13"/>
       <c r="R48" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S48" s="12">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
@@ -4480,26 +4667,30 @@
       <c r="F49" s="9">
         <v>1</v>
       </c>
-      <c r="G49" s="14">
-        <v>0</v>
-      </c>
-      <c r="H49" s="14"/>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="14"/>
-      <c r="Q49" s="14"/>
+      <c r="G49" s="13">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
+        <v>1</v>
+      </c>
+      <c r="I49" s="13">
+        <v>100</v>
+      </c>
+      <c r="J49" s="13"/>
+      <c r="K49" s="13"/>
+      <c r="L49" s="13"/>
+      <c r="M49" s="13"/>
+      <c r="N49" s="13"/>
+      <c r="O49" s="13"/>
+      <c r="P49" s="13"/>
+      <c r="Q49" s="13"/>
       <c r="R49" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S49" s="12">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
@@ -4521,26 +4712,30 @@
       <c r="F50" s="9">
         <v>1</v>
       </c>
-      <c r="G50" s="14">
-        <v>0</v>
-      </c>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="14"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="14"/>
-      <c r="P50" s="14"/>
-      <c r="Q50" s="14"/>
+      <c r="G50" s="13">
+        <v>0</v>
+      </c>
+      <c r="H50" s="13">
+        <v>1</v>
+      </c>
+      <c r="I50" s="13">
+        <v>100</v>
+      </c>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13"/>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="13"/>
+      <c r="Q50" s="13"/>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S50" s="12">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
@@ -4562,26 +4757,30 @@
       <c r="F51" s="9">
         <v>1</v>
       </c>
-      <c r="G51" s="14">
-        <v>0</v>
-      </c>
-      <c r="H51" s="14"/>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
-      <c r="Q51" s="14"/>
+      <c r="G51" s="13">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
+        <v>1</v>
+      </c>
+      <c r="I51" s="13">
+        <v>100</v>
+      </c>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="L51" s="13"/>
+      <c r="M51" s="13"/>
+      <c r="N51" s="13"/>
+      <c r="O51" s="13"/>
+      <c r="P51" s="13"/>
+      <c r="Q51" s="13"/>
       <c r="R51" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S51" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S51" s="14">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -4603,26 +4802,30 @@
       <c r="F52" s="9">
         <v>1</v>
       </c>
-      <c r="G52" s="14">
-        <v>0</v>
-      </c>
-      <c r="H52" s="14"/>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="14"/>
-      <c r="Q52" s="14"/>
+      <c r="G52" s="13">
+        <v>0</v>
+      </c>
+      <c r="H52" s="13">
+        <v>1</v>
+      </c>
+      <c r="I52" s="13">
+        <v>100</v>
+      </c>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
       <c r="R52" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S52" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S52" s="14">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -4644,26 +4847,30 @@
       <c r="F53" s="9">
         <v>1</v>
       </c>
-      <c r="G53" s="14">
-        <v>0</v>
-      </c>
-      <c r="H53" s="14"/>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="14"/>
-      <c r="Q53" s="14"/>
+      <c r="G53" s="13">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
+        <v>1</v>
+      </c>
+      <c r="I53" s="13">
+        <v>100</v>
+      </c>
+      <c r="J53" s="13"/>
+      <c r="K53" s="13"/>
+      <c r="L53" s="13"/>
+      <c r="M53" s="13"/>
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+      <c r="P53" s="13"/>
+      <c r="Q53" s="13"/>
       <c r="R53" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S53" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S53" s="14">
         <f t="shared" si="3"/>
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -4685,24 +4892,28 @@
       <c r="F54" s="9">
         <v>1</v>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="13">
         <v>15</v>
       </c>
-      <c r="H54" s="14"/>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="14"/>
-      <c r="Q54" s="14"/>
+      <c r="H54" s="13">
+        <v>1</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13"/>
+      <c r="K54" s="13"/>
+      <c r="L54" s="13"/>
+      <c r="M54" s="13"/>
+      <c r="N54" s="13"/>
+      <c r="O54" s="13"/>
+      <c r="P54" s="13"/>
+      <c r="Q54" s="13"/>
       <c r="R54" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S54" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S54" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4726,24 +4937,28 @@
       <c r="F55" s="9">
         <v>1</v>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="13">
         <v>15</v>
       </c>
-      <c r="H55" s="14"/>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="14"/>
-      <c r="Q55" s="14"/>
+      <c r="H55" s="13">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13">
+        <v>0</v>
+      </c>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
+      <c r="N55" s="13"/>
+      <c r="O55" s="13"/>
+      <c r="P55" s="13"/>
+      <c r="Q55" s="13"/>
       <c r="R55" s="4">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="S55" s="15">
+      <c r="S55" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4767,24 +4982,28 @@
       <c r="F56" s="9">
         <v>1</v>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="13">
         <v>15</v>
       </c>
-      <c r="H56" s="14"/>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="14"/>
-      <c r="N56" s="14"/>
-      <c r="O56" s="14"/>
-      <c r="P56" s="14"/>
-      <c r="Q56" s="14"/>
+      <c r="H56" s="13">
+        <v>0</v>
+      </c>
+      <c r="I56" s="13">
+        <v>0</v>
+      </c>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+      <c r="L56" s="13"/>
+      <c r="M56" s="13"/>
+      <c r="N56" s="13"/>
+      <c r="O56" s="13"/>
+      <c r="P56" s="13"/>
+      <c r="Q56" s="13"/>
       <c r="R56" s="4">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="S56" s="15">
+      <c r="S56" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4808,24 +5027,28 @@
       <c r="F57" s="9">
         <v>1</v>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="13">
         <v>15</v>
       </c>
-      <c r="H57" s="14"/>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-      <c r="P57" s="14"/>
-      <c r="Q57" s="14"/>
+      <c r="H57" s="13">
+        <v>1</v>
+      </c>
+      <c r="I57" s="13">
+        <v>0</v>
+      </c>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13"/>
+      <c r="O57" s="13"/>
+      <c r="P57" s="13"/>
+      <c r="Q57" s="13"/>
       <c r="R57" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S57" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S57" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4849,24 +5072,28 @@
       <c r="F58" s="9">
         <v>1</v>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="13">
         <v>15</v>
       </c>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="14"/>
-      <c r="Q58" s="14"/>
+      <c r="H58" s="13">
+        <v>1</v>
+      </c>
+      <c r="I58" s="13">
+        <v>0</v>
+      </c>
+      <c r="J58" s="13"/>
+      <c r="K58" s="13"/>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13"/>
+      <c r="O58" s="13"/>
+      <c r="P58" s="13"/>
+      <c r="Q58" s="13"/>
       <c r="R58" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S58" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S58" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4890,24 +5117,28 @@
       <c r="F59" s="9">
         <v>1</v>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="13">
         <v>15</v>
       </c>
-      <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="14"/>
-      <c r="Q59" s="14"/>
+      <c r="H59" s="13">
+        <v>1</v>
+      </c>
+      <c r="I59" s="13">
+        <v>0</v>
+      </c>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
+      <c r="Q59" s="13"/>
       <c r="R59" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S59" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S59" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4931,24 +5162,28 @@
       <c r="F60" s="11">
         <v>1</v>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="13">
         <v>15</v>
       </c>
-      <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="14"/>
-      <c r="Q60" s="14"/>
-      <c r="R60" s="17">
+      <c r="H60" s="13">
+        <v>1</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13"/>
+      <c r="O60" s="13"/>
+      <c r="P60" s="13"/>
+      <c r="Q60" s="13"/>
+      <c r="R60" s="16">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S60" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S60" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -4972,24 +5207,28 @@
       <c r="F61" s="11">
         <v>1</v>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="13">
         <v>15</v>
       </c>
-      <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14"/>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="17">
+      <c r="H61" s="13">
+        <v>1</v>
+      </c>
+      <c r="I61" s="13">
+        <v>0</v>
+      </c>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13"/>
+      <c r="O61" s="13"/>
+      <c r="P61" s="13"/>
+      <c r="Q61" s="13"/>
+      <c r="R61" s="16">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S61" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S61" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -5013,24 +5252,28 @@
       <c r="F62" s="11">
         <v>1</v>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="13">
         <v>15</v>
       </c>
-      <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14"/>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="17">
+      <c r="H62" s="13">
+        <v>1</v>
+      </c>
+      <c r="I62" s="13">
+        <v>0</v>
+      </c>
+      <c r="J62" s="13"/>
+      <c r="K62" s="13"/>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13"/>
+      <c r="O62" s="13"/>
+      <c r="P62" s="13"/>
+      <c r="Q62" s="13"/>
+      <c r="R62" s="16">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S62" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S62" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -5054,24 +5297,28 @@
       <c r="F63" s="11">
         <v>1</v>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="13">
         <v>15</v>
       </c>
-      <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="14"/>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="17">
+      <c r="H63" s="13">
+        <v>1</v>
+      </c>
+      <c r="I63" s="13">
+        <v>0</v>
+      </c>
+      <c r="J63" s="13"/>
+      <c r="K63" s="13"/>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13"/>
+      <c r="O63" s="13"/>
+      <c r="P63" s="13"/>
+      <c r="Q63" s="13"/>
+      <c r="R63" s="16">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="S63" s="15">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S63" s="14">
         <f t="shared" si="3"/>
         <v>65</v>
       </c>
@@ -5103,9 +5350,9 @@
   <dimension ref="A3:C12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -5123,99 +5370,99 @@
       <c r="A4" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B4">
-        <v>65</v>
+      <c r="B4" s="26">
+        <v>95</v>
       </c>
       <c r="C4" s="7">
-        <v>0.28571428571428564</v>
+        <v>0.4081632653061224</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="26">
         <v>50</v>
       </c>
       <c r="C5" s="7">
-        <v>0.24489795918367344</v>
+        <v>0.36734693877551017</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6">
-        <v>65</v>
+      <c r="B6" s="26">
+        <v>215</v>
       </c>
       <c r="C6" s="7">
-        <v>0.27142857142857135</v>
+        <v>0.39999999999999991</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="26">
         <v>150</v>
       </c>
       <c r="C7" s="7">
-        <v>0.19047619047619047</v>
+        <v>0.30952380952380948</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="26">
         <v>50</v>
       </c>
       <c r="C8" s="7">
-        <v>0.25714285714285706</v>
+        <v>0.32857142857142851</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B9">
-        <v>0</v>
+      <c r="B9" s="26">
+        <v>45</v>
       </c>
       <c r="C9" s="7">
-        <v>0.14285714285714285</v>
+        <v>0.24999999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="26">
         <v>150</v>
       </c>
       <c r="C10" s="7">
-        <v>0.28571428571428564</v>
+        <v>0.42857142857142849</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="26">
         <v>65</v>
       </c>
       <c r="C11" s="7">
-        <v>0.28571428571428564</v>
+        <v>0.39999999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B12">
-        <v>74.672131147540981</v>
+      <c r="B12" s="26">
+        <v>105.65573770491804</v>
       </c>
       <c r="C12" s="7">
-        <v>0.25526932084309156</v>
+        <v>0.37002341920374682</v>
       </c>
     </row>
   </sheetData>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E1A4D8-2BA0-D946-AD03-D8AB09E0CE52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F721E69-697A-2941-A3D6-FEE65819BE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -719,7 +719,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46124.457464467596" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46131.405947916668" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -761,10 +761,10 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-5" maxValue="100"/>
     </cacheField>
     <cacheField name="L4 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L4 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="50"/>
     </cacheField>
     <cacheField name="L5 Presenza" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -785,7 +785,7 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.42857142857142855"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.5714285714285714"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45" maxValue="215"/>
@@ -811,16 +811,16 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -832,8 +832,8 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
@@ -841,7 +841,7 @@
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -853,16 +853,16 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -874,16 +874,16 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -895,8 +895,8 @@
     <n v="15"/>
     <n v="0"/>
     <n v="30"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
@@ -904,7 +904,7 @@
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="95"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -916,16 +916,16 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -937,16 +937,16 @@
     <n v="15"/>
     <n v="1"/>
     <n v="30"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="95"/>
+    <n v="1"/>
+    <n v="50"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
+    <n v="145"/>
   </r>
   <r>
     <s v="Cuomo"/>
@@ -958,15 +958,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -979,8 +979,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1000,15 +1000,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1021,8 +1021,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1042,15 +1042,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1063,8 +1063,8 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1084,15 +1084,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1105,15 +1105,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1126,15 +1126,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1147,15 +1147,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1168,15 +1168,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1189,15 +1189,15 @@
     <n v="115"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="215"/>
   </r>
   <r>
@@ -1210,8 +1210,8 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1231,15 +1231,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1252,8 +1252,8 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1273,15 +1273,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1294,15 +1294,15 @@
     <n v="115"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1315,15 +1315,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="150"/>
   </r>
   <r>
@@ -1336,8 +1336,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1357,15 +1357,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="150"/>
   </r>
   <r>
@@ -1378,15 +1378,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1399,15 +1399,15 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <n v="150"/>
   </r>
   <r>
@@ -1420,15 +1420,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="150"/>
   </r>
   <r>
@@ -1441,8 +1441,8 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1462,15 +1462,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1483,15 +1483,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1504,15 +1504,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1525,8 +1525,8 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1546,15 +1546,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1567,15 +1567,15 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1588,15 +1588,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1609,8 +1609,8 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1630,15 +1630,15 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <n v="50"/>
   </r>
   <r>
@@ -1651,8 +1651,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-5"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1672,8 +1672,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-5"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1693,8 +1693,8 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-5"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1714,8 +1714,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-5"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1735,8 +1735,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1756,15 +1756,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1777,15 +1777,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1798,15 +1798,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1819,8 +1819,8 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1840,15 +1840,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1861,15 +1861,15 @@
     <n v="0"/>
     <n v="1"/>
     <n v="100"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1882,15 +1882,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -1903,8 +1903,8 @@
     <n v="15"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="0"/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1924,15 +1924,15 @@
     <n v="15"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="65"/>
   </r>
   <r>
@@ -1945,15 +1945,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -1966,15 +1966,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -1987,15 +1987,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -2008,15 +2008,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -2029,15 +2029,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -2050,15 +2050,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
   <r>
@@ -2071,15 +2071,15 @@
     <n v="15"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="65"/>
   </r>
 </pivotCacheRecords>
@@ -2614,8 +2614,12 @@
       <c r="I3" s="17">
         <v>30</v>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="J3" s="17">
+        <v>1</v>
+      </c>
+      <c r="K3" s="17">
+        <v>50</v>
+      </c>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
@@ -2624,11 +2628,11 @@
       <c r="Q3" s="17"/>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2659,8 +2663,12 @@
       <c r="I4" s="17">
         <v>30</v>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
+      <c r="J4" s="17">
+        <v>0</v>
+      </c>
+      <c r="K4" s="17">
+        <v>50</v>
+      </c>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
@@ -2673,7 +2681,7 @@
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2704,8 +2712,12 @@
       <c r="I5" s="17">
         <v>30</v>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
+      <c r="J5" s="17">
+        <v>1</v>
+      </c>
+      <c r="K5" s="17">
+        <v>50</v>
+      </c>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
@@ -2714,11 +2726,11 @@
       <c r="Q5" s="17"/>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2749,8 +2761,12 @@
       <c r="I6" s="17">
         <v>30</v>
       </c>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
+      <c r="J6" s="17">
+        <v>1</v>
+      </c>
+      <c r="K6" s="17">
+        <v>50</v>
+      </c>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
@@ -2759,11 +2775,11 @@
       <c r="Q6" s="17"/>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2794,8 +2810,12 @@
       <c r="I7" s="17">
         <v>30</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
+      <c r="J7" s="17">
+        <v>0</v>
+      </c>
+      <c r="K7" s="17">
+        <v>50</v>
+      </c>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
@@ -2808,7 +2828,7 @@
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2839,8 +2859,12 @@
       <c r="I8" s="17">
         <v>30</v>
       </c>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
+      <c r="J8" s="17">
+        <v>1</v>
+      </c>
+      <c r="K8" s="17">
+        <v>50</v>
+      </c>
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
@@ -2849,11 +2873,11 @@
       <c r="Q8" s="17"/>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2884,8 +2908,12 @@
       <c r="I9" s="17">
         <v>30</v>
       </c>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
+      <c r="J9" s="17">
+        <v>1</v>
+      </c>
+      <c r="K9" s="17">
+        <v>50</v>
+      </c>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
@@ -2894,11 +2922,11 @@
       <c r="Q9" s="17"/>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>95</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -2929,8 +2957,12 @@
       <c r="I10" s="17">
         <v>0</v>
       </c>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
+      <c r="J10" s="17">
+        <v>1</v>
+      </c>
+      <c r="K10" s="17">
+        <v>0</v>
+      </c>
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
@@ -2939,7 +2971,7 @@
       <c r="Q10" s="17"/>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
@@ -2974,8 +3006,12 @@
       <c r="I11" s="17">
         <v>0</v>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
+      <c r="J11" s="17">
+        <v>0</v>
+      </c>
+      <c r="K11" s="17">
+        <v>0</v>
+      </c>
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
@@ -3019,8 +3055,12 @@
       <c r="I12" s="17">
         <v>0</v>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
+      <c r="J12" s="17">
+        <v>1</v>
+      </c>
+      <c r="K12" s="17">
+        <v>0</v>
+      </c>
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
@@ -3029,7 +3069,7 @@
       <c r="Q12" s="17"/>
       <c r="R12" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S12" s="3">
         <f t="shared" si="1"/>
@@ -3064,8 +3104,12 @@
       <c r="I13" s="17">
         <v>0</v>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
@@ -3109,8 +3153,12 @@
       <c r="I14" s="17">
         <v>0</v>
       </c>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
+      <c r="J14" s="17">
+        <v>1</v>
+      </c>
+      <c r="K14" s="17">
+        <v>0</v>
+      </c>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
@@ -3119,7 +3167,7 @@
       <c r="Q14" s="17"/>
       <c r="R14" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S14" s="3">
         <f t="shared" si="1"/>
@@ -3154,8 +3202,12 @@
       <c r="I15" s="17">
         <v>0</v>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
+      <c r="J15" s="17">
+        <v>0</v>
+      </c>
+      <c r="K15" s="17">
+        <v>0</v>
+      </c>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
@@ -3199,8 +3251,12 @@
       <c r="I16" s="17">
         <v>0</v>
       </c>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
+      <c r="J16" s="17">
+        <v>1</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
@@ -3209,7 +3265,7 @@
       <c r="Q16" s="17"/>
       <c r="R16" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S16" s="3">
         <f t="shared" si="1"/>
@@ -3244,8 +3300,12 @@
       <c r="I17" s="9">
         <v>50</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
+      <c r="J17" s="9">
+        <v>1</v>
+      </c>
+      <c r="K17" s="17">
+        <v>0</v>
+      </c>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
@@ -3254,7 +3314,7 @@
       <c r="Q17" s="9"/>
       <c r="R17" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S17" s="3">
         <f t="shared" si="1"/>
@@ -3289,8 +3349,12 @@
       <c r="I18" s="9">
         <v>50</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="J18" s="9">
+        <v>1</v>
+      </c>
+      <c r="K18" s="17">
+        <v>0</v>
+      </c>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
@@ -3299,7 +3363,7 @@
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
@@ -3334,8 +3398,12 @@
       <c r="I19" s="9">
         <v>50</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="J19" s="9">
+        <v>1</v>
+      </c>
+      <c r="K19" s="17">
+        <v>0</v>
+      </c>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
@@ -3344,7 +3412,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
@@ -3379,8 +3447,12 @@
       <c r="I20" s="9">
         <v>50</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
+      <c r="J20" s="9">
+        <v>1</v>
+      </c>
+      <c r="K20" s="17">
+        <v>0</v>
+      </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
@@ -3389,7 +3461,7 @@
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="1"/>
@@ -3424,8 +3496,12 @@
       <c r="I21" s="9">
         <v>50</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
+      <c r="J21" s="9">
+        <v>1</v>
+      </c>
+      <c r="K21" s="17">
+        <v>0</v>
+      </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
@@ -3434,7 +3510,7 @@
       <c r="Q21" s="9"/>
       <c r="R21" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S21" s="3">
         <f t="shared" si="1"/>
@@ -3469,8 +3545,12 @@
       <c r="I22" s="9">
         <v>50</v>
       </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
+      <c r="J22" s="9">
+        <v>0</v>
+      </c>
+      <c r="K22" s="17">
+        <v>0</v>
+      </c>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
@@ -3514,8 +3594,12 @@
       <c r="I23" s="9">
         <v>50</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
+      <c r="J23" s="9">
+        <v>1</v>
+      </c>
+      <c r="K23" s="17">
+        <v>0</v>
+      </c>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
@@ -3524,7 +3608,7 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="1"/>
@@ -3559,8 +3643,12 @@
       <c r="I24" s="9">
         <v>50</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="17">
+        <v>0</v>
+      </c>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
@@ -3604,8 +3692,12 @@
       <c r="I25" s="9">
         <v>50</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
+      <c r="J25" s="9">
+        <v>1</v>
+      </c>
+      <c r="K25" s="17">
+        <v>0</v>
+      </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
@@ -3614,7 +3706,7 @@
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="1"/>
@@ -3649,8 +3741,12 @@
       <c r="I26" s="9">
         <v>50</v>
       </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
+      <c r="J26" s="9">
+        <v>1</v>
+      </c>
+      <c r="K26" s="17">
+        <v>0</v>
+      </c>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
@@ -3659,7 +3755,7 @@
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="1"/>
@@ -3694,8 +3790,12 @@
       <c r="I27" s="9">
         <v>0</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="17">
+        <v>0</v>
+      </c>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
@@ -3704,7 +3804,7 @@
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="1"/>
@@ -3739,8 +3839,12 @@
       <c r="I28" s="9">
         <v>0</v>
       </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
+      <c r="J28" s="9">
+        <v>0</v>
+      </c>
+      <c r="K28" s="17">
+        <v>0</v>
+      </c>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
@@ -3784,8 +3888,12 @@
       <c r="I29" s="9">
         <v>0</v>
       </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
+      <c r="J29" s="9">
+        <v>1</v>
+      </c>
+      <c r="K29" s="17">
+        <v>0</v>
+      </c>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
@@ -3794,7 +3902,7 @@
       <c r="Q29" s="9"/>
       <c r="R29" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S29" s="3">
         <f t="shared" si="1"/>
@@ -3829,8 +3937,12 @@
       <c r="I30" s="9">
         <v>0</v>
       </c>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
+      <c r="J30" s="9">
+        <v>1</v>
+      </c>
+      <c r="K30" s="17">
+        <v>0</v>
+      </c>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
@@ -3839,7 +3951,7 @@
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S30" s="3">
         <f t="shared" si="1"/>
@@ -3874,8 +3986,12 @@
       <c r="I31" s="9">
         <v>0</v>
       </c>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
+      <c r="J31" s="9">
+        <v>1</v>
+      </c>
+      <c r="K31" s="17">
+        <v>0</v>
+      </c>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
@@ -3884,7 +4000,7 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="4">
         <f t="shared" si="0"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S31" s="3">
         <f t="shared" si="1"/>
@@ -3919,8 +4035,12 @@
       <c r="I32" s="9">
         <v>0</v>
       </c>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
+      <c r="J32" s="9">
+        <v>1</v>
+      </c>
+      <c r="K32" s="17">
+        <v>0</v>
+      </c>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
@@ -3929,7 +4049,7 @@
       <c r="Q32" s="9"/>
       <c r="R32" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S32" s="3">
         <f t="shared" si="1"/>
@@ -3964,8 +4084,12 @@
       <c r="I33" s="9">
         <v>0</v>
       </c>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
+      <c r="J33" s="9">
+        <v>0</v>
+      </c>
+      <c r="K33" s="17">
+        <v>0</v>
+      </c>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
@@ -4009,8 +4133,12 @@
       <c r="I34" s="9">
         <v>0</v>
       </c>
-      <c r="J34" s="9"/>
-      <c r="K34" s="9"/>
+      <c r="J34" s="9">
+        <v>1</v>
+      </c>
+      <c r="K34" s="17">
+        <v>0</v>
+      </c>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
@@ -4019,7 +4147,7 @@
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S34" s="3">
         <f t="shared" si="1"/>
@@ -4054,8 +4182,12 @@
       <c r="I35" s="9">
         <v>0</v>
       </c>
-      <c r="J35" s="9"/>
-      <c r="K35" s="9"/>
+      <c r="J35" s="9">
+        <v>1</v>
+      </c>
+      <c r="K35" s="17">
+        <v>0</v>
+      </c>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
@@ -4064,7 +4196,7 @@
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
         <f t="shared" ref="R35:R63" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S35" s="3">
         <f t="shared" ref="S35:S63" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
@@ -4099,8 +4231,12 @@
       <c r="I36" s="9">
         <v>0</v>
       </c>
-      <c r="J36" s="9"/>
-      <c r="K36" s="9"/>
+      <c r="J36" s="9">
+        <v>1</v>
+      </c>
+      <c r="K36" s="17">
+        <v>0</v>
+      </c>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
@@ -4109,7 +4245,7 @@
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S36" s="3">
         <f t="shared" si="3"/>
@@ -4144,8 +4280,12 @@
       <c r="I37" s="9">
         <v>0</v>
       </c>
-      <c r="J37" s="9"/>
-      <c r="K37" s="9"/>
+      <c r="J37" s="9">
+        <v>0</v>
+      </c>
+      <c r="K37" s="17">
+        <v>0</v>
+      </c>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
@@ -4189,8 +4329,12 @@
       <c r="I38" s="9">
         <v>0</v>
       </c>
-      <c r="J38" s="9"/>
-      <c r="K38" s="9"/>
+      <c r="J38" s="9">
+        <v>1</v>
+      </c>
+      <c r="K38" s="17">
+        <v>0</v>
+      </c>
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
@@ -4199,7 +4343,7 @@
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S38" s="3">
         <f t="shared" si="3"/>
@@ -4234,8 +4378,12 @@
       <c r="I39" s="9">
         <v>0</v>
       </c>
-      <c r="J39" s="9"/>
-      <c r="K39" s="9"/>
+      <c r="J39" s="9">
+        <v>1</v>
+      </c>
+      <c r="K39" s="17">
+        <v>0</v>
+      </c>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
       <c r="N39" s="9"/>
@@ -4244,7 +4392,7 @@
       <c r="Q39" s="9"/>
       <c r="R39" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S39" s="3">
         <f t="shared" si="3"/>
@@ -4279,8 +4427,12 @@
       <c r="I40" s="9">
         <v>0</v>
       </c>
-      <c r="J40" s="9"/>
-      <c r="K40" s="9"/>
+      <c r="J40" s="9">
+        <v>1</v>
+      </c>
+      <c r="K40" s="17">
+        <v>0</v>
+      </c>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
@@ -4289,7 +4441,7 @@
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S40" s="3">
         <f t="shared" si="3"/>
@@ -4324,8 +4476,12 @@
       <c r="I41" s="9">
         <v>0</v>
       </c>
-      <c r="J41" s="9"/>
-      <c r="K41" s="9"/>
+      <c r="J41" s="9">
+        <v>0</v>
+      </c>
+      <c r="K41" s="17">
+        <v>0</v>
+      </c>
       <c r="L41" s="9"/>
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
@@ -4369,8 +4525,12 @@
       <c r="I42" s="9">
         <v>0</v>
       </c>
-      <c r="J42" s="9"/>
-      <c r="K42" s="9"/>
+      <c r="J42" s="9">
+        <v>1</v>
+      </c>
+      <c r="K42" s="17">
+        <v>0</v>
+      </c>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
@@ -4379,7 +4539,7 @@
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
         <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S42" s="3">
         <f t="shared" si="3"/>
@@ -4414,8 +4574,12 @@
       <c r="I43" s="17">
         <v>-5</v>
       </c>
-      <c r="J43" s="17"/>
-      <c r="K43" s="17"/>
+      <c r="J43" s="17">
+        <v>0</v>
+      </c>
+      <c r="K43" s="17">
+        <v>0</v>
+      </c>
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="17"/>
@@ -4459,8 +4623,12 @@
       <c r="I44" s="17">
         <v>-5</v>
       </c>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
+      <c r="J44" s="17">
+        <v>0</v>
+      </c>
+      <c r="K44" s="17">
+        <v>0</v>
+      </c>
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
@@ -4504,8 +4672,12 @@
       <c r="I45" s="17">
         <v>-5</v>
       </c>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
+      <c r="J45" s="17">
+        <v>0</v>
+      </c>
+      <c r="K45" s="17">
+        <v>0</v>
+      </c>
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
@@ -4549,6 +4721,12 @@
       <c r="I46" s="17">
         <v>-5</v>
       </c>
+      <c r="J46" s="18">
+        <v>0</v>
+      </c>
+      <c r="K46" s="17">
+        <v>0</v>
+      </c>
       <c r="R46" s="4">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
@@ -4586,8 +4764,12 @@
       <c r="I47" s="13">
         <v>100</v>
       </c>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
+      <c r="J47" s="13">
+        <v>0</v>
+      </c>
+      <c r="K47" s="17">
+        <v>0</v>
+      </c>
       <c r="L47" s="13"/>
       <c r="M47" s="13"/>
       <c r="N47" s="13"/>
@@ -4631,8 +4813,12 @@
       <c r="I48" s="13">
         <v>100</v>
       </c>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
+      <c r="J48" s="13">
+        <v>1</v>
+      </c>
+      <c r="K48" s="17">
+        <v>0</v>
+      </c>
       <c r="L48" s="13"/>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
@@ -4641,7 +4827,7 @@
       <c r="Q48" s="13"/>
       <c r="R48" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S48" s="12">
         <f t="shared" si="3"/>
@@ -4676,8 +4862,12 @@
       <c r="I49" s="13">
         <v>100</v>
       </c>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
+      <c r="J49" s="13">
+        <v>1</v>
+      </c>
+      <c r="K49" s="17">
+        <v>0</v>
+      </c>
       <c r="L49" s="13"/>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
@@ -4686,7 +4876,7 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S49" s="12">
         <f t="shared" si="3"/>
@@ -4721,8 +4911,12 @@
       <c r="I50" s="13">
         <v>100</v>
       </c>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
+      <c r="J50" s="13">
+        <v>1</v>
+      </c>
+      <c r="K50" s="17">
+        <v>0</v>
+      </c>
       <c r="L50" s="13"/>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
@@ -4731,7 +4925,7 @@
       <c r="Q50" s="13"/>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S50" s="12">
         <f t="shared" si="3"/>
@@ -4766,8 +4960,12 @@
       <c r="I51" s="13">
         <v>100</v>
       </c>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
+      <c r="J51" s="13">
+        <v>0</v>
+      </c>
+      <c r="K51" s="17">
+        <v>0</v>
+      </c>
       <c r="L51" s="13"/>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
@@ -4811,8 +5009,12 @@
       <c r="I52" s="13">
         <v>100</v>
       </c>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
+      <c r="J52" s="13">
+        <v>1</v>
+      </c>
+      <c r="K52" s="17">
+        <v>0</v>
+      </c>
       <c r="L52" s="13"/>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
@@ -4821,7 +5023,7 @@
       <c r="Q52" s="13"/>
       <c r="R52" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S52" s="14">
         <f t="shared" si="3"/>
@@ -4856,8 +5058,12 @@
       <c r="I53" s="13">
         <v>100</v>
       </c>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
+      <c r="J53" s="13">
+        <v>1</v>
+      </c>
+      <c r="K53" s="17">
+        <v>0</v>
+      </c>
       <c r="L53" s="13"/>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
@@ -4866,7 +5072,7 @@
       <c r="Q53" s="13"/>
       <c r="R53" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S53" s="14">
         <f t="shared" si="3"/>
@@ -4901,8 +5107,12 @@
       <c r="I54" s="13">
         <v>0</v>
       </c>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
+      <c r="J54" s="13">
+        <v>1</v>
+      </c>
+      <c r="K54" s="17">
+        <v>0</v>
+      </c>
       <c r="L54" s="13"/>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
@@ -4911,7 +5121,7 @@
       <c r="Q54" s="13"/>
       <c r="R54" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S54" s="14">
         <f t="shared" si="3"/>
@@ -4946,8 +5156,12 @@
       <c r="I55" s="13">
         <v>0</v>
       </c>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
+      <c r="J55" s="13">
+        <v>0</v>
+      </c>
+      <c r="K55" s="17">
+        <v>0</v>
+      </c>
       <c r="L55" s="13"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
@@ -4991,8 +5205,12 @@
       <c r="I56" s="13">
         <v>0</v>
       </c>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
+      <c r="J56" s="13">
+        <v>1</v>
+      </c>
+      <c r="K56" s="17">
+        <v>0</v>
+      </c>
       <c r="L56" s="13"/>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
@@ -5001,7 +5219,7 @@
       <c r="Q56" s="13"/>
       <c r="R56" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S56" s="14">
         <f t="shared" si="3"/>
@@ -5036,8 +5254,12 @@
       <c r="I57" s="13">
         <v>0</v>
       </c>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
+      <c r="J57" s="13">
+        <v>1</v>
+      </c>
+      <c r="K57" s="17">
+        <v>0</v>
+      </c>
       <c r="L57" s="13"/>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
@@ -5046,7 +5268,7 @@
       <c r="Q57" s="13"/>
       <c r="R57" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S57" s="14">
         <f t="shared" si="3"/>
@@ -5081,8 +5303,12 @@
       <c r="I58" s="13">
         <v>0</v>
       </c>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
+      <c r="J58" s="13">
+        <v>1</v>
+      </c>
+      <c r="K58" s="17">
+        <v>0</v>
+      </c>
       <c r="L58" s="13"/>
       <c r="M58" s="13"/>
       <c r="N58" s="13"/>
@@ -5091,7 +5317,7 @@
       <c r="Q58" s="13"/>
       <c r="R58" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S58" s="14">
         <f t="shared" si="3"/>
@@ -5126,8 +5352,12 @@
       <c r="I59" s="13">
         <v>0</v>
       </c>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
+      <c r="J59" s="13">
+        <v>1</v>
+      </c>
+      <c r="K59" s="17">
+        <v>0</v>
+      </c>
       <c r="L59" s="13"/>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
@@ -5136,7 +5366,7 @@
       <c r="Q59" s="13"/>
       <c r="R59" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S59" s="14">
         <f t="shared" si="3"/>
@@ -5171,8 +5401,12 @@
       <c r="I60" s="13">
         <v>0</v>
       </c>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
+      <c r="J60" s="13">
+        <v>1</v>
+      </c>
+      <c r="K60" s="17">
+        <v>0</v>
+      </c>
       <c r="L60" s="13"/>
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
@@ -5181,7 +5415,7 @@
       <c r="Q60" s="13"/>
       <c r="R60" s="16">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S60" s="14">
         <f t="shared" si="3"/>
@@ -5216,8 +5450,12 @@
       <c r="I61" s="13">
         <v>0</v>
       </c>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
+      <c r="J61" s="13">
+        <v>1</v>
+      </c>
+      <c r="K61" s="17">
+        <v>0</v>
+      </c>
       <c r="L61" s="13"/>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
@@ -5226,7 +5464,7 @@
       <c r="Q61" s="13"/>
       <c r="R61" s="16">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S61" s="14">
         <f t="shared" si="3"/>
@@ -5261,8 +5499,12 @@
       <c r="I62" s="13">
         <v>0</v>
       </c>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
+      <c r="J62" s="13">
+        <v>1</v>
+      </c>
+      <c r="K62" s="17">
+        <v>0</v>
+      </c>
       <c r="L62" s="13"/>
       <c r="M62" s="13"/>
       <c r="N62" s="13"/>
@@ -5271,7 +5513,7 @@
       <c r="Q62" s="13"/>
       <c r="R62" s="16">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S62" s="14">
         <f t="shared" si="3"/>
@@ -5306,8 +5548,12 @@
       <c r="I63" s="13">
         <v>0</v>
       </c>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
+      <c r="J63" s="13">
+        <v>1</v>
+      </c>
+      <c r="K63" s="17">
+        <v>0</v>
+      </c>
       <c r="L63" s="13"/>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
@@ -5316,7 +5562,7 @@
       <c r="Q63" s="13"/>
       <c r="R63" s="16">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S63" s="14">
         <f t="shared" si="3"/>
@@ -5371,10 +5617,10 @@
         <v>123</v>
       </c>
       <c r="B4" s="26">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="C4" s="7">
-        <v>0.4081632653061224</v>
+        <v>0.51020408163265307</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5385,7 +5631,7 @@
         <v>50</v>
       </c>
       <c r="C5" s="7">
-        <v>0.36734693877551017</v>
+        <v>0.44897959183673464</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5396,7 +5642,7 @@
         <v>215</v>
       </c>
       <c r="C6" s="7">
-        <v>0.39999999999999991</v>
+        <v>0.51428571428571423</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -5407,7 +5653,7 @@
         <v>150</v>
       </c>
       <c r="C7" s="7">
-        <v>0.30952380952380948</v>
+        <v>0.42857142857142855</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -5418,7 +5664,7 @@
         <v>50</v>
       </c>
       <c r="C8" s="7">
-        <v>0.32857142857142851</v>
+        <v>0.42857142857142849</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -5440,7 +5686,7 @@
         <v>150</v>
       </c>
       <c r="C10" s="7">
-        <v>0.42857142857142849</v>
+        <v>0.53061224489795911</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -5451,7 +5697,7 @@
         <v>65</v>
       </c>
       <c r="C11" s="7">
-        <v>0.39999999999999991</v>
+        <v>0.52857142857142847</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -5459,10 +5705,10 @@
         <v>117</v>
       </c>
       <c r="B12" s="26">
-        <v>105.65573770491804</v>
+        <v>111.39344262295081</v>
       </c>
       <c r="C12" s="7">
-        <v>0.37002341920374682</v>
+        <v>0.47072599531615938</v>
       </c>
     </row>
   </sheetData>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F721E69-697A-2941-A3D6-FEE65819BE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C90DF4-AF1B-5E4E-832C-172F264BEC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="153">
   <si>
     <t>Anagrafica</t>
   </si>
@@ -493,6 +493,12 @@
   </si>
   <si>
     <t>Marcello</t>
+  </si>
+  <si>
+    <t>Castiglia</t>
+  </si>
+  <si>
+    <t>Vincenza</t>
   </si>
 </sst>
 </file>
@@ -628,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -699,6 +705,21 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -719,7 +740,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46131.405947916668" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46133.448483217595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -767,7 +788,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="50"/>
     </cacheField>
     <cacheField name="L5 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L5 XP" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -785,7 +806,7 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.14285714285714285" maxValue="0.5714285714285714"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="0.7142857142857143"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45" maxValue="215"/>
@@ -813,13 +834,13 @@
     <n v="30"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="145"/>
   </r>
   <r>
@@ -834,13 +855,13 @@
     <n v="30"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="145"/>
   </r>
   <r>
@@ -855,13 +876,13 @@
     <n v="30"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="145"/>
   </r>
   <r>
@@ -876,13 +897,13 @@
     <n v="30"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="145"/>
   </r>
   <r>
@@ -897,13 +918,13 @@
     <n v="30"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="145"/>
   </r>
   <r>
@@ -918,13 +939,13 @@
     <n v="30"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="145"/>
   </r>
   <r>
@@ -939,13 +960,34 @@
     <n v="30"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
+    <n v="145"/>
+  </r>
+  <r>
+    <s v="Castiglia"/>
+    <s v="Vincenza"/>
+    <x v="0"/>
+    <n v="0"/>
+    <n v="50"/>
+    <n v="0"/>
+    <n v="15"/>
+    <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
+    <n v="50"/>
+    <n v="0"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <n v="145"/>
   </r>
   <r>
@@ -960,7 +1002,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -981,7 +1023,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1002,13 +1044,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1023,7 +1065,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1044,7 +1086,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1065,7 +1107,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1086,13 +1128,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="50"/>
   </r>
   <r>
@@ -1107,13 +1149,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="215"/>
   </r>
   <r>
@@ -1128,7 +1170,7 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1149,13 +1191,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="215"/>
   </r>
   <r>
@@ -1170,13 +1212,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="215"/>
   </r>
   <r>
@@ -1191,13 +1233,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1212,13 +1254,13 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="215"/>
   </r>
   <r>
@@ -1233,13 +1275,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="215"/>
   </r>
   <r>
@@ -1254,13 +1296,13 @@
     <n v="50"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="215"/>
   </r>
   <r>
@@ -1275,7 +1317,7 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1296,13 +1338,13 @@
     <n v="50"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="215"/>
   </r>
   <r>
@@ -1317,13 +1359,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1338,13 +1380,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1359,13 +1401,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1380,13 +1422,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1401,13 +1443,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="150"/>
   </r>
   <r>
@@ -1422,13 +1464,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1443,13 +1485,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1464,13 +1506,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="50"/>
   </r>
   <r>
@@ -1485,13 +1527,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="50"/>
   </r>
   <r>
@@ -1506,13 +1548,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="50"/>
   </r>
   <r>
@@ -1527,13 +1569,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1548,13 +1590,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="50"/>
   </r>
   <r>
@@ -1569,7 +1611,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1590,13 +1632,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="50"/>
   </r>
   <r>
@@ -1611,13 +1653,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="50"/>
   </r>
   <r>
@@ -1632,7 +1674,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1653,13 +1695,13 @@
     <n v="-5"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="45"/>
   </r>
   <r>
@@ -1674,13 +1716,13 @@
     <n v="-5"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="45"/>
   </r>
   <r>
@@ -1695,13 +1737,13 @@
     <n v="-5"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.14285714285714285"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.2857142857142857"/>
     <n v="45"/>
   </r>
   <r>
@@ -1716,13 +1758,13 @@
     <n v="-5"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="45"/>
   </r>
   <r>
@@ -1737,13 +1779,13 @@
     <n v="100"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="150"/>
   </r>
   <r>
@@ -1758,13 +1800,13 @@
     <n v="100"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1779,13 +1821,13 @@
     <n v="100"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1800,13 +1842,13 @@
     <n v="100"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1821,7 +1863,7 @@
     <n v="100"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1842,13 +1884,13 @@
     <n v="100"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1863,13 +1905,13 @@
     <n v="100"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="150"/>
   </r>
   <r>
@@ -1884,13 +1926,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
   <r>
@@ -1905,7 +1947,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1926,7 +1968,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1947,13 +1989,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
   <r>
@@ -1968,13 +2010,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
   <r>
@@ -1989,7 +2031,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -2010,13 +2052,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
   <r>
@@ -2031,13 +2073,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
   <r>
@@ -2052,34 +2094,13 @@
     <n v="0"/>
     <n v="1"/>
     <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="65"/>
-  </r>
-  <r>
-    <s v="Vitale"/>
-    <s v="Marco"/>
-    <x v="7"/>
-    <n v="1"/>
-    <n v="50"/>
-    <n v="1"/>
-    <n v="15"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="0"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="65"/>
   </r>
 </pivotCacheRecords>
@@ -2465,15 +2486,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S63"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="4" max="4" width="11" style="18" customWidth="1"/>
+    <col min="5" max="5" width="8" style="18" customWidth="1"/>
+    <col min="6" max="6" width="11" style="18" customWidth="1"/>
     <col min="7" max="7" width="8" style="18" customWidth="1"/>
     <col min="8" max="8" width="11" style="18" customWidth="1"/>
     <col min="9" max="9" width="8" style="18" customWidth="1"/>
@@ -2497,11 +2518,11 @@
       <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="23"/>
+      <c r="E1" s="21"/>
       <c r="F1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="23"/>
+      <c r="G1" s="21"/>
       <c r="H1" s="20" t="s">
         <v>3</v>
       </c>
@@ -2620,18 +2641,20 @@
       <c r="K3" s="17">
         <v>50</v>
       </c>
-      <c r="L3" s="17"/>
+      <c r="L3" s="17">
+        <v>1</v>
+      </c>
       <c r="M3" s="17"/>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="4">
-        <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.5714285714285714</v>
+        <f>(D3+F3+H3+J3+L3+N3+P3)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S3" s="3">
-        <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
+        <f>E3+G3+I3+K3+M3+O3+Q3</f>
         <v>145</v>
       </c>
     </row>
@@ -2669,18 +2692,20 @@
       <c r="K4" s="17">
         <v>50</v>
       </c>
-      <c r="L4" s="17"/>
+      <c r="L4" s="17">
+        <v>1</v>
+      </c>
       <c r="M4" s="17"/>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D4+F4+H4+J4+L4+N4+P4)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S4" s="3">
-        <f t="shared" si="1"/>
+        <f>E4+G4+I4+K4+M4+O4+Q4</f>
         <v>145</v>
       </c>
     </row>
@@ -2718,18 +2743,20 @@
       <c r="K5" s="17">
         <v>50</v>
       </c>
-      <c r="L5" s="17"/>
+      <c r="L5" s="17">
+        <v>1</v>
+      </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D5+F5+H5+J5+L5+N5+P5)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" si="1"/>
+        <f>E5+G5+I5+K5+M5+O5+Q5</f>
         <v>145</v>
       </c>
     </row>
@@ -2767,18 +2794,20 @@
       <c r="K6" s="17">
         <v>50</v>
       </c>
-      <c r="L6" s="17"/>
+      <c r="L6" s="17">
+        <v>1</v>
+      </c>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D6+F6+H6+J6+L6+N6+P6)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" si="1"/>
+        <f>E6+G6+I6+K6+M6+O6+Q6</f>
         <v>145</v>
       </c>
     </row>
@@ -2816,18 +2845,20 @@
       <c r="K7" s="17">
         <v>50</v>
       </c>
-      <c r="L7" s="17"/>
+      <c r="L7" s="17">
+        <v>1</v>
+      </c>
       <c r="M7" s="17"/>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D7+F7+H7+J7+L7+N7+P7)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" si="1"/>
+        <f>E7+G7+I7+K7+M7+O7+Q7</f>
         <v>145</v>
       </c>
     </row>
@@ -2865,18 +2896,20 @@
       <c r="K8" s="17">
         <v>50</v>
       </c>
-      <c r="L8" s="17"/>
+      <c r="L8" s="17">
+        <v>1</v>
+      </c>
       <c r="M8" s="17"/>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D8+F8+H8+J8+L8+N8+P8)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" si="1"/>
+        <f>E8+G8+I8+K8+M8+O8+Q8</f>
         <v>145</v>
       </c>
     </row>
@@ -2914,76 +2947,80 @@
       <c r="K9" s="17">
         <v>50</v>
       </c>
-      <c r="L9" s="17"/>
+      <c r="L9" s="17">
+        <v>1</v>
+      </c>
       <c r="M9" s="17"/>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D9+F9+H9+J9+L9+N9+P9)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" si="1"/>
+        <f>E9+G9+I9+K9+M9+O9+Q9</f>
         <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9">
-        <v>50</v>
-      </c>
-      <c r="F10" s="15">
-        <v>1</v>
+      <c r="A10" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" s="27">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
+        <v>50</v>
+      </c>
+      <c r="F10" s="27">
+        <v>0</v>
       </c>
       <c r="G10" s="17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H10" s="17">
         <v>1</v>
       </c>
       <c r="I10" s="17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J10" s="17">
         <v>1</v>
       </c>
       <c r="K10" s="17">
-        <v>0</v>
-      </c>
-      <c r="L10" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D10+F10+H10+J10+L10+N10+P10)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f>E10+G10+I10+K10+M10+O10+Q10</f>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>135</v>
@@ -3007,32 +3044,34 @@
         <v>0</v>
       </c>
       <c r="J11" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" s="17">
         <v>0</v>
       </c>
-      <c r="L11" s="17"/>
+      <c r="L11" s="17">
+        <v>0</v>
+      </c>
       <c r="M11" s="17"/>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D11+F11+H11+J11+L11+N11+P11)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S11" s="3">
-        <f t="shared" si="1"/>
+        <f>E11+G11+I11+K11+M11+O11+Q11</f>
         <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>142</v>
+        <v>46</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>135</v>
@@ -3044,7 +3083,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="17">
         <v>0</v>
@@ -3056,32 +3095,34 @@
         <v>0</v>
       </c>
       <c r="J12" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="17">
         <v>0</v>
       </c>
-      <c r="L12" s="17"/>
+      <c r="L12" s="17">
+        <v>0</v>
+      </c>
       <c r="M12" s="17"/>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="4">
-        <f t="shared" si="0"/>
+        <f>(D12+F12+H12+J12+L12+N12+P12)/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" si="1"/>
+        <f>E12+G12+I12+K12+M12+O12+Q12</f>
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>135</v>
@@ -3105,32 +3146,34 @@
         <v>0</v>
       </c>
       <c r="J13" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" s="17">
         <v>0</v>
       </c>
-      <c r="L13" s="17"/>
+      <c r="L13" s="17">
+        <v>1</v>
+      </c>
       <c r="M13" s="17"/>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D13+F13+H13+J13+L13+N13+P13)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" si="1"/>
+        <f>E13+G13+I13+K13+M13+O13+Q13</f>
         <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="C14" s="8" t="s">
         <v>135</v>
@@ -3142,7 +3185,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="17">
         <v>0</v>
@@ -3154,32 +3197,34 @@
         <v>0</v>
       </c>
       <c r="J14" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="17">
         <v>0</v>
       </c>
-      <c r="L14" s="17"/>
+      <c r="L14" s="17">
+        <v>0</v>
+      </c>
       <c r="M14" s="17"/>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D14+F14+H14+J14+L14+N14+P14)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S14" s="3">
-        <f t="shared" si="1"/>
+        <f>E14+G14+I14+K14+M14+O14+Q14</f>
         <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>135</v>
@@ -3197,38 +3242,40 @@
         <v>0</v>
       </c>
       <c r="H15" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="17">
         <v>0</v>
       </c>
       <c r="J15" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" s="17">
         <v>0</v>
       </c>
-      <c r="L15" s="17"/>
+      <c r="L15" s="17">
+        <v>0</v>
+      </c>
       <c r="M15" s="17"/>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D15+F15+H15+J15+L15+N15+P15)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" si="1"/>
+        <f>E15+G15+I15+K15+M15+O15+Q15</f>
         <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>135</v>
@@ -3246,41 +3293,43 @@
         <v>0</v>
       </c>
       <c r="H16" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" s="17">
         <v>0</v>
       </c>
       <c r="J16" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="17">
         <v>0</v>
       </c>
-      <c r="L16" s="17"/>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
       <c r="M16" s="17"/>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D16+F16+H16+J16+L16+N16+P16)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" si="1"/>
+        <f>E16+G16+I16+K16+M16+O16+Q16</f>
         <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>31</v>
+        <v>135</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -3288,45 +3337,47 @@
       <c r="E17" s="9">
         <v>50</v>
       </c>
-      <c r="F17" s="9">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9">
-        <v>115</v>
-      </c>
-      <c r="H17" s="9">
-        <v>1</v>
-      </c>
-      <c r="I17" s="9">
-        <v>50</v>
-      </c>
-      <c r="J17" s="9">
+      <c r="F17" s="15">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17">
+        <v>0</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1</v>
+      </c>
+      <c r="I17" s="17">
+        <v>0</v>
+      </c>
+      <c r="J17" s="17">
         <v>1</v>
       </c>
       <c r="K17" s="17">
         <v>0</v>
       </c>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
       <c r="R17" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D17+F17+H17+J17+L17+N17+P17)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S17" s="3">
-        <f t="shared" si="1"/>
-        <v>215</v>
+        <f>E17+G17+I17+K17+M17+O17+Q17</f>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>31</v>
@@ -3355,27 +3406,29 @@
       <c r="K18" s="17">
         <v>0</v>
       </c>
-      <c r="L18" s="9"/>
+      <c r="L18" s="9">
+        <v>1</v>
+      </c>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D18+F18+H18+J18+L18+N18+P18)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S18" s="3">
-        <f t="shared" si="1"/>
+        <f>E18+G18+I18+K18+M18+O18+Q18</f>
         <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>31</v>
@@ -3404,27 +3457,29 @@
       <c r="K19" s="17">
         <v>0</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
-        <f t="shared" si="0"/>
+        <f>(D19+F19+H19+J19+L19+N19+P19)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" si="1"/>
+        <f>E19+G19+I19+K19+M19+O19+Q19</f>
         <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>31</v>
@@ -3453,27 +3508,29 @@
       <c r="K20" s="17">
         <v>0</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="9">
+        <v>1</v>
+      </c>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D20+F20+H20+J20+L20+N20+P20)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" si="1"/>
+        <f>E20+G20+I20+K20+M20+O20+Q20</f>
         <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>31</v>
@@ -3491,7 +3548,7 @@
         <v>115</v>
       </c>
       <c r="H21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="9">
         <v>50</v>
@@ -3502,27 +3559,29 @@
       <c r="K21" s="17">
         <v>0</v>
       </c>
-      <c r="L21" s="9"/>
+      <c r="L21" s="9">
+        <v>1</v>
+      </c>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D21+F21+H21+J21+L21+N21+P21)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" si="1"/>
+        <f>E21+G21+I21+K21+M21+O21+Q21</f>
         <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="C22" s="8" t="s">
         <v>31</v>
@@ -3534,44 +3593,46 @@
         <v>50</v>
       </c>
       <c r="F22" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="9">
         <v>115</v>
       </c>
       <c r="H22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9">
         <v>50</v>
       </c>
       <c r="J22" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="17">
         <v>0</v>
       </c>
-      <c r="L22" s="9"/>
+      <c r="L22" s="9">
+        <v>1</v>
+      </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D22+F22+H22+J22+L22+N22+P22)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" si="1"/>
+        <f>E22+G22+I22+K22+M22+O22+Q22</f>
         <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" s="8" t="s">
         <v>31</v>
@@ -3583,7 +3644,7 @@
         <v>50</v>
       </c>
       <c r="F23" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="9">
         <v>115</v>
@@ -3595,32 +3656,34 @@
         <v>50</v>
       </c>
       <c r="J23" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="17">
         <v>0</v>
       </c>
-      <c r="L23" s="9"/>
+      <c r="L23" s="9">
+        <v>1</v>
+      </c>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D23+F23+H23+J23+L23+N23+P23)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" si="1"/>
+        <f>E23+G23+I23+K23+M23+O23+Q23</f>
         <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="8" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>31</v>
@@ -3644,32 +3707,34 @@
         <v>50</v>
       </c>
       <c r="J24" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="17">
         <v>0</v>
       </c>
-      <c r="L24" s="9"/>
+      <c r="L24" s="9">
+        <v>1</v>
+      </c>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D24+F24+H24+J24+L24+N24+P24)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" si="1"/>
+        <f>E24+G24+I24+K24+M24+O24+Q24</f>
         <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>31</v>
@@ -3693,32 +3758,34 @@
         <v>50</v>
       </c>
       <c r="J25" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="17">
         <v>0</v>
       </c>
-      <c r="L25" s="9"/>
+      <c r="L25" s="9">
+        <v>1</v>
+      </c>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
-        <f t="shared" si="0"/>
+        <f>(D25+F25+H25+J25+L25+N25+P25)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S25" s="3">
-        <f t="shared" si="1"/>
+        <f>E25+G25+I25+K25+M25+O25+Q25</f>
         <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C26" s="8" t="s">
         <v>31</v>
@@ -3747,48 +3814,50 @@
       <c r="K26" s="17">
         <v>0</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="9">
+        <v>0</v>
+      </c>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
-        <f t="shared" si="0"/>
+        <f>(D26+F26+H26+J26+L26+N26+P26)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" si="1"/>
+        <f>E26+G26+I26+K26+M26+O26+Q26</f>
         <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D27" s="9">
         <v>1</v>
       </c>
       <c r="E27" s="9">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="F27" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="9">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H27" s="9">
         <v>1</v>
       </c>
       <c r="I27" s="9">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J27" s="9">
         <v>1</v>
@@ -3796,27 +3865,29 @@
       <c r="K27" s="17">
         <v>0</v>
       </c>
-      <c r="L27" s="9"/>
+      <c r="L27" s="9">
+        <v>1</v>
+      </c>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D27+F27+H27+J27+L27+N27+P27)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" si="1"/>
-        <v>150</v>
+        <f>E27+G27+I27+K27+M27+O27+Q27</f>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>66</v>
@@ -3828,7 +3899,7 @@
         <v>150</v>
       </c>
       <c r="F28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="9">
         <v>0</v>
@@ -3840,32 +3911,34 @@
         <v>0</v>
       </c>
       <c r="J28" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" s="17">
         <v>0</v>
       </c>
-      <c r="L28" s="9"/>
+      <c r="L28" s="9">
+        <v>1</v>
+      </c>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D28+F28+H28+J28+L28+N28+P28)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" si="1"/>
+        <f>E28+G28+I28+K28+M28+O28+Q28</f>
         <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>66</v>
@@ -3877,7 +3950,7 @@
         <v>150</v>
       </c>
       <c r="F29" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="9">
         <v>0</v>
@@ -3889,32 +3962,34 @@
         <v>0</v>
       </c>
       <c r="J29" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" s="17">
         <v>0</v>
       </c>
-      <c r="L29" s="9"/>
+      <c r="L29" s="9">
+        <v>1</v>
+      </c>
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="4">
-        <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <f>(D29+F29+H29+J29+L29+N29+P29)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S29" s="3">
-        <f t="shared" si="1"/>
+        <f>E29+G29+I29+K29+M29+O29+Q29</f>
         <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>66</v>
@@ -3926,7 +4001,7 @@
         <v>150</v>
       </c>
       <c r="F30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="9">
         <v>0</v>
@@ -3943,27 +4018,29 @@
       <c r="K30" s="17">
         <v>0</v>
       </c>
-      <c r="L30" s="9"/>
+      <c r="L30" s="9">
+        <v>1</v>
+      </c>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
-        <f t="shared" si="0"/>
+        <f>(D30+F30+H30+J30+L30+N30+P30)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S30" s="3">
-        <f t="shared" si="1"/>
+        <f>E30+G30+I30+K30+M30+O30+Q30</f>
         <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>66</v>
@@ -3975,13 +4052,13 @@
         <v>150</v>
       </c>
       <c r="F31" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="9">
         <v>0</v>
       </c>
       <c r="H31" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="9">
         <v>0</v>
@@ -3992,27 +4069,29 @@
       <c r="K31" s="17">
         <v>0</v>
       </c>
-      <c r="L31" s="9"/>
+      <c r="L31" s="9">
+        <v>1</v>
+      </c>
       <c r="M31" s="9"/>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D31+F31+H31+J31+L31+N31+P31)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S31" s="3">
-        <f t="shared" si="1"/>
+        <f>E31+G31+I31+K31+M31+O31+Q31</f>
         <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>66</v>
@@ -4030,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9">
         <v>0</v>
@@ -4041,76 +4120,80 @@
       <c r="K32" s="17">
         <v>0</v>
       </c>
-      <c r="L32" s="9"/>
+      <c r="L32" s="9">
+        <v>1</v>
+      </c>
       <c r="M32" s="9"/>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="4">
-        <f t="shared" si="0"/>
+        <f>(D32+F32+H32+J32+L32+N32+P32)/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="S32" s="3">
-        <f t="shared" si="1"/>
+        <f>E32+G32+I32+K32+M32+O32+Q32</f>
         <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="D33" s="9">
         <v>1</v>
       </c>
       <c r="E33" s="9">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="F33" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="9">
         <v>0</v>
       </c>
       <c r="H33" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="9">
         <v>0</v>
       </c>
       <c r="J33" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="17">
         <v>0</v>
       </c>
-      <c r="L33" s="9"/>
+      <c r="L33" s="9">
+        <v>1</v>
+      </c>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="4">
-        <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <f>(D33+F33+H33+J33+L33+N33+P33)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f>E33+G33+I33+K33+M33+O33+Q33</f>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>36</v>
@@ -4128,38 +4211,40 @@
         <v>0</v>
       </c>
       <c r="H34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9">
         <v>0</v>
       </c>
       <c r="J34" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" s="17">
         <v>0</v>
       </c>
-      <c r="L34" s="9"/>
+      <c r="L34" s="9">
+        <v>1</v>
+      </c>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
-        <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <f>(D34+F34+H34+J34+L34+N34+P34)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S34" s="3">
-        <f t="shared" si="1"/>
+        <f>E34+G34+I34+K34+M34+O34+Q34</f>
         <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>36</v>
@@ -4188,27 +4273,29 @@
       <c r="K35" s="17">
         <v>0</v>
       </c>
-      <c r="L35" s="9"/>
+      <c r="L35" s="9">
+        <v>1</v>
+      </c>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
-        <f t="shared" ref="R35:R63" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
-        <v>0.5714285714285714</v>
+        <f>(D35+F35+H35+J35+L35+N35+P35)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S35" s="3">
-        <f t="shared" ref="S35:S63" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
+        <f>E35+G35+I35+K35+M35+O35+Q35</f>
         <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>36</v>
@@ -4237,27 +4324,29 @@
       <c r="K36" s="17">
         <v>0</v>
       </c>
-      <c r="L36" s="9"/>
+      <c r="L36" s="9">
+        <v>1</v>
+      </c>
       <c r="M36" s="9"/>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D36+F36+H36+J36+L36+N36+P36)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S36" s="3">
-        <f t="shared" si="3"/>
+        <f>E36+G36+I36+K36+M36+O36+Q36</f>
         <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>36</v>
@@ -4275,38 +4364,40 @@
         <v>0</v>
       </c>
       <c r="H37" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="9">
         <v>0</v>
       </c>
       <c r="J37" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" s="17">
         <v>0</v>
       </c>
-      <c r="L37" s="9"/>
+      <c r="L37" s="9">
+        <v>1</v>
+      </c>
       <c r="M37" s="9"/>
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="4">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <f>(D37+F37+H37+J37+L37+N37+P37)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S37" s="3">
-        <f t="shared" si="3"/>
+        <f>E37+G37+I37+K37+M37+O37+Q37</f>
         <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>36</v>
@@ -4318,44 +4409,46 @@
         <v>50</v>
       </c>
       <c r="F38" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="9">
         <v>0</v>
       </c>
       <c r="H38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9">
         <v>0</v>
       </c>
       <c r="J38" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="17">
         <v>0</v>
       </c>
-      <c r="L38" s="9"/>
+      <c r="L38" s="9">
+        <v>1</v>
+      </c>
       <c r="M38" s="9"/>
       <c r="N38" s="9"/>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
-        <f t="shared" si="2"/>
+        <f>(D38+F38+H38+J38+L38+N38+P38)/7</f>
         <v>0.42857142857142855</v>
       </c>
       <c r="S38" s="3">
-        <f t="shared" si="3"/>
+        <f>E38+G38+I38+K38+M38+O38+Q38</f>
         <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C39" s="8" t="s">
         <v>36</v>
@@ -4367,13 +4460,13 @@
         <v>50</v>
       </c>
       <c r="F39" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="9">
         <v>0</v>
       </c>
       <c r="H39" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="9">
         <v>0</v>
@@ -4384,27 +4477,29 @@
       <c r="K39" s="17">
         <v>0</v>
       </c>
-      <c r="L39" s="9"/>
+      <c r="L39" s="9">
+        <v>1</v>
+      </c>
       <c r="M39" s="9"/>
       <c r="N39" s="9"/>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="4">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <f>(D39+F39+H39+J39+L39+N39+P39)/7</f>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S39" s="3">
-        <f t="shared" si="3"/>
+        <f>E39+G39+I39+K39+M39+O39+Q39</f>
         <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C40" s="8" t="s">
         <v>36</v>
@@ -4422,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9">
         <v>0</v>
@@ -4433,27 +4528,29 @@
       <c r="K40" s="17">
         <v>0</v>
       </c>
-      <c r="L40" s="9"/>
+      <c r="L40" s="9">
+        <v>0</v>
+      </c>
       <c r="M40" s="9"/>
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D40+F40+H40+J40+L40+N40+P40)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S40" s="3">
-        <f t="shared" si="3"/>
+        <f>E40+G40+I40+K40+M40+O40+Q40</f>
         <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="C41" s="8" t="s">
         <v>36</v>
@@ -4471,38 +4568,40 @@
         <v>0</v>
       </c>
       <c r="H41" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="9">
         <v>0</v>
       </c>
       <c r="J41" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="17">
         <v>0</v>
       </c>
-      <c r="L41" s="9"/>
+      <c r="L41" s="9">
+        <v>1</v>
+      </c>
       <c r="M41" s="9"/>
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="4">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <f>(D41+F41+H41+J41+L41+N41+P41)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S41" s="3">
-        <f t="shared" si="3"/>
+        <f>E41+G41+I41+K41+M41+O41+Q41</f>
         <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>36</v>
@@ -4514,7 +4613,7 @@
         <v>50</v>
       </c>
       <c r="F42" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" s="9">
         <v>0</v>
@@ -4526,81 +4625,85 @@
         <v>0</v>
       </c>
       <c r="J42" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="17">
         <v>0</v>
       </c>
-      <c r="L42" s="9"/>
+      <c r="L42" s="9">
+        <v>1</v>
+      </c>
       <c r="M42" s="9"/>
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <f>(D42+F42+H42+J42+L42+N42+P42)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S42" s="3">
-        <f t="shared" si="3"/>
+        <f>E42+G42+I42+K42+M42+O42+Q42</f>
         <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>149</v>
+        <v>36</v>
       </c>
       <c r="D43" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="9">
         <v>50</v>
       </c>
       <c r="F43" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="9">
         <v>0</v>
       </c>
-      <c r="H43" s="17">
-        <v>1</v>
-      </c>
-      <c r="I43" s="17">
-        <v>-5</v>
-      </c>
-      <c r="J43" s="17">
-        <v>0</v>
+      <c r="H43" s="9">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9">
+        <v>0</v>
+      </c>
+      <c r="J43" s="9">
+        <v>1</v>
       </c>
       <c r="K43" s="17">
         <v>0</v>
       </c>
-      <c r="L43" s="17"/>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17"/>
-      <c r="P43" s="17"/>
-      <c r="Q43" s="17"/>
+      <c r="L43" s="9">
+        <v>0</v>
+      </c>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
       <c r="R43" s="4">
-        <f t="shared" si="2"/>
+        <f>(D43+F43+H43+J43+L43+N43+P43)/7</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="S43" s="3">
-        <f t="shared" si="3"/>
-        <v>45</v>
+        <f>E43+G43+I43+K43+M43+O43+Q43</f>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>149</v>
@@ -4629,27 +4732,29 @@
       <c r="K44" s="17">
         <v>0</v>
       </c>
-      <c r="L44" s="17"/>
+      <c r="L44" s="17">
+        <v>1</v>
+      </c>
       <c r="M44" s="17"/>
       <c r="N44" s="17"/>
       <c r="O44" s="17"/>
       <c r="P44" s="17"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="4">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <f>(D44+F44+H44+J44+L44+N44+P44)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S44" s="3">
-        <f t="shared" si="3"/>
+        <f>E44+G44+I44+K44+M44+O44+Q44</f>
         <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>53</v>
+        <v>145</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>149</v>
@@ -4667,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="17">
         <v>-5</v>
@@ -4678,27 +4783,29 @@
       <c r="K45" s="17">
         <v>0</v>
       </c>
-      <c r="L45" s="17"/>
+      <c r="L45" s="17">
+        <v>1</v>
+      </c>
       <c r="M45" s="17"/>
       <c r="N45" s="17"/>
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="4">
-        <f t="shared" si="2"/>
-        <v>0.14285714285714285</v>
+        <f>(D45+F45+H45+J45+L45+N45+P45)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S45" s="3">
-        <f t="shared" si="3"/>
+        <f>E45+G45+I45+K45+M45+O45+Q45</f>
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>149</v>
@@ -4716,81 +4823,86 @@
         <v>0</v>
       </c>
       <c r="H46" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="17">
         <v>-5</v>
       </c>
-      <c r="J46" s="18">
+      <c r="J46" s="29">
         <v>0</v>
       </c>
       <c r="K46" s="17">
         <v>0</v>
       </c>
+      <c r="L46" s="29">
+        <v>1</v>
+      </c>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
       <c r="R46" s="4">
-        <f t="shared" si="2"/>
+        <f>(D46+F46+H46+J46+L46+N46+P46)/7</f>
         <v>0.2857142857142857</v>
       </c>
       <c r="S46" s="12">
-        <f t="shared" si="3"/>
+        <f>E46+G46+I46+K46+M46+O46+Q46</f>
         <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11">
+        <v>50</v>
+      </c>
+      <c r="F47" s="9">
+        <v>1</v>
+      </c>
+      <c r="G47" s="28">
+        <v>0</v>
+      </c>
+      <c r="H47" s="29">
+        <v>1</v>
+      </c>
+      <c r="I47" s="29">
+        <v>-5</v>
+      </c>
+      <c r="J47" s="18">
+        <v>0</v>
+      </c>
+      <c r="K47" s="17">
+        <v>0</v>
+      </c>
+      <c r="L47" s="18">
+        <v>1</v>
+      </c>
+      <c r="R47" s="4">
+        <f>(D47+F47+H47+J47+L47+N47+P47)/7</f>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="S47" s="12">
+        <f>E47+G47+I47+K47+M47+O47+Q47</f>
         <v>45</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="11">
-        <v>1</v>
-      </c>
-      <c r="E47" s="11">
-        <v>50</v>
-      </c>
-      <c r="F47" s="9">
-        <v>1</v>
-      </c>
-      <c r="G47" s="13">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13">
-        <v>1</v>
-      </c>
-      <c r="I47" s="13">
-        <v>100</v>
-      </c>
-      <c r="J47" s="13">
-        <v>0</v>
-      </c>
-      <c r="K47" s="17">
-        <v>0</v>
-      </c>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="4">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S47" s="12">
-        <f t="shared" si="3"/>
-        <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>47</v>
@@ -4814,32 +4926,34 @@
         <v>100</v>
       </c>
       <c r="J48" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" s="17">
         <v>0</v>
       </c>
-      <c r="L48" s="13"/>
+      <c r="L48" s="13">
+        <v>1</v>
+      </c>
       <c r="M48" s="13"/>
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
       <c r="Q48" s="13"/>
       <c r="R48" s="4">
-        <f t="shared" si="2"/>
+        <f>(D48+F48+H48+J48+L48+N48+P48)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S48" s="12">
-        <f t="shared" si="3"/>
+        <f>E48+G48+I48+K48+M48+O48+Q48</f>
         <v>150</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>47</v>
@@ -4868,27 +4982,29 @@
       <c r="K49" s="17">
         <v>0</v>
       </c>
-      <c r="L49" s="13"/>
+      <c r="L49" s="13">
+        <v>1</v>
+      </c>
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
       <c r="R49" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D49+F49+H49+J49+L49+N49+P49)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S49" s="12">
-        <f t="shared" si="3"/>
+        <f>E49+G49+I49+K49+M49+O49+Q49</f>
         <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>47</v>
@@ -4917,27 +5033,29 @@
       <c r="K50" s="17">
         <v>0</v>
       </c>
-      <c r="L50" s="13"/>
+      <c r="L50" s="13">
+        <v>1</v>
+      </c>
       <c r="M50" s="13"/>
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D50+F50+H50+J50+L50+N50+P50)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S50" s="12">
-        <f t="shared" si="3"/>
+        <f>E50+G50+I50+K50+M50+O50+Q50</f>
         <v>150</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" s="10" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>47</v>
@@ -4961,32 +5079,34 @@
         <v>100</v>
       </c>
       <c r="J51" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" s="17">
         <v>0</v>
       </c>
-      <c r="L51" s="13"/>
+      <c r="L51" s="13">
+        <v>1</v>
+      </c>
       <c r="M51" s="13"/>
       <c r="N51" s="13"/>
       <c r="O51" s="13"/>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
       <c r="R51" s="4">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="S51" s="14">
-        <f t="shared" si="3"/>
+        <f>(D51+F51+H51+J51+L51+N51+P51)/7</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="S51" s="30">
+        <f>E51+G51+I51+K51+M51+O51+Q51</f>
         <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" s="10" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>47</v>
@@ -5010,32 +5130,34 @@
         <v>100</v>
       </c>
       <c r="J52" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" s="17">
         <v>0</v>
       </c>
-      <c r="L52" s="13"/>
+      <c r="L52" s="13">
+        <v>0</v>
+      </c>
       <c r="M52" s="13"/>
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
       <c r="R52" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D52+F52+H52+J52+L52+N52+P52)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S52" s="14">
-        <f t="shared" si="3"/>
+        <f>E52+G52+I52+K52+M52+O52+Q52</f>
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C53" s="10" t="s">
         <v>47</v>
@@ -5064,30 +5186,32 @@
       <c r="K53" s="17">
         <v>0</v>
       </c>
-      <c r="L53" s="13"/>
+      <c r="L53" s="13">
+        <v>1</v>
+      </c>
       <c r="M53" s="13"/>
       <c r="N53" s="13"/>
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
       <c r="R53" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D53+F53+H53+J53+L53+N53+P53)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S53" s="14">
-        <f t="shared" si="3"/>
+        <f>E53+G53+I53+K53+M53+O53+Q53</f>
         <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54" s="10" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D54" s="11">
         <v>1</v>
@@ -5099,13 +5223,13 @@
         <v>1</v>
       </c>
       <c r="G54" s="13">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H54" s="13">
         <v>1</v>
       </c>
       <c r="I54" s="13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J54" s="13">
         <v>1</v>
@@ -5113,27 +5237,29 @@
       <c r="K54" s="17">
         <v>0</v>
       </c>
-      <c r="L54" s="13"/>
+      <c r="L54" s="13">
+        <v>1</v>
+      </c>
       <c r="M54" s="13"/>
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
       <c r="R54" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D54+F54+H54+J54+L54+N54+P54)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S54" s="14">
-        <f t="shared" si="3"/>
-        <v>65</v>
+        <f>E54+G54+I54+K54+M54+O54+Q54</f>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55" s="10" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>28</v>
@@ -5151,38 +5277,40 @@
         <v>15</v>
       </c>
       <c r="H55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
       </c>
       <c r="J55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="17">
         <v>0</v>
       </c>
-      <c r="L55" s="13"/>
+      <c r="L55" s="13">
+        <v>1</v>
+      </c>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
       <c r="O55" s="13"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
       <c r="R55" s="4">
-        <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <f>(D55+F55+H55+J55+L55+N55+P55)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S55" s="14">
-        <f t="shared" si="3"/>
+        <f>E55+G55+I55+K55+M55+O55+Q55</f>
         <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>28</v>
@@ -5206,32 +5334,34 @@
         <v>0</v>
       </c>
       <c r="J56" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" s="17">
         <v>0</v>
       </c>
-      <c r="L56" s="13"/>
+      <c r="L56" s="13">
+        <v>0</v>
+      </c>
       <c r="M56" s="13"/>
       <c r="N56" s="13"/>
       <c r="O56" s="13"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
       <c r="R56" s="4">
-        <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <f>(D56+F56+H56+J56+L56+N56+P56)/7</f>
+        <v>0.2857142857142857</v>
       </c>
       <c r="S56" s="14">
-        <f t="shared" si="3"/>
+        <f>E56+G56+I56+K56+M56+O56+Q56</f>
         <v>65</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>28</v>
@@ -5249,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="H57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -5260,27 +5390,29 @@
       <c r="K57" s="17">
         <v>0</v>
       </c>
-      <c r="L57" s="13"/>
+      <c r="L57" s="13">
+        <v>0</v>
+      </c>
       <c r="M57" s="13"/>
       <c r="N57" s="13"/>
       <c r="O57" s="13"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
       <c r="R57" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D57+F57+H57+J57+L57+N57+P57)/7</f>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S57" s="14">
-        <f t="shared" si="3"/>
+        <f>E57+G57+I57+K57+M57+O57+Q57</f>
         <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>28</v>
@@ -5309,27 +5441,29 @@
       <c r="K58" s="17">
         <v>0</v>
       </c>
-      <c r="L58" s="13"/>
+      <c r="L58" s="13">
+        <v>1</v>
+      </c>
       <c r="M58" s="13"/>
       <c r="N58" s="13"/>
       <c r="O58" s="13"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D58+F58+H58+J58+L58+N58+P58)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S58" s="14">
-        <f t="shared" si="3"/>
+        <f>E58+G58+I58+K58+M58+O58+Q58</f>
         <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C59" s="10" t="s">
         <v>28</v>
@@ -5358,27 +5492,29 @@
       <c r="K59" s="17">
         <v>0</v>
       </c>
-      <c r="L59" s="13"/>
+      <c r="L59" s="13">
+        <v>1</v>
+      </c>
       <c r="M59" s="13"/>
       <c r="N59" s="13"/>
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
       <c r="R59" s="4">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D59+F59+H59+J59+L59+N59+P59)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S59" s="14">
-        <f t="shared" si="3"/>
+        <f>E59+G59+I59+K59+M59+O59+Q59</f>
         <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C60" s="10" t="s">
         <v>28</v>
@@ -5407,27 +5543,29 @@
       <c r="K60" s="17">
         <v>0</v>
       </c>
-      <c r="L60" s="13"/>
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
       <c r="M60" s="13"/>
       <c r="N60" s="13"/>
       <c r="O60" s="13"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
       <c r="R60" s="16">
-        <f t="shared" si="2"/>
+        <f>(D60+F60+H60+J60+L60+N60+P60)/7</f>
         <v>0.5714285714285714</v>
       </c>
       <c r="S60" s="14">
-        <f t="shared" si="3"/>
+        <f>E60+G60+I60+K60+M60+O60+Q60</f>
         <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C61" s="10" t="s">
         <v>28</v>
@@ -5456,27 +5594,29 @@
       <c r="K61" s="17">
         <v>0</v>
       </c>
-      <c r="L61" s="13"/>
+      <c r="L61" s="13">
+        <v>1</v>
+      </c>
       <c r="M61" s="13"/>
       <c r="N61" s="13"/>
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
       <c r="R61" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D61+F61+H61+J61+L61+N61+P61)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S61" s="14">
-        <f t="shared" si="3"/>
+        <f>E61+G61+I61+K61+M61+O61+Q61</f>
         <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>28</v>
@@ -5505,27 +5645,29 @@
       <c r="K62" s="17">
         <v>0</v>
       </c>
-      <c r="L62" s="13"/>
+      <c r="L62" s="13">
+        <v>1</v>
+      </c>
       <c r="M62" s="13"/>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
       <c r="P62" s="13"/>
       <c r="Q62" s="13"/>
       <c r="R62" s="16">
-        <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <f>(D62+F62+H62+J62+L62+N62+P62)/7</f>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S62" s="14">
-        <f t="shared" si="3"/>
+        <f>E62+G62+I62+K62+M62+O62+Q62</f>
         <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63" s="10" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C63" s="10" t="s">
         <v>28</v>
@@ -5554,25 +5696,78 @@
       <c r="K63" s="17">
         <v>0</v>
       </c>
-      <c r="L63" s="13"/>
+      <c r="L63" s="13">
+        <v>1</v>
+      </c>
       <c r="M63" s="13"/>
       <c r="N63" s="13"/>
       <c r="O63" s="13"/>
       <c r="P63" s="13"/>
       <c r="Q63" s="13"/>
       <c r="R63" s="16">
-        <f t="shared" si="2"/>
+        <f>(D63+F63+H63+J63+L63+N63+P63)/7</f>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="S63" s="14">
+        <f>E63+G63+I63+K63+M63+O63+Q63</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A64" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64" s="11">
+        <v>1</v>
+      </c>
+      <c r="E64" s="28">
+        <v>50</v>
+      </c>
+      <c r="F64" s="11">
+        <v>1</v>
+      </c>
+      <c r="G64" s="13">
+        <v>15</v>
+      </c>
+      <c r="H64" s="13">
+        <v>1</v>
+      </c>
+      <c r="I64" s="13">
+        <v>0</v>
+      </c>
+      <c r="J64" s="13">
+        <v>1</v>
+      </c>
+      <c r="K64" s="29">
+        <v>0</v>
+      </c>
+      <c r="L64" s="13">
+        <v>0</v>
+      </c>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13"/>
+      <c r="O64" s="13"/>
+      <c r="P64" s="13"/>
+      <c r="Q64" s="13"/>
+      <c r="R64" s="16">
+        <f>(D64+F64+H64+J64+L64+N64+P64)/7</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="S63" s="14">
-        <f t="shared" si="3"/>
+      <c r="S64" s="14">
+        <f>E64+G64+I64+K64+M64+O64+Q64</f>
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="F1:F59" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:S65">
-    <sortCondition ref="C2:C65"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:S64">
+    <sortCondition ref="C2:C64"/>
   </sortState>
   <mergeCells count="9">
     <mergeCell ref="P1:Q1"/>
@@ -5597,7 +5792,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5616,99 +5811,99 @@
       <c r="A4" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="26">
+      <c r="B4" s="31">
         <v>145</v>
       </c>
       <c r="C4" s="7">
-        <v>0.51020408163265307</v>
+        <v>0.6071428571428571</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="31">
         <v>50</v>
       </c>
       <c r="C5" s="7">
-        <v>0.44897959183673464</v>
+        <v>0.48979591836734698</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="31">
         <v>215</v>
       </c>
       <c r="C6" s="7">
-        <v>0.51428571428571423</v>
+        <v>0.62857142857142845</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="31">
         <v>150</v>
       </c>
       <c r="C7" s="7">
-        <v>0.42857142857142855</v>
+        <v>0.57142857142857129</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="31">
         <v>50</v>
       </c>
       <c r="C8" s="7">
-        <v>0.42857142857142849</v>
+        <v>0.54285714285714282</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="31">
         <v>45</v>
       </c>
       <c r="C9" s="7">
-        <v>0.24999999999999997</v>
+        <v>0.39285714285714285</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="31">
         <v>150</v>
       </c>
       <c r="C10" s="7">
-        <v>0.53061224489795911</v>
+        <v>0.65306122448979587</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="31">
         <v>65</v>
       </c>
       <c r="C11" s="7">
-        <v>0.52857142857142847</v>
+        <v>0.61904761904761907</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="26">
-        <v>111.39344262295081</v>
+      <c r="B12" s="31">
+        <v>112.70491803278688</v>
       </c>
       <c r="C12" s="7">
-        <v>0.47072599531615938</v>
+        <v>0.57611241217798592</v>
       </c>
     </row>
   </sheetData>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C90DF4-AF1B-5E4E-832C-172F264BEC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D223E7-0CBA-9B46-B8CB-7BC01A8D449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="24" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -634,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -698,28 +698,13 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -740,7 +725,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46133.448483217595" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46137.652650578704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -791,7 +776,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L5 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-10" maxValue="120"/>
     </cacheField>
     <cacheField name="L6 Presenza" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -809,7 +794,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="0.7142857142857143"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45" maxValue="215"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="35" maxValue="270"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -835,13 +820,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -856,13 +841,13 @@
     <n v="0"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -877,13 +862,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -898,13 +883,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -919,13 +904,13 @@
     <n v="0"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -940,13 +925,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -961,13 +946,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Castiglia"/>
@@ -982,13 +967,13 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="145"/>
+    <n v="265"/>
   </r>
   <r>
     <s v="Cuomo"/>
@@ -1003,13 +988,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Ercolano"/>
@@ -1024,13 +1009,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Forte"/>
@@ -1045,13 +1030,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1066,13 +1051,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Paone"/>
@@ -1087,13 +1072,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Petrone"/>
@@ -1108,13 +1093,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Preteverde"/>
@@ -1129,13 +1114,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="50"/>
+    <n v="40"/>
   </r>
   <r>
     <s v="Baudrand"/>
@@ -1150,13 +1135,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Borreca"/>
@@ -1171,13 +1156,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Borrione"/>
@@ -1192,13 +1177,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Cappelluccio"/>
@@ -1213,13 +1198,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Casale"/>
@@ -1234,13 +1219,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Marrazzo"/>
@@ -1255,13 +1240,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Miles"/>
@@ -1276,13 +1261,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Parente"/>
@@ -1297,13 +1282,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Pietropaolo"/>
@@ -1318,13 +1303,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Rispoli"/>
@@ -1339,13 +1324,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="215"/>
+    <n v="255"/>
   </r>
   <r>
     <s v="Maione"/>
@@ -1360,13 +1345,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Nasti"/>
@@ -1381,13 +1366,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Noviello"/>
@@ -1402,13 +1387,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Pepe"/>
@@ -1423,13 +1408,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Tartaro"/>
@@ -1444,13 +1429,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Versi"/>
@@ -1465,13 +1450,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="40"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="150"/>
+    <n v="190"/>
   </r>
   <r>
     <s v="Borrelli"/>
@@ -1486,13 +1471,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Canzolino"/>
@@ -1507,13 +1492,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="De Siena"/>
@@ -1528,13 +1513,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Di Meglio"/>
@@ -1549,13 +1534,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Esposito"/>
@@ -1570,13 +1555,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Ferrante"/>
@@ -1591,13 +1576,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Maglietta"/>
@@ -1612,13 +1597,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Patroni Griffi"/>
@@ -1633,13 +1618,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Semioli"/>
@@ -1654,13 +1639,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Siano"/>
@@ -1675,13 +1660,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="50"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="Agliottone"/>
@@ -1696,13 +1681,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="45"/>
+    <n v="35"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1717,13 +1702,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="45"/>
+    <n v="35"/>
   </r>
   <r>
     <s v="Imperatore"/>
@@ -1738,13 +1723,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="45"/>
+    <n v="35"/>
   </r>
   <r>
     <s v="Monaco"/>
@@ -1759,13 +1744,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="-10"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="45"/>
+    <n v="35"/>
   </r>
   <r>
     <s v="Cerundolo"/>
@@ -1780,13 +1765,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Chieti"/>
@@ -1801,13 +1786,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Coda"/>
@@ -1822,13 +1807,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Dibartolomeo"/>
@@ -1843,13 +1828,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Raduazzo"/>
@@ -1864,13 +1849,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Vable"/>
@@ -1885,13 +1870,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Zito"/>
@@ -1906,13 +1891,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="120"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="150"/>
+    <n v="270"/>
   </r>
   <r>
     <s v="Antico"/>
@@ -1927,13 +1912,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="D'Acunto"/>
@@ -1948,13 +1933,13 @@
     <n v="0"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Di Fiore"/>
@@ -1969,13 +1954,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Ditri"/>
@@ -1990,13 +1975,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Fraddanno"/>
@@ -2011,13 +1996,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Marciello"/>
@@ -2032,13 +2017,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="0"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Miranda"/>
@@ -2053,13 +2038,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Rolletta"/>
@@ -2074,13 +2059,13 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
   <r>
     <s v="Soriano"/>
@@ -2095,24 +2080,24 @@
     <n v="1"/>
     <n v="0"/>
     <n v="1"/>
-    <m/>
+    <n v="50"/>
     <m/>
     <m/>
     <m/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="65"/>
+    <n v="115"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="9">
         <item x="0"/>
         <item x="1"/>
@@ -2124,6 +2109,15 @@
         <item x="7"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -2147,10 +2141,10 @@
   </rowFields>
   <rowItems count="9">
     <i>
-      <x/>
+      <x v="6"/>
     </i>
     <i>
-      <x v="1"/>
+      <x/>
     </i>
     <i>
       <x v="2"/>
@@ -2159,16 +2153,16 @@
       <x v="3"/>
     </i>
     <i>
+      <x v="7"/>
+    </i>
+    <i>
       <x v="4"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
+      <x v="5"/>
     </i>
     <i t="grand">
       <x/>
@@ -2510,11 +2504,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
       <c r="D1" s="20" t="s">
         <v>1</v>
       </c>
@@ -2543,10 +2537,10 @@
         <v>7</v>
       </c>
       <c r="Q1" s="21"/>
-      <c r="R1" s="24" t="s">
+      <c r="R1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="24"/>
+      <c r="S1" s="23"/>
     </row>
     <row r="2" spans="1:19" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -2644,18 +2638,20 @@
       <c r="L3" s="17">
         <v>1</v>
       </c>
-      <c r="M3" s="17"/>
+      <c r="M3" s="17">
+        <v>120</v>
+      </c>
       <c r="N3" s="17"/>
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="4">
-        <f>(D3+F3+H3+J3+L3+N3+P3)/7</f>
+        <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
         <v>0.7142857142857143</v>
       </c>
       <c r="S3" s="3">
-        <f>E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>145</v>
+        <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2695,18 +2691,20 @@
       <c r="L4" s="17">
         <v>1</v>
       </c>
-      <c r="M4" s="17"/>
+      <c r="M4" s="17">
+        <v>120</v>
+      </c>
       <c r="N4" s="17"/>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="4">
-        <f>(D4+F4+H4+J4+L4+N4+P4)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S4" s="3">
-        <f>E4+G4+I4+K4+M4+O4+Q4</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2746,18 +2744,20 @@
       <c r="L5" s="17">
         <v>1</v>
       </c>
-      <c r="M5" s="17"/>
+      <c r="M5" s="17">
+        <v>120</v>
+      </c>
       <c r="N5" s="17"/>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
       <c r="R5" s="4">
-        <f>(D5+F5+H5+J5+L5+N5+P5)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S5" s="3">
-        <f>E5+G5+I5+K5+M5+O5+Q5</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2797,18 +2797,20 @@
       <c r="L6" s="17">
         <v>1</v>
       </c>
-      <c r="M6" s="17"/>
+      <c r="M6" s="17">
+        <v>120</v>
+      </c>
       <c r="N6" s="17"/>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="4">
-        <f>(D6+F6+H6+J6+L6+N6+P6)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S6" s="3">
-        <f>E6+G6+I6+K6+M6+O6+Q6</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2848,18 +2850,20 @@
       <c r="L7" s="17">
         <v>1</v>
       </c>
-      <c r="M7" s="17"/>
+      <c r="M7" s="17">
+        <v>120</v>
+      </c>
       <c r="N7" s="17"/>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="4">
-        <f>(D7+F7+H7+J7+L7+N7+P7)/7</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S7" s="3">
-        <f>E7+G7+I7+K7+M7+O7+Q7</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2899,18 +2903,20 @@
       <c r="L8" s="17">
         <v>1</v>
       </c>
-      <c r="M8" s="17"/>
+      <c r="M8" s="17">
+        <v>120</v>
+      </c>
       <c r="N8" s="17"/>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="4">
-        <f>(D8+F8+H8+J8+L8+N8+P8)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S8" s="3">
-        <f>E8+G8+I8+K8+M8+O8+Q8</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2950,37 +2956,39 @@
       <c r="L9" s="17">
         <v>1</v>
       </c>
-      <c r="M9" s="17"/>
+      <c r="M9" s="17">
+        <v>120</v>
+      </c>
       <c r="N9" s="17"/>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="4">
-        <f>(D9+F9+H9+J9+L9+N9+P9)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S9" s="3">
-        <f>E9+G9+I9+K9+M9+O9+Q9</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="9">
         <v>0</v>
       </c>
       <c r="E10" s="17">
         <v>50</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="9">
         <v>0</v>
       </c>
       <c r="G10" s="17">
@@ -3001,18 +3009,20 @@
       <c r="L10" s="17">
         <v>0</v>
       </c>
-      <c r="M10" s="17"/>
+      <c r="M10" s="17">
+        <v>120</v>
+      </c>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="4">
-        <f>(D10+F10+H10+J10+L10+N10+P10)/7</f>
+        <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S10" s="3">
-        <f>E10+G10+I10+K10+M10+O10+Q10</f>
-        <v>145</v>
+        <f t="shared" si="1"/>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -3052,18 +3062,20 @@
       <c r="L11" s="17">
         <v>0</v>
       </c>
-      <c r="M11" s="17"/>
+      <c r="M11" s="17">
+        <v>-10</v>
+      </c>
       <c r="N11" s="17"/>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
       <c r="R11" s="4">
-        <f>(D11+F11+H11+J11+L11+N11+P11)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S11" s="3">
-        <f>E11+G11+I11+K11+M11+O11+Q11</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -3103,18 +3115,20 @@
       <c r="L12" s="17">
         <v>0</v>
       </c>
-      <c r="M12" s="17"/>
+      <c r="M12" s="17">
+        <v>-10</v>
+      </c>
       <c r="N12" s="17"/>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
       <c r="R12" s="4">
-        <f>(D12+F12+H12+J12+L12+N12+P12)/7</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S12" s="3">
-        <f>E12+G12+I12+K12+M12+O12+Q12</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -3154,18 +3168,20 @@
       <c r="L13" s="17">
         <v>1</v>
       </c>
-      <c r="M13" s="17"/>
+      <c r="M13" s="17">
+        <v>-10</v>
+      </c>
       <c r="N13" s="17"/>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
       <c r="R13" s="4">
-        <f>(D13+F13+H13+J13+L13+N13+P13)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S13" s="3">
-        <f>E13+G13+I13+K13+M13+O13+Q13</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
@@ -3205,18 +3221,20 @@
       <c r="L14" s="17">
         <v>0</v>
       </c>
-      <c r="M14" s="17"/>
+      <c r="M14" s="17">
+        <v>-10</v>
+      </c>
       <c r="N14" s="17"/>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
       <c r="R14" s="4">
-        <f>(D14+F14+H14+J14+L14+N14+P14)/7</f>
+        <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S14" s="3">
-        <f>E14+G14+I14+K14+M14+O14+Q14</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -3256,18 +3274,20 @@
       <c r="L15" s="17">
         <v>0</v>
       </c>
-      <c r="M15" s="17"/>
+      <c r="M15" s="17">
+        <v>-10</v>
+      </c>
       <c r="N15" s="17"/>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
       <c r="R15" s="4">
-        <f>(D15+F15+H15+J15+L15+N15+P15)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S15" s="3">
-        <f>E15+G15+I15+K15+M15+O15+Q15</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -3307,18 +3327,20 @@
       <c r="L16" s="17">
         <v>0</v>
       </c>
-      <c r="M16" s="17"/>
+      <c r="M16" s="17">
+        <v>-10</v>
+      </c>
       <c r="N16" s="17"/>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
       <c r="R16" s="4">
-        <f>(D16+F16+H16+J16+L16+N16+P16)/7</f>
+        <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S16" s="3">
-        <f>E16+G16+I16+K16+M16+O16+Q16</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
@@ -3358,18 +3380,20 @@
       <c r="L17" s="17">
         <v>1</v>
       </c>
-      <c r="M17" s="17"/>
+      <c r="M17" s="17">
+        <v>-10</v>
+      </c>
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
       <c r="R17" s="4">
-        <f>(D17+F17+H17+J17+L17+N17+P17)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S17" s="3">
-        <f>E17+G17+I17+K17+M17+O17+Q17</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
@@ -3409,18 +3433,20 @@
       <c r="L18" s="9">
         <v>1</v>
       </c>
-      <c r="M18" s="9"/>
+      <c r="M18" s="9">
+        <v>40</v>
+      </c>
       <c r="N18" s="9"/>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
-        <f>(D18+F18+H18+J18+L18+N18+P18)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S18" s="3">
-        <f>E18+G18+I18+K18+M18+O18+Q18</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -3460,18 +3486,20 @@
       <c r="L19" s="9">
         <v>0</v>
       </c>
-      <c r="M19" s="9"/>
+      <c r="M19" s="9">
+        <v>40</v>
+      </c>
       <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
-        <f>(D19+F19+H19+J19+L19+N19+P19)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S19" s="3">
-        <f>E19+G19+I19+K19+M19+O19+Q19</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -3511,18 +3539,20 @@
       <c r="L20" s="9">
         <v>1</v>
       </c>
-      <c r="M20" s="9"/>
+      <c r="M20" s="9">
+        <v>40</v>
+      </c>
       <c r="N20" s="9"/>
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
-        <f>(D20+F20+H20+J20+L20+N20+P20)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S20" s="3">
-        <f>E20+G20+I20+K20+M20+O20+Q20</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -3562,18 +3592,20 @@
       <c r="L21" s="9">
         <v>1</v>
       </c>
-      <c r="M21" s="9"/>
+      <c r="M21" s="9">
+        <v>40</v>
+      </c>
       <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
       <c r="R21" s="4">
-        <f>(D21+F21+H21+J21+L21+N21+P21)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S21" s="3">
-        <f>E21+G21+I21+K21+M21+O21+Q21</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -3613,18 +3645,20 @@
       <c r="L22" s="9">
         <v>1</v>
       </c>
-      <c r="M22" s="9"/>
+      <c r="M22" s="9">
+        <v>40</v>
+      </c>
       <c r="N22" s="9"/>
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="4">
-        <f>(D22+F22+H22+J22+L22+N22+P22)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S22" s="3">
-        <f>E22+G22+I22+K22+M22+O22+Q22</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -3664,18 +3698,20 @@
       <c r="L23" s="9">
         <v>1</v>
       </c>
-      <c r="M23" s="9"/>
+      <c r="M23" s="9">
+        <v>40</v>
+      </c>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
-        <f>(D23+F23+H23+J23+L23+N23+P23)/7</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S23" s="3">
-        <f>E23+G23+I23+K23+M23+O23+Q23</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -3715,18 +3751,20 @@
       <c r="L24" s="9">
         <v>1</v>
       </c>
-      <c r="M24" s="9"/>
+      <c r="M24" s="9">
+        <v>40</v>
+      </c>
       <c r="N24" s="9"/>
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
-        <f>(D24+F24+H24+J24+L24+N24+P24)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S24" s="3">
-        <f>E24+G24+I24+K24+M24+O24+Q24</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -3766,18 +3804,20 @@
       <c r="L25" s="9">
         <v>1</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="9">
+        <v>40</v>
+      </c>
       <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
-        <f>(D25+F25+H25+J25+L25+N25+P25)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S25" s="3">
-        <f>E25+G25+I25+K25+M25+O25+Q25</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -3817,18 +3857,20 @@
       <c r="L26" s="9">
         <v>0</v>
       </c>
-      <c r="M26" s="9"/>
+      <c r="M26" s="9">
+        <v>40</v>
+      </c>
       <c r="N26" s="9"/>
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
-        <f>(D26+F26+H26+J26+L26+N26+P26)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S26" s="3">
-        <f>E26+G26+I26+K26+M26+O26+Q26</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -3868,18 +3910,20 @@
       <c r="L27" s="9">
         <v>1</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="9">
+        <v>40</v>
+      </c>
       <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
-        <f>(D27+F27+H27+J27+L27+N27+P27)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S27" s="3">
-        <f>E27+G27+I27+K27+M27+O27+Q27</f>
-        <v>215</v>
+        <f t="shared" si="1"/>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -3919,18 +3963,20 @@
       <c r="L28" s="9">
         <v>1</v>
       </c>
-      <c r="M28" s="9"/>
+      <c r="M28" s="9">
+        <v>40</v>
+      </c>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="4">
-        <f>(D28+F28+H28+J28+L28+N28+P28)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S28" s="3">
-        <f>E28+G28+I28+K28+M28+O28+Q28</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -3970,18 +4016,20 @@
       <c r="L29" s="9">
         <v>1</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="9">
+        <v>40</v>
+      </c>
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
       <c r="R29" s="4">
-        <f>(D29+F29+H29+J29+L29+N29+P29)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S29" s="3">
-        <f>E29+G29+I29+K29+M29+O29+Q29</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -4021,18 +4069,20 @@
       <c r="L30" s="9">
         <v>1</v>
       </c>
-      <c r="M30" s="9"/>
+      <c r="M30" s="9">
+        <v>40</v>
+      </c>
       <c r="N30" s="9"/>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
-        <f>(D30+F30+H30+J30+L30+N30+P30)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S30" s="3">
-        <f>E30+G30+I30+K30+M30+O30+Q30</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
@@ -4072,18 +4122,20 @@
       <c r="L31" s="9">
         <v>1</v>
       </c>
-      <c r="M31" s="9"/>
+      <c r="M31" s="9">
+        <v>40</v>
+      </c>
       <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="R31" s="4">
-        <f>(D31+F31+H31+J31+L31+N31+P31)/7</f>
+        <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S31" s="3">
-        <f>E31+G31+I31+K31+M31+O31+Q31</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -4123,18 +4175,20 @@
       <c r="L32" s="9">
         <v>1</v>
       </c>
-      <c r="M32" s="9"/>
+      <c r="M32" s="9">
+        <v>40</v>
+      </c>
       <c r="N32" s="9"/>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
       <c r="R32" s="4">
-        <f>(D32+F32+H32+J32+L32+N32+P32)/7</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S32" s="3">
-        <f>E32+G32+I32+K32+M32+O32+Q32</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
@@ -4174,18 +4228,20 @@
       <c r="L33" s="9">
         <v>1</v>
       </c>
-      <c r="M33" s="9"/>
+      <c r="M33" s="9">
+        <v>40</v>
+      </c>
       <c r="N33" s="9"/>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
       <c r="R33" s="4">
-        <f>(D33+F33+H33+J33+L33+N33+P33)/7</f>
+        <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S33" s="3">
-        <f>E33+G33+I33+K33+M33+O33+Q33</f>
-        <v>150</v>
+        <f t="shared" si="1"/>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -4225,18 +4281,20 @@
       <c r="L34" s="9">
         <v>1</v>
       </c>
-      <c r="M34" s="9"/>
+      <c r="M34" s="9">
+        <v>50</v>
+      </c>
       <c r="N34" s="9"/>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
-        <f>(D34+F34+H34+J34+L34+N34+P34)/7</f>
+        <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S34" s="3">
-        <f>E34+G34+I34+K34+M34+O34+Q34</f>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -4276,18 +4334,20 @@
       <c r="L35" s="9">
         <v>1</v>
       </c>
-      <c r="M35" s="9"/>
+      <c r="M35" s="9">
+        <v>50</v>
+      </c>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
-        <f>(D35+F35+H35+J35+L35+N35+P35)/7</f>
+        <f t="shared" ref="R35:R64" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
         <v>0.7142857142857143</v>
       </c>
       <c r="S35" s="3">
-        <f>E35+G35+I35+K35+M35+O35+Q35</f>
-        <v>50</v>
+        <f t="shared" ref="S35:S64" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -4327,18 +4387,20 @@
       <c r="L36" s="9">
         <v>1</v>
       </c>
-      <c r="M36" s="9"/>
+      <c r="M36" s="9">
+        <v>50</v>
+      </c>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
-        <f>(D36+F36+H36+J36+L36+N36+P36)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S36" s="3">
-        <f>E36+G36+I36+K36+M36+O36+Q36</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -4378,18 +4440,20 @@
       <c r="L37" s="9">
         <v>1</v>
       </c>
-      <c r="M37" s="9"/>
+      <c r="M37" s="9">
+        <v>50</v>
+      </c>
       <c r="N37" s="9"/>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
       <c r="R37" s="4">
-        <f>(D37+F37+H37+J37+L37+N37+P37)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S37" s="3">
-        <f>E37+G37+I37+K37+M37+O37+Q37</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -4429,18 +4493,20 @@
       <c r="L38" s="9">
         <v>1</v>
       </c>
-      <c r="M38" s="9"/>
+      <c r="M38" s="9">
+        <v>50</v>
+      </c>
       <c r="N38" s="9"/>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
-        <f>(D38+F38+H38+J38+L38+N38+P38)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S38" s="3">
-        <f>E38+G38+I38+K38+M38+O38+Q38</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -4480,18 +4546,20 @@
       <c r="L39" s="9">
         <v>1</v>
       </c>
-      <c r="M39" s="9"/>
+      <c r="M39" s="9">
+        <v>50</v>
+      </c>
       <c r="N39" s="9"/>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
       <c r="R39" s="4">
-        <f>(D39+F39+H39+J39+L39+N39+P39)/7</f>
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S39" s="3">
-        <f>E39+G39+I39+K39+M39+O39+Q39</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -4531,18 +4599,20 @@
       <c r="L40" s="9">
         <v>0</v>
       </c>
-      <c r="M40" s="9"/>
+      <c r="M40" s="9">
+        <v>50</v>
+      </c>
       <c r="N40" s="9"/>
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
-        <f>(D40+F40+H40+J40+L40+N40+P40)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S40" s="3">
-        <f>E40+G40+I40+K40+M40+O40+Q40</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -4582,18 +4652,20 @@
       <c r="L41" s="9">
         <v>1</v>
       </c>
-      <c r="M41" s="9"/>
+      <c r="M41" s="9">
+        <v>50</v>
+      </c>
       <c r="N41" s="9"/>
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
       <c r="R41" s="4">
-        <f>(D41+F41+H41+J41+L41+N41+P41)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S41" s="3">
-        <f>E41+G41+I41+K41+M41+O41+Q41</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
@@ -4633,18 +4705,20 @@
       <c r="L42" s="9">
         <v>1</v>
       </c>
-      <c r="M42" s="9"/>
+      <c r="M42" s="9">
+        <v>50</v>
+      </c>
       <c r="N42" s="9"/>
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
-        <f>(D42+F42+H42+J42+L42+N42+P42)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S42" s="3">
-        <f>E42+G42+I42+K42+M42+O42+Q42</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
@@ -4684,18 +4758,20 @@
       <c r="L43" s="9">
         <v>0</v>
       </c>
-      <c r="M43" s="9"/>
+      <c r="M43" s="9">
+        <v>50</v>
+      </c>
       <c r="N43" s="9"/>
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
       <c r="R43" s="4">
-        <f>(D43+F43+H43+J43+L43+N43+P43)/7</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S43" s="3">
-        <f>E43+G43+I43+K43+M43+O43+Q43</f>
-        <v>50</v>
+        <f t="shared" si="3"/>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
@@ -4735,18 +4811,20 @@
       <c r="L44" s="17">
         <v>1</v>
       </c>
-      <c r="M44" s="17"/>
+      <c r="M44" s="17">
+        <v>-10</v>
+      </c>
       <c r="N44" s="17"/>
       <c r="O44" s="17"/>
       <c r="P44" s="17"/>
       <c r="Q44" s="17"/>
       <c r="R44" s="4">
-        <f>(D44+F44+H44+J44+L44+N44+P44)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S44" s="3">
-        <f>E44+G44+I44+K44+M44+O44+Q44</f>
-        <v>45</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
@@ -4786,18 +4864,20 @@
       <c r="L45" s="17">
         <v>1</v>
       </c>
-      <c r="M45" s="17"/>
+      <c r="M45" s="17">
+        <v>-10</v>
+      </c>
       <c r="N45" s="17"/>
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
       <c r="Q45" s="17"/>
       <c r="R45" s="4">
-        <f>(D45+F45+H45+J45+L45+N45+P45)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S45" s="3">
-        <f>E45+G45+I45+K45+M45+O45+Q45</f>
-        <v>45</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -4828,27 +4908,25 @@
       <c r="I46" s="17">
         <v>-5</v>
       </c>
-      <c r="J46" s="29">
+      <c r="J46" s="18">
         <v>0</v>
       </c>
       <c r="K46" s="17">
         <v>0</v>
       </c>
-      <c r="L46" s="29">
-        <v>1</v>
-      </c>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
+      <c r="L46" s="18">
+        <v>1</v>
+      </c>
+      <c r="M46" s="17">
+        <v>-10</v>
+      </c>
       <c r="R46" s="4">
-        <f>(D46+F46+H46+J46+L46+N46+P46)/7</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S46" s="12">
-        <f>E46+G46+I46+K46+M46+O46+Q46</f>
-        <v>45</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -4870,13 +4948,13 @@
       <c r="F47" s="9">
         <v>1</v>
       </c>
-      <c r="G47" s="28">
-        <v>0</v>
-      </c>
-      <c r="H47" s="29">
-        <v>1</v>
-      </c>
-      <c r="I47" s="29">
+      <c r="G47" s="13">
+        <v>0</v>
+      </c>
+      <c r="H47" s="18">
+        <v>1</v>
+      </c>
+      <c r="I47" s="18">
         <v>-5</v>
       </c>
       <c r="J47" s="18">
@@ -4888,13 +4966,16 @@
       <c r="L47" s="18">
         <v>1</v>
       </c>
+      <c r="M47" s="17">
+        <v>-10</v>
+      </c>
       <c r="R47" s="4">
-        <f>(D47+F47+H47+J47+L47+N47+P47)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S47" s="12">
-        <f>E47+G47+I47+K47+M47+O47+Q47</f>
-        <v>45</v>
+        <f t="shared" si="3"/>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
@@ -4934,18 +5015,20 @@
       <c r="L48" s="13">
         <v>1</v>
       </c>
-      <c r="M48" s="13"/>
+      <c r="M48" s="13">
+        <v>120</v>
+      </c>
       <c r="N48" s="13"/>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
       <c r="Q48" s="13"/>
       <c r="R48" s="4">
-        <f>(D48+F48+H48+J48+L48+N48+P48)/7</f>
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S48" s="12">
-        <f>E48+G48+I48+K48+M48+O48+Q48</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
@@ -4985,18 +5068,20 @@
       <c r="L49" s="13">
         <v>1</v>
       </c>
-      <c r="M49" s="13"/>
+      <c r="M49" s="13">
+        <v>120</v>
+      </c>
       <c r="N49" s="13"/>
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
       <c r="R49" s="4">
-        <f>(D49+F49+H49+J49+L49+N49+P49)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S49" s="12">
-        <f>E49+G49+I49+K49+M49+O49+Q49</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
@@ -5036,18 +5121,20 @@
       <c r="L50" s="13">
         <v>1</v>
       </c>
-      <c r="M50" s="13"/>
+      <c r="M50" s="13">
+        <v>120</v>
+      </c>
       <c r="N50" s="13"/>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="4">
-        <f>(D50+F50+H50+J50+L50+N50+P50)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S50" s="12">
-        <f>E50+G50+I50+K50+M50+O50+Q50</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
@@ -5087,18 +5174,20 @@
       <c r="L51" s="13">
         <v>1</v>
       </c>
-      <c r="M51" s="13"/>
+      <c r="M51" s="13">
+        <v>120</v>
+      </c>
       <c r="N51" s="13"/>
       <c r="O51" s="13"/>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
       <c r="R51" s="4">
-        <f>(D51+F51+H51+J51+L51+N51+P51)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="S51" s="30">
-        <f>E51+G51+I51+K51+M51+O51+Q51</f>
-        <v>150</v>
+      <c r="S51" s="14">
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -5138,18 +5227,20 @@
       <c r="L52" s="13">
         <v>0</v>
       </c>
-      <c r="M52" s="13"/>
+      <c r="M52" s="13">
+        <v>120</v>
+      </c>
       <c r="N52" s="13"/>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
       <c r="R52" s="4">
-        <f>(D52+F52+H52+J52+L52+N52+P52)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S52" s="14">
-        <f>E52+G52+I52+K52+M52+O52+Q52</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -5189,18 +5280,20 @@
       <c r="L53" s="13">
         <v>1</v>
       </c>
-      <c r="M53" s="13"/>
+      <c r="M53" s="13">
+        <v>120</v>
+      </c>
       <c r="N53" s="13"/>
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
       <c r="R53" s="4">
-        <f>(D53+F53+H53+J53+L53+N53+P53)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S53" s="14">
-        <f>E53+G53+I53+K53+M53+O53+Q53</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -5240,18 +5333,20 @@
       <c r="L54" s="13">
         <v>1</v>
       </c>
-      <c r="M54" s="13"/>
+      <c r="M54" s="13">
+        <v>120</v>
+      </c>
       <c r="N54" s="13"/>
       <c r="O54" s="13"/>
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
       <c r="R54" s="4">
-        <f>(D54+F54+H54+J54+L54+N54+P54)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S54" s="14">
-        <f>E54+G54+I54+K54+M54+O54+Q54</f>
-        <v>150</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
@@ -5291,18 +5386,20 @@
       <c r="L55" s="13">
         <v>1</v>
       </c>
-      <c r="M55" s="13"/>
+      <c r="M55" s="13">
+        <v>50</v>
+      </c>
       <c r="N55" s="13"/>
       <c r="O55" s="13"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
       <c r="R55" s="4">
-        <f>(D55+F55+H55+J55+L55+N55+P55)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S55" s="14">
-        <f>E55+G55+I55+K55+M55+O55+Q55</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -5342,18 +5439,20 @@
       <c r="L56" s="13">
         <v>0</v>
       </c>
-      <c r="M56" s="13"/>
+      <c r="M56" s="13">
+        <v>50</v>
+      </c>
       <c r="N56" s="13"/>
       <c r="O56" s="13"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
       <c r="R56" s="4">
-        <f>(D56+F56+H56+J56+L56+N56+P56)/7</f>
+        <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="S56" s="14">
-        <f>E56+G56+I56+K56+M56+O56+Q56</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
@@ -5393,18 +5492,20 @@
       <c r="L57" s="13">
         <v>0</v>
       </c>
-      <c r="M57" s="13"/>
+      <c r="M57" s="13">
+        <v>50</v>
+      </c>
       <c r="N57" s="13"/>
       <c r="O57" s="13"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
       <c r="R57" s="4">
-        <f>(D57+F57+H57+J57+L57+N57+P57)/7</f>
+        <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S57" s="14">
-        <f>E57+G57+I57+K57+M57+O57+Q57</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
@@ -5444,18 +5545,20 @@
       <c r="L58" s="13">
         <v>1</v>
       </c>
-      <c r="M58" s="13"/>
+      <c r="M58" s="13">
+        <v>50</v>
+      </c>
       <c r="N58" s="13"/>
       <c r="O58" s="13"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="4">
-        <f>(D58+F58+H58+J58+L58+N58+P58)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S58" s="14">
-        <f>E58+G58+I58+K58+M58+O58+Q58</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
@@ -5495,18 +5598,20 @@
       <c r="L59" s="13">
         <v>1</v>
       </c>
-      <c r="M59" s="13"/>
+      <c r="M59" s="13">
+        <v>50</v>
+      </c>
       <c r="N59" s="13"/>
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
       <c r="R59" s="4">
-        <f>(D59+F59+H59+J59+L59+N59+P59)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S59" s="14">
-        <f>E59+G59+I59+K59+M59+O59+Q59</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
@@ -5546,18 +5651,20 @@
       <c r="L60" s="13">
         <v>0</v>
       </c>
-      <c r="M60" s="13"/>
+      <c r="M60" s="13">
+        <v>50</v>
+      </c>
       <c r="N60" s="13"/>
       <c r="O60" s="13"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
       <c r="R60" s="16">
-        <f>(D60+F60+H60+J60+L60+N60+P60)/7</f>
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S60" s="14">
-        <f>E60+G60+I60+K60+M60+O60+Q60</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
@@ -5597,18 +5704,20 @@
       <c r="L61" s="13">
         <v>1</v>
       </c>
-      <c r="M61" s="13"/>
+      <c r="M61" s="13">
+        <v>50</v>
+      </c>
       <c r="N61" s="13"/>
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
       <c r="R61" s="16">
-        <f>(D61+F61+H61+J61+L61+N61+P61)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S61" s="14">
-        <f>E61+G61+I61+K61+M61+O61+Q61</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">
@@ -5648,18 +5757,20 @@
       <c r="L62" s="13">
         <v>1</v>
       </c>
-      <c r="M62" s="13"/>
+      <c r="M62" s="13">
+        <v>50</v>
+      </c>
       <c r="N62" s="13"/>
       <c r="O62" s="13"/>
       <c r="P62" s="13"/>
       <c r="Q62" s="13"/>
       <c r="R62" s="16">
-        <f>(D62+F62+H62+J62+L62+N62+P62)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S62" s="14">
-        <f>E62+G62+I62+K62+M62+O62+Q62</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
@@ -5699,18 +5810,20 @@
       <c r="L63" s="13">
         <v>1</v>
       </c>
-      <c r="M63" s="13"/>
+      <c r="M63" s="13">
+        <v>50</v>
+      </c>
       <c r="N63" s="13"/>
       <c r="O63" s="13"/>
       <c r="P63" s="13"/>
       <c r="Q63" s="13"/>
       <c r="R63" s="16">
-        <f>(D63+F63+H63+J63+L63+N63+P63)/7</f>
+        <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S63" s="14">
-        <f>E63+G63+I63+K63+M63+O63+Q63</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.2">
@@ -5726,7 +5839,7 @@
       <c r="D64" s="11">
         <v>1</v>
       </c>
-      <c r="E64" s="28">
+      <c r="E64" s="13">
         <v>50</v>
       </c>
       <c r="F64" s="11">
@@ -5744,24 +5857,26 @@
       <c r="J64" s="13">
         <v>1</v>
       </c>
-      <c r="K64" s="29">
+      <c r="K64" s="18">
         <v>0</v>
       </c>
       <c r="L64" s="13">
         <v>0</v>
       </c>
-      <c r="M64" s="13"/>
+      <c r="M64" s="13">
+        <v>50</v>
+      </c>
       <c r="N64" s="13"/>
       <c r="O64" s="13"/>
       <c r="P64" s="13"/>
       <c r="Q64" s="13"/>
       <c r="R64" s="16">
-        <f>(D64+F64+H64+J64+L64+N64+P64)/7</f>
+        <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S64" s="14">
-        <f>E64+G64+I64+K64+M64+O64+Q64</f>
-        <v>65</v>
+        <f t="shared" si="3"/>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -5792,7 +5907,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5809,32 +5924,32 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B4" s="31">
-        <v>145</v>
+        <v>47</v>
+      </c>
+      <c r="B4" s="26">
+        <v>270</v>
       </c>
       <c r="C4" s="7">
-        <v>0.6071428571428571</v>
+        <v>0.65306122448979587</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="B5" s="31">
-        <v>50</v>
+        <v>123</v>
+      </c>
+      <c r="B5" s="26">
+        <v>265</v>
       </c>
       <c r="C5" s="7">
-        <v>0.48979591836734698</v>
+        <v>0.6071428571428571</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="31">
-        <v>215</v>
+      <c r="B6" s="26">
+        <v>255</v>
       </c>
       <c r="C6" s="7">
         <v>0.62857142857142845</v>
@@ -5844,8 +5959,8 @@
       <c r="A7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="31">
-        <v>150</v>
+      <c r="B7" s="26">
+        <v>190</v>
       </c>
       <c r="C7" s="7">
         <v>0.57142857142857129</v>
@@ -5853,54 +5968,54 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="31">
-        <v>50</v>
+        <v>28</v>
+      </c>
+      <c r="B8" s="26">
+        <v>115</v>
       </c>
       <c r="C8" s="7">
-        <v>0.54285714285714282</v>
+        <v>0.61904761904761907</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="31">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="B9" s="26">
+        <v>100</v>
       </c>
       <c r="C9" s="7">
-        <v>0.39285714285714285</v>
+        <v>0.54285714285714282</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="31">
-        <v>150</v>
+        <v>135</v>
+      </c>
+      <c r="B10" s="26">
+        <v>40</v>
       </c>
       <c r="C10" s="7">
-        <v>0.65306122448979587</v>
+        <v>0.48979591836734698</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="31">
-        <v>65</v>
+        <v>149</v>
+      </c>
+      <c r="B11" s="26">
+        <v>35</v>
       </c>
       <c r="C11" s="7">
-        <v>0.61904761904761907</v>
+        <v>0.39285714285714285</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="B12" s="31">
-        <v>112.70491803278688</v>
+      <c r="B12" s="26">
+        <v>166.47540983606558</v>
       </c>
       <c r="C12" s="7">
         <v>0.57611241217798592</v>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D223E7-0CBA-9B46-B8CB-7BC01A8D449F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3B1EF-1720-A24B-80CB-59ECA45D892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="24" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -725,7 +725,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46137.652650578704" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46141.659967361113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -779,7 +779,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-10" maxValue="120"/>
     </cacheField>
     <cacheField name="L6 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L6 XP" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
@@ -791,7 +791,7 @@
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="0.7142857142857143"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="0.8571428571428571"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="35" maxValue="270"/>
@@ -821,11 +821,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="265"/>
   </r>
   <r>
@@ -842,11 +842,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="265"/>
   </r>
   <r>
@@ -863,7 +863,7 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -884,11 +884,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="265"/>
   </r>
   <r>
@@ -905,11 +905,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="265"/>
   </r>
   <r>
@@ -926,11 +926,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="265"/>
   </r>
   <r>
@@ -947,11 +947,11 @@
     <n v="50"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="265"/>
   </r>
   <r>
@@ -968,11 +968,11 @@
     <n v="50"/>
     <n v="0"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="265"/>
   </r>
   <r>
@@ -989,7 +989,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1010,7 +1010,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1031,7 +1031,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1052,7 +1052,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1073,7 +1073,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1094,7 +1094,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1115,7 +1115,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1136,11 +1136,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="255"/>
   </r>
   <r>
@@ -1157,11 +1157,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="255"/>
   </r>
   <r>
@@ -1178,11 +1178,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="255"/>
   </r>
   <r>
@@ -1199,7 +1199,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1220,11 +1220,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="255"/>
   </r>
   <r>
@@ -1241,11 +1241,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="255"/>
   </r>
   <r>
@@ -1262,11 +1262,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="255"/>
   </r>
   <r>
@@ -1283,11 +1283,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="255"/>
   </r>
   <r>
@@ -1304,11 +1304,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="255"/>
   </r>
   <r>
@@ -1325,11 +1325,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="255"/>
   </r>
   <r>
@@ -1346,7 +1346,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1367,7 +1367,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1388,7 +1388,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1409,7 +1409,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1430,7 +1430,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1451,7 +1451,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="40"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1472,7 +1472,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1493,7 +1493,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1514,7 +1514,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1535,7 +1535,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1556,7 +1556,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1577,7 +1577,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1598,7 +1598,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1619,7 +1619,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1640,11 +1640,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="100"/>
   </r>
   <r>
@@ -1661,7 +1661,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1682,7 +1682,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1703,7 +1703,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1724,7 +1724,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1745,7 +1745,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="-10"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1766,7 +1766,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1787,11 +1787,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="270"/>
   </r>
   <r>
@@ -1808,11 +1808,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="270"/>
   </r>
   <r>
@@ -1829,11 +1829,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="270"/>
   </r>
   <r>
@@ -1850,11 +1850,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.5714285714285714"/>
     <n v="270"/>
   </r>
   <r>
@@ -1871,11 +1871,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="270"/>
   </r>
   <r>
@@ -1892,11 +1892,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="120"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="270"/>
   </r>
   <r>
@@ -1913,11 +1913,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="115"/>
   </r>
   <r>
@@ -1934,11 +1934,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.42857142857142855"/>
     <n v="115"/>
   </r>
   <r>
@@ -1955,7 +1955,7 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -1976,11 +1976,11 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.8571428571428571"/>
     <n v="115"/>
   </r>
   <r>
@@ -1997,7 +1997,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -2018,11 +2018,11 @@
     <n v="0"/>
     <n v="0"/>
     <n v="50"/>
-    <m/>
-    <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
+    <n v="1"/>
+    <m/>
+    <m/>
+    <m/>
+    <n v="0.7142857142857143"/>
     <n v="115"/>
   </r>
   <r>
@@ -2039,7 +2039,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -2060,7 +2060,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -2081,7 +2081,7 @@
     <n v="0"/>
     <n v="1"/>
     <n v="50"/>
-    <m/>
+    <n v="0"/>
     <m/>
     <m/>
     <m/>
@@ -2092,7 +2092,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -2641,13 +2641,15 @@
       <c r="M3" s="17">
         <v>120</v>
       </c>
-      <c r="N3" s="17"/>
+      <c r="N3" s="17">
+        <v>1</v>
+      </c>
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
@@ -2694,13 +2696,15 @@
       <c r="M4" s="17">
         <v>120</v>
       </c>
-      <c r="N4" s="17"/>
+      <c r="N4" s="17">
+        <v>1</v>
+      </c>
       <c r="O4" s="17"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
@@ -2747,7 +2751,9 @@
       <c r="M5" s="17">
         <v>120</v>
       </c>
-      <c r="N5" s="17"/>
+      <c r="N5" s="17">
+        <v>0</v>
+      </c>
       <c r="O5" s="17"/>
       <c r="P5" s="17"/>
       <c r="Q5" s="17"/>
@@ -2800,13 +2806,15 @@
       <c r="M6" s="17">
         <v>120</v>
       </c>
-      <c r="N6" s="17"/>
+      <c r="N6" s="17">
+        <v>1</v>
+      </c>
       <c r="O6" s="17"/>
       <c r="P6" s="17"/>
       <c r="Q6" s="17"/>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
@@ -2853,13 +2861,15 @@
       <c r="M7" s="17">
         <v>120</v>
       </c>
-      <c r="N7" s="17"/>
+      <c r="N7" s="17">
+        <v>1</v>
+      </c>
       <c r="O7" s="17"/>
       <c r="P7" s="17"/>
       <c r="Q7" s="17"/>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
@@ -2906,13 +2916,15 @@
       <c r="M8" s="17">
         <v>120</v>
       </c>
-      <c r="N8" s="17"/>
+      <c r="N8" s="17">
+        <v>1</v>
+      </c>
       <c r="O8" s="17"/>
       <c r="P8" s="17"/>
       <c r="Q8" s="17"/>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
@@ -2959,13 +2971,15 @@
       <c r="M9" s="17">
         <v>120</v>
       </c>
-      <c r="N9" s="17"/>
+      <c r="N9" s="17">
+        <v>1</v>
+      </c>
       <c r="O9" s="17"/>
       <c r="P9" s="17"/>
       <c r="Q9" s="17"/>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
@@ -3012,13 +3026,15 @@
       <c r="M10" s="17">
         <v>120</v>
       </c>
-      <c r="N10" s="17"/>
+      <c r="N10" s="17">
+        <v>1</v>
+      </c>
       <c r="O10" s="17"/>
       <c r="P10" s="17"/>
       <c r="Q10" s="17"/>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
@@ -3065,7 +3081,9 @@
       <c r="M11" s="17">
         <v>-10</v>
       </c>
-      <c r="N11" s="17"/>
+      <c r="N11" s="17">
+        <v>0</v>
+      </c>
       <c r="O11" s="17"/>
       <c r="P11" s="17"/>
       <c r="Q11" s="17"/>
@@ -3118,7 +3136,9 @@
       <c r="M12" s="17">
         <v>-10</v>
       </c>
-      <c r="N12" s="17"/>
+      <c r="N12" s="17">
+        <v>0</v>
+      </c>
       <c r="O12" s="17"/>
       <c r="P12" s="17"/>
       <c r="Q12" s="17"/>
@@ -3171,7 +3191,9 @@
       <c r="M13" s="17">
         <v>-10</v>
       </c>
-      <c r="N13" s="17"/>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
       <c r="O13" s="17"/>
       <c r="P13" s="17"/>
       <c r="Q13" s="17"/>
@@ -3224,7 +3246,9 @@
       <c r="M14" s="17">
         <v>-10</v>
       </c>
-      <c r="N14" s="17"/>
+      <c r="N14" s="17">
+        <v>0</v>
+      </c>
       <c r="O14" s="17"/>
       <c r="P14" s="17"/>
       <c r="Q14" s="17"/>
@@ -3277,7 +3301,9 @@
       <c r="M15" s="17">
         <v>-10</v>
       </c>
-      <c r="N15" s="17"/>
+      <c r="N15" s="17">
+        <v>0</v>
+      </c>
       <c r="O15" s="17"/>
       <c r="P15" s="17"/>
       <c r="Q15" s="17"/>
@@ -3330,7 +3356,9 @@
       <c r="M16" s="17">
         <v>-10</v>
       </c>
-      <c r="N16" s="17"/>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
       <c r="O16" s="17"/>
       <c r="P16" s="17"/>
       <c r="Q16" s="17"/>
@@ -3383,7 +3411,9 @@
       <c r="M17" s="17">
         <v>-10</v>
       </c>
-      <c r="N17" s="17"/>
+      <c r="N17" s="17">
+        <v>0</v>
+      </c>
       <c r="O17" s="17"/>
       <c r="P17" s="17"/>
       <c r="Q17" s="17"/>
@@ -3436,13 +3466,15 @@
       <c r="M18" s="9">
         <v>40</v>
       </c>
-      <c r="N18" s="9"/>
+      <c r="N18" s="9">
+        <v>1</v>
+      </c>
       <c r="O18" s="9"/>
       <c r="P18" s="9"/>
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
@@ -3489,13 +3521,15 @@
       <c r="M19" s="9">
         <v>40</v>
       </c>
-      <c r="N19" s="9"/>
+      <c r="N19" s="9">
+        <v>1</v>
+      </c>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
@@ -3542,13 +3576,15 @@
       <c r="M20" s="9">
         <v>40</v>
       </c>
-      <c r="N20" s="9"/>
+      <c r="N20" s="9">
+        <v>1</v>
+      </c>
       <c r="O20" s="9"/>
       <c r="P20" s="9"/>
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="1"/>
@@ -3595,7 +3631,9 @@
       <c r="M21" s="9">
         <v>40</v>
       </c>
-      <c r="N21" s="9"/>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
@@ -3648,13 +3686,15 @@
       <c r="M22" s="9">
         <v>40</v>
       </c>
-      <c r="N22" s="9"/>
+      <c r="N22" s="9">
+        <v>1</v>
+      </c>
       <c r="O22" s="9"/>
       <c r="P22" s="9"/>
       <c r="Q22" s="9"/>
       <c r="R22" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S22" s="3">
         <f t="shared" si="1"/>
@@ -3701,13 +3741,15 @@
       <c r="M23" s="9">
         <v>40</v>
       </c>
-      <c r="N23" s="9"/>
+      <c r="N23" s="9">
+        <v>1</v>
+      </c>
       <c r="O23" s="9"/>
       <c r="P23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="1"/>
@@ -3754,13 +3796,15 @@
       <c r="M24" s="9">
         <v>40</v>
       </c>
-      <c r="N24" s="9"/>
+      <c r="N24" s="9">
+        <v>1</v>
+      </c>
       <c r="O24" s="9"/>
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S24" s="3">
         <f t="shared" si="1"/>
@@ -3807,13 +3851,15 @@
       <c r="M25" s="9">
         <v>40</v>
       </c>
-      <c r="N25" s="9"/>
+      <c r="N25" s="9">
+        <v>1</v>
+      </c>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="1"/>
@@ -3860,13 +3906,15 @@
       <c r="M26" s="9">
         <v>40</v>
       </c>
-      <c r="N26" s="9"/>
+      <c r="N26" s="9">
+        <v>1</v>
+      </c>
       <c r="O26" s="9"/>
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="1"/>
@@ -3913,13 +3961,15 @@
       <c r="M27" s="9">
         <v>40</v>
       </c>
-      <c r="N27" s="9"/>
+      <c r="N27" s="9">
+        <v>1</v>
+      </c>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="1"/>
@@ -3966,7 +4016,9 @@
       <c r="M28" s="9">
         <v>40</v>
       </c>
-      <c r="N28" s="9"/>
+      <c r="N28" s="9">
+        <v>0</v>
+      </c>
       <c r="O28" s="9"/>
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
@@ -4019,7 +4071,9 @@
       <c r="M29" s="9">
         <v>40</v>
       </c>
-      <c r="N29" s="9"/>
+      <c r="N29" s="9">
+        <v>0</v>
+      </c>
       <c r="O29" s="9"/>
       <c r="P29" s="9"/>
       <c r="Q29" s="9"/>
@@ -4072,7 +4126,9 @@
       <c r="M30" s="9">
         <v>40</v>
       </c>
-      <c r="N30" s="9"/>
+      <c r="N30" s="9">
+        <v>0</v>
+      </c>
       <c r="O30" s="9"/>
       <c r="P30" s="9"/>
       <c r="Q30" s="9"/>
@@ -4125,7 +4181,9 @@
       <c r="M31" s="9">
         <v>40</v>
       </c>
-      <c r="N31" s="9"/>
+      <c r="N31" s="9">
+        <v>0</v>
+      </c>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
@@ -4178,7 +4236,9 @@
       <c r="M32" s="9">
         <v>40</v>
       </c>
-      <c r="N32" s="9"/>
+      <c r="N32" s="9">
+        <v>0</v>
+      </c>
       <c r="O32" s="9"/>
       <c r="P32" s="9"/>
       <c r="Q32" s="9"/>
@@ -4231,7 +4291,9 @@
       <c r="M33" s="9">
         <v>40</v>
       </c>
-      <c r="N33" s="9"/>
+      <c r="N33" s="9">
+        <v>0</v>
+      </c>
       <c r="O33" s="9"/>
       <c r="P33" s="9"/>
       <c r="Q33" s="9"/>
@@ -4284,7 +4346,9 @@
       <c r="M34" s="9">
         <v>50</v>
       </c>
-      <c r="N34" s="9"/>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
       <c r="O34" s="9"/>
       <c r="P34" s="9"/>
       <c r="Q34" s="9"/>
@@ -4337,7 +4401,9 @@
       <c r="M35" s="9">
         <v>50</v>
       </c>
-      <c r="N35" s="9"/>
+      <c r="N35" s="9">
+        <v>0</v>
+      </c>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -4390,7 +4456,9 @@
       <c r="M36" s="9">
         <v>50</v>
       </c>
-      <c r="N36" s="9"/>
+      <c r="N36" s="9">
+        <v>0</v>
+      </c>
       <c r="O36" s="9"/>
       <c r="P36" s="9"/>
       <c r="Q36" s="9"/>
@@ -4443,7 +4511,9 @@
       <c r="M37" s="9">
         <v>50</v>
       </c>
-      <c r="N37" s="9"/>
+      <c r="N37" s="9">
+        <v>0</v>
+      </c>
       <c r="O37" s="9"/>
       <c r="P37" s="9"/>
       <c r="Q37" s="9"/>
@@ -4496,7 +4566,9 @@
       <c r="M38" s="9">
         <v>50</v>
       </c>
-      <c r="N38" s="9"/>
+      <c r="N38" s="9">
+        <v>0</v>
+      </c>
       <c r="O38" s="9"/>
       <c r="P38" s="9"/>
       <c r="Q38" s="9"/>
@@ -4549,7 +4621,9 @@
       <c r="M39" s="9">
         <v>50</v>
       </c>
-      <c r="N39" s="9"/>
+      <c r="N39" s="9">
+        <v>0</v>
+      </c>
       <c r="O39" s="9"/>
       <c r="P39" s="9"/>
       <c r="Q39" s="9"/>
@@ -4602,7 +4676,9 @@
       <c r="M40" s="9">
         <v>50</v>
       </c>
-      <c r="N40" s="9"/>
+      <c r="N40" s="9">
+        <v>0</v>
+      </c>
       <c r="O40" s="9"/>
       <c r="P40" s="9"/>
       <c r="Q40" s="9"/>
@@ -4655,7 +4731,9 @@
       <c r="M41" s="9">
         <v>50</v>
       </c>
-      <c r="N41" s="9"/>
+      <c r="N41" s="9">
+        <v>0</v>
+      </c>
       <c r="O41" s="9"/>
       <c r="P41" s="9"/>
       <c r="Q41" s="9"/>
@@ -4708,13 +4786,15 @@
       <c r="M42" s="9">
         <v>50</v>
       </c>
-      <c r="N42" s="9"/>
+      <c r="N42" s="9">
+        <v>1</v>
+      </c>
       <c r="O42" s="9"/>
       <c r="P42" s="9"/>
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S42" s="3">
         <f t="shared" si="3"/>
@@ -4761,7 +4841,9 @@
       <c r="M43" s="9">
         <v>50</v>
       </c>
-      <c r="N43" s="9"/>
+      <c r="N43" s="9">
+        <v>0</v>
+      </c>
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -4814,7 +4896,9 @@
       <c r="M44" s="17">
         <v>-10</v>
       </c>
-      <c r="N44" s="17"/>
+      <c r="N44" s="17">
+        <v>0</v>
+      </c>
       <c r="O44" s="17"/>
       <c r="P44" s="17"/>
       <c r="Q44" s="17"/>
@@ -4867,7 +4951,9 @@
       <c r="M45" s="17">
         <v>-10</v>
       </c>
-      <c r="N45" s="17"/>
+      <c r="N45" s="17">
+        <v>0</v>
+      </c>
       <c r="O45" s="17"/>
       <c r="P45" s="17"/>
       <c r="Q45" s="17"/>
@@ -4920,6 +5006,9 @@
       <c r="M46" s="17">
         <v>-10</v>
       </c>
+      <c r="N46" s="18">
+        <v>0</v>
+      </c>
       <c r="R46" s="4">
         <f t="shared" si="2"/>
         <v>0.2857142857142857</v>
@@ -4969,6 +5058,9 @@
       <c r="M47" s="17">
         <v>-10</v>
       </c>
+      <c r="N47" s="18">
+        <v>0</v>
+      </c>
       <c r="R47" s="4">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
@@ -5018,7 +5110,9 @@
       <c r="M48" s="13">
         <v>120</v>
       </c>
-      <c r="N48" s="13"/>
+      <c r="N48" s="13">
+        <v>0</v>
+      </c>
       <c r="O48" s="13"/>
       <c r="P48" s="13"/>
       <c r="Q48" s="13"/>
@@ -5071,13 +5165,15 @@
       <c r="M49" s="13">
         <v>120</v>
       </c>
-      <c r="N49" s="13"/>
+      <c r="N49" s="13">
+        <v>1</v>
+      </c>
       <c r="O49" s="13"/>
       <c r="P49" s="13"/>
       <c r="Q49" s="13"/>
       <c r="R49" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S49" s="12">
         <f t="shared" si="3"/>
@@ -5124,13 +5220,15 @@
       <c r="M50" s="13">
         <v>120</v>
       </c>
-      <c r="N50" s="13"/>
+      <c r="N50" s="13">
+        <v>1</v>
+      </c>
       <c r="O50" s="13"/>
       <c r="P50" s="13"/>
       <c r="Q50" s="13"/>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S50" s="12">
         <f t="shared" si="3"/>
@@ -5177,13 +5275,15 @@
       <c r="M51" s="13">
         <v>120</v>
       </c>
-      <c r="N51" s="13"/>
+      <c r="N51" s="13">
+        <v>1</v>
+      </c>
       <c r="O51" s="13"/>
       <c r="P51" s="13"/>
       <c r="Q51" s="13"/>
       <c r="R51" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S51" s="14">
         <f t="shared" si="3"/>
@@ -5230,13 +5330,15 @@
       <c r="M52" s="13">
         <v>120</v>
       </c>
-      <c r="N52" s="13"/>
+      <c r="N52" s="13">
+        <v>1</v>
+      </c>
       <c r="O52" s="13"/>
       <c r="P52" s="13"/>
       <c r="Q52" s="13"/>
       <c r="R52" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S52" s="14">
         <f t="shared" si="3"/>
@@ -5283,13 +5385,15 @@
       <c r="M53" s="13">
         <v>120</v>
       </c>
-      <c r="N53" s="13"/>
+      <c r="N53" s="13">
+        <v>1</v>
+      </c>
       <c r="O53" s="13"/>
       <c r="P53" s="13"/>
       <c r="Q53" s="13"/>
       <c r="R53" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S53" s="14">
         <f t="shared" si="3"/>
@@ -5336,13 +5440,15 @@
       <c r="M54" s="13">
         <v>120</v>
       </c>
-      <c r="N54" s="13"/>
+      <c r="N54" s="13">
+        <v>1</v>
+      </c>
       <c r="O54" s="13"/>
       <c r="P54" s="13"/>
       <c r="Q54" s="13"/>
       <c r="R54" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S54" s="14">
         <f t="shared" si="3"/>
@@ -5389,13 +5495,15 @@
       <c r="M55" s="13">
         <v>50</v>
       </c>
-      <c r="N55" s="13"/>
+      <c r="N55" s="13">
+        <v>1</v>
+      </c>
       <c r="O55" s="13"/>
       <c r="P55" s="13"/>
       <c r="Q55" s="13"/>
       <c r="R55" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S55" s="14">
         <f t="shared" si="3"/>
@@ -5442,13 +5550,15 @@
       <c r="M56" s="13">
         <v>50</v>
       </c>
-      <c r="N56" s="13"/>
+      <c r="N56" s="13">
+        <v>1</v>
+      </c>
       <c r="O56" s="13"/>
       <c r="P56" s="13"/>
       <c r="Q56" s="13"/>
       <c r="R56" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S56" s="14">
         <f t="shared" si="3"/>
@@ -5495,7 +5605,9 @@
       <c r="M57" s="13">
         <v>50</v>
       </c>
-      <c r="N57" s="13"/>
+      <c r="N57" s="13">
+        <v>0</v>
+      </c>
       <c r="O57" s="13"/>
       <c r="P57" s="13"/>
       <c r="Q57" s="13"/>
@@ -5548,13 +5660,15 @@
       <c r="M58" s="13">
         <v>50</v>
       </c>
-      <c r="N58" s="13"/>
+      <c r="N58" s="13">
+        <v>1</v>
+      </c>
       <c r="O58" s="13"/>
       <c r="P58" s="13"/>
       <c r="Q58" s="13"/>
       <c r="R58" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S58" s="14">
         <f t="shared" si="3"/>
@@ -5601,7 +5715,9 @@
       <c r="M59" s="13">
         <v>50</v>
       </c>
-      <c r="N59" s="13"/>
+      <c r="N59" s="13">
+        <v>0</v>
+      </c>
       <c r="O59" s="13"/>
       <c r="P59" s="13"/>
       <c r="Q59" s="13"/>
@@ -5654,13 +5770,15 @@
       <c r="M60" s="13">
         <v>50</v>
       </c>
-      <c r="N60" s="13"/>
+      <c r="N60" s="13">
+        <v>1</v>
+      </c>
       <c r="O60" s="13"/>
       <c r="P60" s="13"/>
       <c r="Q60" s="13"/>
       <c r="R60" s="16">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S60" s="14">
         <f t="shared" si="3"/>
@@ -5707,7 +5825,9 @@
       <c r="M61" s="13">
         <v>50</v>
       </c>
-      <c r="N61" s="13"/>
+      <c r="N61" s="13">
+        <v>0</v>
+      </c>
       <c r="O61" s="13"/>
       <c r="P61" s="13"/>
       <c r="Q61" s="13"/>
@@ -5760,7 +5880,9 @@
       <c r="M62" s="13">
         <v>50</v>
       </c>
-      <c r="N62" s="13"/>
+      <c r="N62" s="13">
+        <v>0</v>
+      </c>
       <c r="O62" s="13"/>
       <c r="P62" s="13"/>
       <c r="Q62" s="13"/>
@@ -5813,7 +5935,9 @@
       <c r="M63" s="13">
         <v>50</v>
       </c>
-      <c r="N63" s="13"/>
+      <c r="N63" s="13">
+        <v>0</v>
+      </c>
       <c r="O63" s="13"/>
       <c r="P63" s="13"/>
       <c r="Q63" s="13"/>
@@ -5866,13 +5990,15 @@
       <c r="M64" s="13">
         <v>50</v>
       </c>
-      <c r="N64" s="13"/>
+      <c r="N64" s="13">
+        <v>1</v>
+      </c>
       <c r="O64" s="13"/>
       <c r="P64" s="13"/>
       <c r="Q64" s="13"/>
       <c r="R64" s="16">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S64" s="14">
         <f t="shared" si="3"/>
@@ -5930,7 +6056,7 @@
         <v>270</v>
       </c>
       <c r="C4" s="7">
-        <v>0.65306122448979587</v>
+        <v>0.77551020408163251</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5941,7 +6067,7 @@
         <v>265</v>
       </c>
       <c r="C5" s="7">
-        <v>0.6071428571428571</v>
+        <v>0.7321428571428571</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5952,7 +6078,7 @@
         <v>255</v>
       </c>
       <c r="C6" s="7">
-        <v>0.62857142857142845</v>
+        <v>0.75714285714285712</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -5974,7 +6100,7 @@
         <v>115</v>
       </c>
       <c r="C8" s="7">
-        <v>0.61904761904761907</v>
+        <v>0.68253968253968256</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -5985,7 +6111,7 @@
         <v>100</v>
       </c>
       <c r="C9" s="7">
-        <v>0.54285714285714282</v>
+        <v>0.55714285714285705</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -6018,7 +6144,7 @@
         <v>166.47540983606558</v>
       </c>
       <c r="C12" s="7">
-        <v>0.57611241217798592</v>
+        <v>0.63934426229508201</v>
       </c>
     </row>
   </sheetData>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD3B1EF-1720-A24B-80CB-59ECA45D892B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548A4DC6-C2DE-9841-A06A-19568529F19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId3"/>
+    <pivotCache cacheId="12" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -725,7 +725,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46141.659967361113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46150.72872939815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -782,19 +782,19 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L6 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-15" maxValue="130"/>
     </cacheField>
     <cacheField name="L7 Presenza" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L7 XP" numFmtId="0">
       <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="0.8571428571428571"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="1"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="35" maxValue="270"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="25" maxValue="395"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -822,11 +822,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="265"/>
+    <n v="1"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -843,11 +843,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="265"/>
+    <n v="0.8571428571428571"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -864,11 +864,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="0"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="265"/>
+    <n v="0.8571428571428571"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -885,11 +885,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="265"/>
+    <n v="1"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -906,11 +906,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="265"/>
+    <n v="0.7142857142857143"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -927,11 +927,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="265"/>
+    <n v="1"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -948,11 +948,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="265"/>
+    <n v="1"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Castiglia"/>
@@ -969,11 +969,11 @@
     <n v="0"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="130"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="265"/>
+    <n v="0.5714285714285714"/>
+    <n v="395"/>
   </r>
   <r>
     <s v="Cuomo"/>
@@ -990,11 +990,11 @@
     <n v="0"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Ercolano"/>
@@ -1011,11 +1011,11 @@
     <n v="0"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Forte"/>
@@ -1032,11 +1032,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1053,11 +1053,11 @@
     <n v="0"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Paone"/>
@@ -1074,11 +1074,11 @@
     <n v="0"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Petrone"/>
@@ -1095,11 +1095,11 @@
     <n v="0"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.2857142857142857"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Preteverde"/>
@@ -1116,11 +1116,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="40"/>
+    <n v="25"/>
   </r>
   <r>
     <s v="Baudrand"/>
@@ -1137,11 +1137,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="255"/>
+    <n v="1"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Borreca"/>
@@ -1158,11 +1158,11 @@
     <n v="0"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="255"/>
+    <n v="0.8571428571428571"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Borrione"/>
@@ -1179,11 +1179,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="255"/>
+    <n v="1"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Cappelluccio"/>
@@ -1200,11 +1200,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="255"/>
+    <n v="0.8571428571428571"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Casale"/>
@@ -1221,11 +1221,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="255"/>
+    <n v="0.8571428571428571"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Marrazzo"/>
@@ -1242,11 +1242,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="255"/>
+    <n v="0.7142857142857143"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Miles"/>
@@ -1263,11 +1263,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="255"/>
+    <n v="1"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Parente"/>
@@ -1284,11 +1284,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="255"/>
+    <n v="0.8571428571428571"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Pietropaolo"/>
@@ -1305,11 +1305,11 @@
     <n v="0"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="255"/>
+    <n v="0.8571428571428571"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Rispoli"/>
@@ -1326,11 +1326,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="255"/>
+    <n v="1"/>
+    <n v="285"/>
   </r>
   <r>
     <s v="Maione"/>
@@ -1347,11 +1347,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Nasti"/>
@@ -1368,11 +1368,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Noviello"/>
@@ -1389,11 +1389,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Pepe"/>
@@ -1410,11 +1410,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.7142857142857143"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Tartaro"/>
@@ -1431,11 +1431,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.42857142857142855"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Versi"/>
@@ -1452,11 +1452,11 @@
     <n v="1"/>
     <n v="40"/>
     <n v="0"/>
-    <m/>
-    <m/>
+    <n v="-15"/>
+    <n v="0"/>
     <m/>
     <n v="0.5714285714285714"/>
-    <n v="190"/>
+    <n v="175"/>
   </r>
   <r>
     <s v="Borrelli"/>
@@ -1473,11 +1473,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="100"/>
+    <n v="0.5714285714285714"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Canzolino"/>
@@ -1494,11 +1494,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="100"/>
+    <n v="0.8571428571428571"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="De Siena"/>
@@ -1515,11 +1515,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="100"/>
+    <n v="0.8571428571428571"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Di Meglio"/>
@@ -1536,11 +1536,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="100"/>
+    <n v="0.8571428571428571"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Esposito"/>
@@ -1557,11 +1557,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="100"/>
+    <n v="0.5714285714285714"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Ferrante"/>
@@ -1578,11 +1578,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="100"/>
+    <n v="0.7142857142857143"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Maglietta"/>
@@ -1599,11 +1599,11 @@
     <n v="0"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="100"/>
+    <n v="0.5714285714285714"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Patroni Griffi"/>
@@ -1620,11 +1620,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="100"/>
+    <n v="0.8571428571428571"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Semioli"/>
@@ -1641,11 +1641,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="100"/>
+    <n v="0.7142857142857143"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Siano"/>
@@ -1662,11 +1662,11 @@
     <n v="0"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <n v="100"/>
+    <n v="0.42857142857142855"/>
+    <n v="130"/>
   </r>
   <r>
     <s v="Agliottone"/>
@@ -1683,11 +1683,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="35"/>
+    <n v="0.5714285714285714"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1704,11 +1704,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="35"/>
+    <n v="0.5714285714285714"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Imperatore"/>
@@ -1725,11 +1725,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.2857142857142857"/>
-    <n v="35"/>
+    <n v="0.42857142857142855"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Monaco"/>
@@ -1746,11 +1746,11 @@
     <n v="1"/>
     <n v="-10"/>
     <n v="0"/>
+    <n v="30"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="35"/>
+    <n v="0.5714285714285714"/>
+    <n v="65"/>
   </r>
   <r>
     <s v="Cerundolo"/>
@@ -1767,11 +1767,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="270"/>
+    <n v="0.7142857142857143"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Chieti"/>
@@ -1788,11 +1788,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="270"/>
+    <n v="1"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Coda"/>
@@ -1809,11 +1809,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="270"/>
+    <n v="1"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Dibartolomeo"/>
@@ -1830,11 +1830,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="270"/>
+    <n v="1"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Raduazzo"/>
@@ -1851,11 +1851,11 @@
     <n v="0"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.5714285714285714"/>
-    <n v="270"/>
+    <n v="0.7142857142857143"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Vable"/>
@@ -1872,11 +1872,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="270"/>
+    <n v="1"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Zito"/>
@@ -1893,11 +1893,11 @@
     <n v="1"/>
     <n v="120"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="270"/>
+    <n v="1"/>
+    <n v="370"/>
   </r>
   <r>
     <s v="Antico"/>
@@ -1914,11 +1914,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="115"/>
+    <n v="1"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="D'Acunto"/>
@@ -1935,11 +1935,11 @@
     <n v="0"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="115"/>
+    <n v="0.5714285714285714"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Di Fiore"/>
@@ -1956,11 +1956,11 @@
     <n v="0"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.42857142857142855"/>
-    <n v="115"/>
+    <n v="0.5714285714285714"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Ditri"/>
@@ -1977,11 +1977,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.8571428571428571"/>
-    <n v="115"/>
+    <n v="1"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Fraddanno"/>
@@ -1998,11 +1998,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="115"/>
+    <n v="0.8571428571428571"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Marciello"/>
@@ -2019,11 +2019,11 @@
     <n v="0"/>
     <n v="50"/>
     <n v="1"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="115"/>
+    <n v="0.8571428571428571"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Miranda"/>
@@ -2040,11 +2040,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="115"/>
+    <n v="0.8571428571428571"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Rolletta"/>
@@ -2061,11 +2061,11 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="115"/>
+    <n v="0.8571428571428571"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Soriano"/>
@@ -2082,17 +2082,17 @@
     <n v="1"/>
     <n v="50"/>
     <n v="0"/>
+    <n v="100"/>
+    <n v="1"/>
     <m/>
-    <m/>
-    <m/>
-    <n v="0.7142857142857143"/>
-    <n v="115"/>
+    <n v="0.8571428571428571"/>
+    <n v="215"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -2141,28 +2141,28 @@
   </rowFields>
   <rowItems count="9">
     <i>
-      <x v="6"/>
+      <x/>
     </i>
     <i>
-      <x/>
+      <x v="6"/>
     </i>
     <i>
       <x v="2"/>
     </i>
     <i>
-      <x v="3"/>
+      <x v="7"/>
     </i>
     <i>
-      <x v="7"/>
+      <x v="3"/>
     </i>
     <i>
       <x v="4"/>
     </i>
     <i>
-      <x v="1"/>
+      <x v="5"/>
     </i>
     <i>
-      <x v="5"/>
+      <x v="1"/>
     </i>
     <i t="grand">
       <x/>
@@ -2644,16 +2644,20 @@
       <c r="N3" s="17">
         <v>1</v>
       </c>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
+      <c r="O3" s="17">
+        <v>130</v>
+      </c>
+      <c r="P3" s="17">
+        <v>1</v>
+      </c>
       <c r="Q3" s="17"/>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2699,16 +2703,20 @@
       <c r="N4" s="17">
         <v>1</v>
       </c>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
+      <c r="O4" s="17">
+        <v>130</v>
+      </c>
+      <c r="P4" s="17">
+        <v>1</v>
+      </c>
       <c r="Q4" s="17"/>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2754,16 +2762,20 @@
       <c r="N5" s="17">
         <v>0</v>
       </c>
-      <c r="O5" s="17"/>
-      <c r="P5" s="17"/>
+      <c r="O5" s="17">
+        <v>130</v>
+      </c>
+      <c r="P5" s="17">
+        <v>1</v>
+      </c>
       <c r="Q5" s="17"/>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2809,16 +2821,20 @@
       <c r="N6" s="17">
         <v>1</v>
       </c>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
+      <c r="O6" s="17">
+        <v>130</v>
+      </c>
+      <c r="P6" s="17">
+        <v>1</v>
+      </c>
       <c r="Q6" s="17"/>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2864,16 +2880,20 @@
       <c r="N7" s="17">
         <v>1</v>
       </c>
-      <c r="O7" s="17"/>
-      <c r="P7" s="17"/>
+      <c r="O7" s="17">
+        <v>130</v>
+      </c>
+      <c r="P7" s="17">
+        <v>1</v>
+      </c>
       <c r="Q7" s="17"/>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2919,16 +2939,20 @@
       <c r="N8" s="17">
         <v>1</v>
       </c>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
+      <c r="O8" s="17">
+        <v>130</v>
+      </c>
+      <c r="P8" s="17">
+        <v>1</v>
+      </c>
       <c r="Q8" s="17"/>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -2974,16 +2998,20 @@
       <c r="N9" s="17">
         <v>1</v>
       </c>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
+      <c r="O9" s="17">
+        <v>130</v>
+      </c>
+      <c r="P9" s="17">
+        <v>1</v>
+      </c>
       <c r="Q9" s="17"/>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -3029,16 +3057,20 @@
       <c r="N10" s="17">
         <v>1</v>
       </c>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
+      <c r="O10" s="17">
+        <v>130</v>
+      </c>
+      <c r="P10" s="17">
+        <v>1</v>
+      </c>
       <c r="Q10" s="17"/>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -3084,8 +3116,12 @@
       <c r="N11" s="17">
         <v>0</v>
       </c>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
+      <c r="O11" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P11" s="17">
+        <v>0</v>
+      </c>
       <c r="Q11" s="17"/>
       <c r="R11" s="4">
         <f t="shared" si="0"/>
@@ -3093,7 +3129,7 @@
       </c>
       <c r="S11" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
@@ -3139,8 +3175,12 @@
       <c r="N12" s="17">
         <v>0</v>
       </c>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
+      <c r="O12" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P12" s="17">
+        <v>0</v>
+      </c>
       <c r="Q12" s="17"/>
       <c r="R12" s="4">
         <f t="shared" si="0"/>
@@ -3148,7 +3188,7 @@
       </c>
       <c r="S12" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
@@ -3194,8 +3234,12 @@
       <c r="N13" s="17">
         <v>0</v>
       </c>
-      <c r="O13" s="17"/>
-      <c r="P13" s="17"/>
+      <c r="O13" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
       <c r="Q13" s="17"/>
       <c r="R13" s="4">
         <f t="shared" si="0"/>
@@ -3203,7 +3247,7 @@
       </c>
       <c r="S13" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.2">
@@ -3249,8 +3293,12 @@
       <c r="N14" s="17">
         <v>0</v>
       </c>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
+      <c r="O14" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P14" s="17">
+        <v>0</v>
+      </c>
       <c r="Q14" s="17"/>
       <c r="R14" s="4">
         <f t="shared" si="0"/>
@@ -3258,7 +3306,7 @@
       </c>
       <c r="S14" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
@@ -3304,8 +3352,12 @@
       <c r="N15" s="17">
         <v>0</v>
       </c>
-      <c r="O15" s="17"/>
-      <c r="P15" s="17"/>
+      <c r="O15" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P15" s="17">
+        <v>0</v>
+      </c>
       <c r="Q15" s="17"/>
       <c r="R15" s="4">
         <f t="shared" si="0"/>
@@ -3313,7 +3365,7 @@
       </c>
       <c r="S15" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
@@ -3359,8 +3411,12 @@
       <c r="N16" s="17">
         <v>0</v>
       </c>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
+      <c r="O16" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
       <c r="Q16" s="17"/>
       <c r="R16" s="4">
         <f t="shared" si="0"/>
@@ -3368,7 +3424,7 @@
       </c>
       <c r="S16" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
@@ -3414,8 +3470,12 @@
       <c r="N17" s="17">
         <v>0</v>
       </c>
-      <c r="O17" s="17"/>
-      <c r="P17" s="17"/>
+      <c r="O17" s="17">
+        <v>-15</v>
+      </c>
+      <c r="P17" s="17">
+        <v>0</v>
+      </c>
       <c r="Q17" s="17"/>
       <c r="R17" s="4">
         <f t="shared" si="0"/>
@@ -3423,7 +3483,7 @@
       </c>
       <c r="S17" s="3">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
@@ -3469,16 +3529,20 @@
       <c r="N18" s="9">
         <v>1</v>
       </c>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
+      <c r="O18" s="9">
+        <v>30</v>
+      </c>
+      <c r="P18" s="17">
+        <v>1</v>
+      </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -3524,16 +3588,20 @@
       <c r="N19" s="9">
         <v>1</v>
       </c>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
+      <c r="O19" s="9">
+        <v>30</v>
+      </c>
+      <c r="P19" s="17">
+        <v>1</v>
+      </c>
       <c r="Q19" s="9"/>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -3579,16 +3647,20 @@
       <c r="N20" s="9">
         <v>1</v>
       </c>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
+      <c r="O20" s="9">
+        <v>30</v>
+      </c>
+      <c r="P20" s="17">
+        <v>1</v>
+      </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -3634,16 +3706,20 @@
       <c r="N21" s="9">
         <v>0</v>
       </c>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
+      <c r="O21" s="9">
+        <v>30</v>
+      </c>
+      <c r="P21" s="17">
+        <v>1</v>
+      </c>
       <c r="Q21" s="9"/>
       <c r="R21" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S21" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -3689,16 +3765,20 @@
       <c r="N22" s="9">
         <v>1</v>
       </c>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
+      <c r="O22" s="9">
+        <v>30</v>
+      </c>
+      <c r="P22" s="17">
+        <v>1</v>
+      </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S22" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -3744,16 +3824,20 @@
       <c r="N23" s="9">
         <v>1</v>
       </c>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
+      <c r="O23" s="9">
+        <v>30</v>
+      </c>
+      <c r="P23" s="17">
+        <v>1</v>
+      </c>
       <c r="Q23" s="9"/>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -3799,16 +3883,20 @@
       <c r="N24" s="9">
         <v>1</v>
       </c>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
+      <c r="O24" s="9">
+        <v>30</v>
+      </c>
+      <c r="P24" s="17">
+        <v>1</v>
+      </c>
       <c r="Q24" s="9"/>
       <c r="R24" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S24" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -3854,16 +3942,20 @@
       <c r="N25" s="9">
         <v>1</v>
       </c>
-      <c r="O25" s="9"/>
-      <c r="P25" s="9"/>
+      <c r="O25" s="9">
+        <v>30</v>
+      </c>
+      <c r="P25" s="17">
+        <v>1</v>
+      </c>
       <c r="Q25" s="9"/>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -3909,16 +4001,20 @@
       <c r="N26" s="9">
         <v>1</v>
       </c>
-      <c r="O26" s="9"/>
-      <c r="P26" s="9"/>
+      <c r="O26" s="9">
+        <v>30</v>
+      </c>
+      <c r="P26" s="17">
+        <v>1</v>
+      </c>
       <c r="Q26" s="9"/>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -3964,16 +4060,20 @@
       <c r="N27" s="9">
         <v>1</v>
       </c>
-      <c r="O27" s="9"/>
-      <c r="P27" s="9"/>
+      <c r="O27" s="9">
+        <v>30</v>
+      </c>
+      <c r="P27" s="17">
+        <v>1</v>
+      </c>
       <c r="Q27" s="9"/>
       <c r="R27" s="4">
         <f t="shared" si="0"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -4019,8 +4119,12 @@
       <c r="N28" s="9">
         <v>0</v>
       </c>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
+      <c r="O28" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P28" s="17">
+        <v>0</v>
+      </c>
       <c r="Q28" s="9"/>
       <c r="R28" s="4">
         <f t="shared" si="0"/>
@@ -4028,7 +4132,7 @@
       </c>
       <c r="S28" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.2">
@@ -4074,8 +4178,12 @@
       <c r="N29" s="9">
         <v>0</v>
       </c>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
+      <c r="O29" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P29" s="17">
+        <v>0</v>
+      </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="4">
         <f t="shared" si="0"/>
@@ -4083,7 +4191,7 @@
       </c>
       <c r="S29" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.2">
@@ -4129,8 +4237,12 @@
       <c r="N30" s="9">
         <v>0</v>
       </c>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
+      <c r="O30" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P30" s="17">
+        <v>0</v>
+      </c>
       <c r="Q30" s="9"/>
       <c r="R30" s="4">
         <f t="shared" si="0"/>
@@ -4138,7 +4250,7 @@
       </c>
       <c r="S30" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.2">
@@ -4184,8 +4296,12 @@
       <c r="N31" s="9">
         <v>0</v>
       </c>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
+      <c r="O31" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P31" s="17">
+        <v>0</v>
+      </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="4">
         <f t="shared" si="0"/>
@@ -4193,7 +4309,7 @@
       </c>
       <c r="S31" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.2">
@@ -4239,8 +4355,12 @@
       <c r="N32" s="9">
         <v>0</v>
       </c>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
+      <c r="O32" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P32" s="17">
+        <v>0</v>
+      </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="4">
         <f t="shared" si="0"/>
@@ -4248,7 +4368,7 @@
       </c>
       <c r="S32" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.2">
@@ -4294,8 +4414,12 @@
       <c r="N33" s="9">
         <v>0</v>
       </c>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
+      <c r="O33" s="9">
+        <v>-15</v>
+      </c>
+      <c r="P33" s="17">
+        <v>0</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="4">
         <f t="shared" si="0"/>
@@ -4303,7 +4427,7 @@
       </c>
       <c r="S33" s="3">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.2">
@@ -4349,16 +4473,20 @@
       <c r="N34" s="9">
         <v>0</v>
       </c>
-      <c r="O34" s="9"/>
-      <c r="P34" s="9"/>
+      <c r="O34" s="9">
+        <v>30</v>
+      </c>
+      <c r="P34" s="17">
+        <v>1</v>
+      </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="4">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S34" s="3">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -4404,16 +4532,20 @@
       <c r="N35" s="9">
         <v>0</v>
       </c>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
+      <c r="O35" s="9">
+        <v>30</v>
+      </c>
+      <c r="P35" s="17">
+        <v>1</v>
+      </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="4">
         <f t="shared" ref="R35:R64" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S35" s="3">
         <f t="shared" ref="S35:S64" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -4459,16 +4591,20 @@
       <c r="N36" s="9">
         <v>0</v>
       </c>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
+      <c r="O36" s="9">
+        <v>30</v>
+      </c>
+      <c r="P36" s="17">
+        <v>1</v>
+      </c>
       <c r="Q36" s="9"/>
       <c r="R36" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S36" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -4514,16 +4650,20 @@
       <c r="N37" s="9">
         <v>0</v>
       </c>
-      <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
+      <c r="O37" s="9">
+        <v>30</v>
+      </c>
+      <c r="P37" s="17">
+        <v>1</v>
+      </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S37" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -4569,16 +4709,20 @@
       <c r="N38" s="9">
         <v>0</v>
       </c>
-      <c r="O38" s="9"/>
-      <c r="P38" s="9"/>
+      <c r="O38" s="9">
+        <v>30</v>
+      </c>
+      <c r="P38" s="17">
+        <v>1</v>
+      </c>
       <c r="Q38" s="9"/>
       <c r="R38" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S38" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -4624,16 +4768,20 @@
       <c r="N39" s="9">
         <v>0</v>
       </c>
-      <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
+      <c r="O39" s="9">
+        <v>30</v>
+      </c>
+      <c r="P39" s="17">
+        <v>1</v>
+      </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="4">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S39" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -4679,16 +4827,20 @@
       <c r="N40" s="9">
         <v>0</v>
       </c>
-      <c r="O40" s="9"/>
-      <c r="P40" s="9"/>
+      <c r="O40" s="9">
+        <v>30</v>
+      </c>
+      <c r="P40" s="17">
+        <v>1</v>
+      </c>
       <c r="Q40" s="9"/>
       <c r="R40" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S40" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -4734,16 +4886,20 @@
       <c r="N41" s="9">
         <v>0</v>
       </c>
-      <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
+      <c r="O41" s="9">
+        <v>30</v>
+      </c>
+      <c r="P41" s="17">
+        <v>1</v>
+      </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S41" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
@@ -4789,16 +4945,20 @@
       <c r="N42" s="9">
         <v>1</v>
       </c>
-      <c r="O42" s="9"/>
-      <c r="P42" s="9"/>
+      <c r="O42" s="9">
+        <v>30</v>
+      </c>
+      <c r="P42" s="17">
+        <v>1</v>
+      </c>
       <c r="Q42" s="9"/>
       <c r="R42" s="4">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S42" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
@@ -4844,16 +5004,20 @@
       <c r="N43" s="9">
         <v>0</v>
       </c>
-      <c r="O43" s="9"/>
-      <c r="P43" s="9"/>
+      <c r="O43" s="9">
+        <v>30</v>
+      </c>
+      <c r="P43" s="17">
+        <v>1</v>
+      </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S43" s="3">
         <f t="shared" si="3"/>
-        <v>100</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
@@ -4899,16 +5063,20 @@
       <c r="N44" s="17">
         <v>0</v>
       </c>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
+      <c r="O44" s="9">
+        <v>30</v>
+      </c>
+      <c r="P44" s="17">
+        <v>1</v>
+      </c>
       <c r="Q44" s="17"/>
       <c r="R44" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S44" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
@@ -4954,16 +5122,20 @@
       <c r="N45" s="17">
         <v>0</v>
       </c>
-      <c r="O45" s="17"/>
-      <c r="P45" s="17"/>
+      <c r="O45" s="9">
+        <v>30</v>
+      </c>
+      <c r="P45" s="17">
+        <v>1</v>
+      </c>
       <c r="Q45" s="17"/>
       <c r="R45" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S45" s="3">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -5009,13 +5181,19 @@
       <c r="N46" s="18">
         <v>0</v>
       </c>
+      <c r="O46" s="9">
+        <v>30</v>
+      </c>
+      <c r="P46" s="17">
+        <v>1</v>
+      </c>
       <c r="R46" s="4">
         <f t="shared" si="2"/>
-        <v>0.2857142857142857</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -5061,13 +5239,19 @@
       <c r="N47" s="18">
         <v>0</v>
       </c>
+      <c r="O47" s="9">
+        <v>30</v>
+      </c>
+      <c r="P47" s="17">
+        <v>1</v>
+      </c>
       <c r="R47" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S47" s="12">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
@@ -5113,16 +5297,20 @@
       <c r="N48" s="13">
         <v>0</v>
       </c>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13"/>
+      <c r="O48" s="9">
+        <v>100</v>
+      </c>
+      <c r="P48" s="17">
+        <v>1</v>
+      </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="4">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S48" s="12">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
@@ -5168,16 +5356,20 @@
       <c r="N49" s="13">
         <v>1</v>
       </c>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
+      <c r="O49" s="9">
+        <v>100</v>
+      </c>
+      <c r="P49" s="17">
+        <v>1</v>
+      </c>
       <c r="Q49" s="13"/>
       <c r="R49" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S49" s="12">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
@@ -5223,16 +5415,20 @@
       <c r="N50" s="13">
         <v>1</v>
       </c>
-      <c r="O50" s="13"/>
-      <c r="P50" s="13"/>
+      <c r="O50" s="9">
+        <v>100</v>
+      </c>
+      <c r="P50" s="17">
+        <v>1</v>
+      </c>
       <c r="Q50" s="13"/>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S50" s="12">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
@@ -5278,16 +5474,20 @@
       <c r="N51" s="13">
         <v>1</v>
       </c>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
+      <c r="O51" s="9">
+        <v>100</v>
+      </c>
+      <c r="P51" s="17">
+        <v>1</v>
+      </c>
       <c r="Q51" s="13"/>
       <c r="R51" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S51" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -5333,16 +5533,20 @@
       <c r="N52" s="13">
         <v>1</v>
       </c>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
+      <c r="O52" s="9">
+        <v>100</v>
+      </c>
+      <c r="P52" s="17">
+        <v>1</v>
+      </c>
       <c r="Q52" s="13"/>
       <c r="R52" s="4">
         <f t="shared" si="2"/>
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="S52" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -5388,16 +5592,20 @@
       <c r="N53" s="13">
         <v>1</v>
       </c>
-      <c r="O53" s="13"/>
-      <c r="P53" s="13"/>
+      <c r="O53" s="9">
+        <v>100</v>
+      </c>
+      <c r="P53" s="17">
+        <v>1</v>
+      </c>
       <c r="Q53" s="13"/>
       <c r="R53" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S53" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -5443,16 +5651,20 @@
       <c r="N54" s="13">
         <v>1</v>
       </c>
-      <c r="O54" s="13"/>
-      <c r="P54" s="13"/>
+      <c r="O54" s="9">
+        <v>100</v>
+      </c>
+      <c r="P54" s="17">
+        <v>1</v>
+      </c>
       <c r="Q54" s="13"/>
       <c r="R54" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S54" s="14">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
@@ -5498,16 +5710,20 @@
       <c r="N55" s="13">
         <v>1</v>
       </c>
-      <c r="O55" s="13"/>
-      <c r="P55" s="13"/>
+      <c r="O55" s="9">
+        <v>100</v>
+      </c>
+      <c r="P55" s="17">
+        <v>1</v>
+      </c>
       <c r="Q55" s="13"/>
       <c r="R55" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S55" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -5553,16 +5769,20 @@
       <c r="N56" s="13">
         <v>1</v>
       </c>
-      <c r="O56" s="13"/>
-      <c r="P56" s="13"/>
+      <c r="O56" s="9">
+        <v>100</v>
+      </c>
+      <c r="P56" s="17">
+        <v>1</v>
+      </c>
       <c r="Q56" s="13"/>
       <c r="R56" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S56" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
@@ -5608,16 +5828,20 @@
       <c r="N57" s="13">
         <v>0</v>
       </c>
-      <c r="O57" s="13"/>
-      <c r="P57" s="13"/>
+      <c r="O57" s="9">
+        <v>100</v>
+      </c>
+      <c r="P57" s="17">
+        <v>1</v>
+      </c>
       <c r="Q57" s="13"/>
       <c r="R57" s="4">
         <f t="shared" si="2"/>
-        <v>0.42857142857142855</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="S57" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
@@ -5663,16 +5887,20 @@
       <c r="N58" s="13">
         <v>1</v>
       </c>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13"/>
+      <c r="O58" s="9">
+        <v>100</v>
+      </c>
+      <c r="P58" s="17">
+        <v>1</v>
+      </c>
       <c r="Q58" s="13"/>
       <c r="R58" s="4">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="S58" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
@@ -5718,16 +5946,20 @@
       <c r="N59" s="13">
         <v>0</v>
       </c>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13"/>
+      <c r="O59" s="9">
+        <v>100</v>
+      </c>
+      <c r="P59" s="17">
+        <v>1</v>
+      </c>
       <c r="Q59" s="13"/>
       <c r="R59" s="4">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S59" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
@@ -5773,16 +6005,20 @@
       <c r="N60" s="13">
         <v>1</v>
       </c>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13"/>
+      <c r="O60" s="9">
+        <v>100</v>
+      </c>
+      <c r="P60" s="17">
+        <v>1</v>
+      </c>
       <c r="Q60" s="13"/>
       <c r="R60" s="16">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S60" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
@@ -5828,16 +6064,20 @@
       <c r="N61" s="13">
         <v>0</v>
       </c>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13"/>
+      <c r="O61" s="9">
+        <v>100</v>
+      </c>
+      <c r="P61" s="17">
+        <v>1</v>
+      </c>
       <c r="Q61" s="13"/>
       <c r="R61" s="16">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S61" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">
@@ -5883,16 +6123,20 @@
       <c r="N62" s="13">
         <v>0</v>
       </c>
-      <c r="O62" s="13"/>
-      <c r="P62" s="13"/>
+      <c r="O62" s="9">
+        <v>100</v>
+      </c>
+      <c r="P62" s="17">
+        <v>1</v>
+      </c>
       <c r="Q62" s="13"/>
       <c r="R62" s="16">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S62" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
@@ -5938,16 +6182,20 @@
       <c r="N63" s="13">
         <v>0</v>
       </c>
-      <c r="O63" s="13"/>
-      <c r="P63" s="13"/>
+      <c r="O63" s="9">
+        <v>100</v>
+      </c>
+      <c r="P63" s="17">
+        <v>1</v>
+      </c>
       <c r="Q63" s="13"/>
       <c r="R63" s="16">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S63" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.2">
@@ -5993,16 +6241,20 @@
       <c r="N64" s="13">
         <v>1</v>
       </c>
-      <c r="O64" s="13"/>
-      <c r="P64" s="13"/>
+      <c r="O64" s="9">
+        <v>100</v>
+      </c>
+      <c r="P64" s="17">
+        <v>1</v>
+      </c>
       <c r="Q64" s="13"/>
       <c r="R64" s="16">
         <f t="shared" si="2"/>
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="S64" s="14">
         <f t="shared" si="3"/>
-        <v>115</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -6050,24 +6302,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B4" s="26">
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="C4" s="7">
-        <v>0.77551020408163251</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B5" s="26">
-        <v>265</v>
+        <v>370</v>
       </c>
       <c r="C5" s="7">
-        <v>0.7321428571428571</v>
+        <v>0.91836734693877553</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -6075,32 +6327,32 @@
         <v>31</v>
       </c>
       <c r="B6" s="26">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C6" s="7">
-        <v>0.75714285714285712</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B7" s="26">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="C7" s="7">
-        <v>0.57142857142857129</v>
+        <v>0.82539682539682524</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="B8" s="26">
-        <v>115</v>
+        <v>175</v>
       </c>
       <c r="C8" s="7">
-        <v>0.68253968253968256</v>
+        <v>0.57142857142857129</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -6108,32 +6360,32 @@
         <v>36</v>
       </c>
       <c r="B9" s="26">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7">
-        <v>0.55714285714285705</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B10" s="26">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C10" s="7">
-        <v>0.48979591836734698</v>
+        <v>0.5357142857142857</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B11" s="26">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C11" s="7">
-        <v>0.39285714285714285</v>
+        <v>0.48979591836734698</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -6141,10 +6393,10 @@
         <v>117</v>
       </c>
       <c r="B12" s="26">
-        <v>166.47540983606558</v>
+        <v>218.36065573770492</v>
       </c>
       <c r="C12" s="7">
-        <v>0.63934426229508201</v>
+        <v>0.75175644028103039</v>
       </c>
     </row>
   </sheetData>

--- a/mondaylab/26_registro.xlsx
+++ b/mondaylab/26_registro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/giovanbattistacalifano/Documents/Lavoro/Varie/gibi/mondaylab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{548A4DC6-C2DE-9841-A06A-19568529F19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D85335-8263-2D4D-A45C-A8416E806D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId3"/>
+    <pivotCache cacheId="8" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -725,7 +725,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46150.72872939815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Giovanbattista Califano" refreshedDate="46160.692213773145" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="61" xr:uid="{C70F8671-51C1-D74E-A849-9EC8BC6C887D}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A2:S63" sheet="Registro"/>
   </cacheSource>
@@ -788,13 +788,13 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="L7 XP" numFmtId="0">
-      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="550"/>
     </cacheField>
     <cacheField name="Presenza" numFmtId="9">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.2857142857142857" maxValue="1"/>
     </cacheField>
     <cacheField name="XP" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="25" maxValue="395"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="25" maxValue="920"/>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -824,9 +824,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="395"/>
+    <n v="450"/>
+    <n v="1"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Cofano"/>
@@ -845,9 +845,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
+    <n v="450"/>
     <n v="0.8571428571428571"/>
-    <n v="395"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Curto"/>
@@ -866,9 +866,9 @@
     <n v="0"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
+    <n v="450"/>
     <n v="0.8571428571428571"/>
-    <n v="395"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Robustelli"/>
@@ -887,9 +887,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="395"/>
+    <n v="450"/>
+    <n v="1"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Sorvillo"/>
@@ -908,9 +908,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
+    <n v="450"/>
     <n v="0.7142857142857143"/>
-    <n v="395"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Tarallo"/>
@@ -929,9 +929,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="395"/>
+    <n v="450"/>
+    <n v="1"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Valentino"/>
@@ -950,9 +950,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="395"/>
+    <n v="450"/>
+    <n v="1"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Castiglia"/>
@@ -971,9 +971,9 @@
     <n v="1"/>
     <n v="130"/>
     <n v="1"/>
-    <m/>
+    <n v="450"/>
     <n v="0.5714285714285714"/>
-    <n v="395"/>
+    <n v="845"/>
   </r>
   <r>
     <s v="Cuomo"/>
@@ -992,7 +992,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="25"/>
   </r>
@@ -1013,7 +1013,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.42857142857142855"/>
     <n v="25"/>
   </r>
@@ -1034,7 +1034,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="25"/>
   </r>
@@ -1055,7 +1055,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.2857142857142857"/>
     <n v="25"/>
   </r>
@@ -1076,7 +1076,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="25"/>
   </r>
@@ -1097,7 +1097,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.2857142857142857"/>
     <n v="25"/>
   </r>
@@ -1118,7 +1118,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.7142857142857143"/>
     <n v="25"/>
   </r>
@@ -1139,9 +1139,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="285"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Borreca"/>
@@ -1160,9 +1160,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Borrione"/>
@@ -1181,9 +1181,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="285"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Cappelluccio"/>
@@ -1202,9 +1202,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Casale"/>
@@ -1223,9 +1223,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Marrazzo"/>
@@ -1244,9 +1244,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.7142857142857143"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Miles"/>
@@ -1265,9 +1265,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="285"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Parente"/>
@@ -1286,9 +1286,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Pietropaolo"/>
@@ -1307,9 +1307,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="285"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Rispoli"/>
@@ -1328,9 +1328,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="285"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="435"/>
   </r>
   <r>
     <s v="Maione"/>
@@ -1349,7 +1349,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="175"/>
   </r>
@@ -1370,7 +1370,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="175"/>
   </r>
@@ -1391,7 +1391,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="175"/>
   </r>
@@ -1412,7 +1412,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.7142857142857143"/>
     <n v="175"/>
   </r>
@@ -1433,7 +1433,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.42857142857142855"/>
     <n v="175"/>
   </r>
@@ -1454,7 +1454,7 @@
     <n v="0"/>
     <n v="-15"/>
     <n v="0"/>
-    <m/>
+    <n v="0"/>
     <n v="0.5714285714285714"/>
     <n v="175"/>
   </r>
@@ -1475,9 +1475,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Canzolino"/>
@@ -1496,9 +1496,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="De Siena"/>
@@ -1517,9 +1517,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Di Meglio"/>
@@ -1538,9 +1538,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Esposito"/>
@@ -1559,9 +1559,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Ferrante"/>
@@ -1580,9 +1580,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.7142857142857143"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Maglietta"/>
@@ -1601,9 +1601,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Patroni Griffi"/>
@@ -1622,9 +1622,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Semioli"/>
@@ -1643,9 +1643,9 @@
     <n v="1"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.7142857142857143"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Siano"/>
@@ -1664,9 +1664,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.42857142857142855"/>
-    <n v="130"/>
+    <n v="280"/>
   </r>
   <r>
     <s v="Agliottone"/>
@@ -1685,9 +1685,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="65"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Gallo"/>
@@ -1706,9 +1706,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="65"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Imperatore"/>
@@ -1727,9 +1727,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.42857142857142855"/>
-    <n v="65"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Monaco"/>
@@ -1748,9 +1748,9 @@
     <n v="0"/>
     <n v="30"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="65"/>
+    <n v="215"/>
   </r>
   <r>
     <s v="Cerundolo"/>
@@ -1769,9 +1769,9 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="550"/>
     <n v="0.7142857142857143"/>
-    <n v="370"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Chieti"/>
@@ -1790,9 +1790,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="370"/>
+    <n v="550"/>
+    <n v="1"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Coda"/>
@@ -1811,9 +1811,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="370"/>
+    <n v="550"/>
+    <n v="1"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Dibartolomeo"/>
@@ -1832,9 +1832,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="370"/>
+    <n v="550"/>
+    <n v="1"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Raduazzo"/>
@@ -1853,9 +1853,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="550"/>
     <n v="0.7142857142857143"/>
-    <n v="370"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Vable"/>
@@ -1874,9 +1874,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="370"/>
+    <n v="550"/>
+    <n v="1"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Zito"/>
@@ -1895,9 +1895,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="370"/>
+    <n v="550"/>
+    <n v="1"/>
+    <n v="920"/>
   </r>
   <r>
     <s v="Antico"/>
@@ -1916,9 +1916,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="215"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="D'Acunto"/>
@@ -1937,9 +1937,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Di Fiore"/>
@@ -1958,9 +1958,9 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.5714285714285714"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Ditri"/>
@@ -1979,9 +1979,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
-    <n v="1"/>
-    <n v="215"/>
+    <n v="150"/>
+    <n v="1"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Fraddanno"/>
@@ -2000,9 +2000,9 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Marciello"/>
@@ -2021,9 +2021,9 @@
     <n v="1"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Miranda"/>
@@ -2042,9 +2042,9 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Rolletta"/>
@@ -2063,9 +2063,9 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
   <r>
     <s v="Soriano"/>
@@ -2084,15 +2084,15 @@
     <n v="0"/>
     <n v="100"/>
     <n v="1"/>
-    <m/>
+    <n v="150"/>
     <n v="0.8571428571428571"/>
-    <n v="215"/>
+    <n v="365"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CF83B12C-6A4E-BD4A-AC06-E481A24E0FD5}" name="Tabella pivot1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:C12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -2141,10 +2141,10 @@
   </rowFields>
   <rowItems count="9">
     <i>
-      <x/>
+      <x v="6"/>
     </i>
     <i>
-      <x v="6"/>
+      <x/>
     </i>
     <i>
       <x v="2"/>
@@ -2153,13 +2153,13 @@
       <x v="7"/>
     </i>
     <i>
-      <x v="3"/>
-    </i>
-    <i>
       <x v="4"/>
     </i>
     <i>
       <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i>
       <x v="1"/>
@@ -2650,14 +2650,16 @@
       <c r="P3" s="17">
         <v>1</v>
       </c>
-      <c r="Q3" s="17"/>
+      <c r="Q3" s="17">
+        <v>450</v>
+      </c>
       <c r="R3" s="4">
         <f t="shared" ref="R3:R34" si="0">(D3+F3+H3+J3+L3+N3+P3)/7</f>
         <v>1</v>
       </c>
       <c r="S3" s="3">
         <f t="shared" ref="S3:S34" si="1">E3+G3+I3+K3+M3+O3+Q3</f>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -2709,14 +2711,16 @@
       <c r="P4" s="17">
         <v>1</v>
       </c>
-      <c r="Q4" s="17"/>
+      <c r="Q4" s="17">
+        <v>450</v>
+      </c>
       <c r="R4" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S4" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -2768,14 +2772,16 @@
       <c r="P5" s="17">
         <v>1</v>
       </c>
-      <c r="Q5" s="17"/>
+      <c r="Q5" s="17">
+        <v>450</v>
+      </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S5" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.2">
@@ -2827,14 +2833,16 @@
       <c r="P6" s="17">
         <v>1</v>
       </c>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="17">
+        <v>450</v>
+      </c>
       <c r="R6" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S6" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
@@ -2886,14 +2894,16 @@
       <c r="P7" s="17">
         <v>1</v>
       </c>
-      <c r="Q7" s="17"/>
+      <c r="Q7" s="17">
+        <v>450</v>
+      </c>
       <c r="R7" s="4">
         <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S7" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
@@ -2945,14 +2955,16 @@
       <c r="P8" s="17">
         <v>1</v>
       </c>
-      <c r="Q8" s="17"/>
+      <c r="Q8" s="17">
+        <v>450</v>
+      </c>
       <c r="R8" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S8" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.2">
@@ -3004,14 +3016,16 @@
       <c r="P9" s="17">
         <v>1</v>
       </c>
-      <c r="Q9" s="17"/>
+      <c r="Q9" s="17">
+        <v>450</v>
+      </c>
       <c r="R9" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S9" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.2">
@@ -3063,14 +3077,16 @@
       <c r="P10" s="17">
         <v>1</v>
       </c>
-      <c r="Q10" s="17"/>
+      <c r="Q10" s="17">
+        <v>450</v>
+      </c>
       <c r="R10" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S10" s="3">
         <f t="shared" si="1"/>
-        <v>395</v>
+        <v>845</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
@@ -3122,7 +3138,9 @@
       <c r="P11" s="17">
         <v>0</v>
       </c>
-      <c r="Q11" s="17"/>
+      <c r="Q11" s="17">
+        <v>0</v>
+      </c>
       <c r="R11" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -3181,7 +3199,9 @@
       <c r="P12" s="17">
         <v>0</v>
       </c>
-      <c r="Q12" s="17"/>
+      <c r="Q12" s="17">
+        <v>0</v>
+      </c>
       <c r="R12" s="4">
         <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
@@ -3240,7 +3260,9 @@
       <c r="P13" s="17">
         <v>0</v>
       </c>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
       <c r="R13" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -3299,7 +3321,9 @@
       <c r="P14" s="17">
         <v>0</v>
       </c>
-      <c r="Q14" s="17"/>
+      <c r="Q14" s="17">
+        <v>0</v>
+      </c>
       <c r="R14" s="4">
         <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
@@ -3358,7 +3382,9 @@
       <c r="P15" s="17">
         <v>0</v>
       </c>
-      <c r="Q15" s="17"/>
+      <c r="Q15" s="17">
+        <v>0</v>
+      </c>
       <c r="R15" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -3417,7 +3443,9 @@
       <c r="P16" s="17">
         <v>0</v>
       </c>
-      <c r="Q16" s="17"/>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
       <c r="R16" s="4">
         <f t="shared" si="0"/>
         <v>0.2857142857142857</v>
@@ -3476,7 +3504,9 @@
       <c r="P17" s="17">
         <v>0</v>
       </c>
-      <c r="Q17" s="17"/>
+      <c r="Q17" s="17">
+        <v>0</v>
+      </c>
       <c r="R17" s="4">
         <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
@@ -3535,14 +3565,16 @@
       <c r="P18" s="17">
         <v>1</v>
       </c>
-      <c r="Q18" s="9"/>
+      <c r="Q18" s="17">
+        <v>150</v>
+      </c>
       <c r="R18" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S18" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.2">
@@ -3594,14 +3626,16 @@
       <c r="P19" s="17">
         <v>1</v>
       </c>
-      <c r="Q19" s="9"/>
+      <c r="Q19" s="17">
+        <v>150</v>
+      </c>
       <c r="R19" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.2">
@@ -3653,14 +3687,16 @@
       <c r="P20" s="17">
         <v>1</v>
       </c>
-      <c r="Q20" s="9"/>
+      <c r="Q20" s="17">
+        <v>150</v>
+      </c>
       <c r="R20" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S20" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.2">
@@ -3712,14 +3748,16 @@
       <c r="P21" s="17">
         <v>1</v>
       </c>
-      <c r="Q21" s="9"/>
+      <c r="Q21" s="17">
+        <v>150</v>
+      </c>
       <c r="R21" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S21" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.2">
@@ -3771,14 +3809,16 @@
       <c r="P22" s="17">
         <v>1</v>
       </c>
-      <c r="Q22" s="9"/>
+      <c r="Q22" s="17">
+        <v>150</v>
+      </c>
       <c r="R22" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S22" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.2">
@@ -3830,14 +3870,16 @@
       <c r="P23" s="17">
         <v>1</v>
       </c>
-      <c r="Q23" s="9"/>
+      <c r="Q23" s="17">
+        <v>150</v>
+      </c>
       <c r="R23" s="4">
         <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S23" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.2">
@@ -3889,14 +3931,16 @@
       <c r="P24" s="17">
         <v>1</v>
       </c>
-      <c r="Q24" s="9"/>
+      <c r="Q24" s="17">
+        <v>150</v>
+      </c>
       <c r="R24" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S24" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.2">
@@ -3948,14 +3992,16 @@
       <c r="P25" s="17">
         <v>1</v>
       </c>
-      <c r="Q25" s="9"/>
+      <c r="Q25" s="17">
+        <v>150</v>
+      </c>
       <c r="R25" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S25" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.2">
@@ -4007,14 +4053,16 @@
       <c r="P26" s="17">
         <v>1</v>
       </c>
-      <c r="Q26" s="9"/>
+      <c r="Q26" s="17">
+        <v>150</v>
+      </c>
       <c r="R26" s="4">
         <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S26" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
@@ -4066,14 +4114,16 @@
       <c r="P27" s="17">
         <v>1</v>
       </c>
-      <c r="Q27" s="9"/>
+      <c r="Q27" s="17">
+        <v>150</v>
+      </c>
       <c r="R27" s="4">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="S27" s="3">
         <f t="shared" si="1"/>
-        <v>285</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.2">
@@ -4125,7 +4175,9 @@
       <c r="P28" s="17">
         <v>0</v>
       </c>
-      <c r="Q28" s="9"/>
+      <c r="Q28" s="17">
+        <v>0</v>
+      </c>
       <c r="R28" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -4184,7 +4236,9 @@
       <c r="P29" s="17">
         <v>0</v>
       </c>
-      <c r="Q29" s="9"/>
+      <c r="Q29" s="17">
+        <v>0</v>
+      </c>
       <c r="R29" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -4243,7 +4297,9 @@
       <c r="P30" s="17">
         <v>0</v>
       </c>
-      <c r="Q30" s="9"/>
+      <c r="Q30" s="17">
+        <v>0</v>
+      </c>
       <c r="R30" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -4302,7 +4358,9 @@
       <c r="P31" s="17">
         <v>0</v>
       </c>
-      <c r="Q31" s="9"/>
+      <c r="Q31" s="17">
+        <v>0</v>
+      </c>
       <c r="R31" s="4">
         <f t="shared" si="0"/>
         <v>0.7142857142857143</v>
@@ -4361,7 +4419,9 @@
       <c r="P32" s="17">
         <v>0</v>
       </c>
-      <c r="Q32" s="9"/>
+      <c r="Q32" s="17">
+        <v>0</v>
+      </c>
       <c r="R32" s="4">
         <f t="shared" si="0"/>
         <v>0.42857142857142855</v>
@@ -4420,7 +4480,9 @@
       <c r="P33" s="17">
         <v>0</v>
       </c>
-      <c r="Q33" s="9"/>
+      <c r="Q33" s="17">
+        <v>0</v>
+      </c>
       <c r="R33" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
@@ -4479,14 +4541,16 @@
       <c r="P34" s="17">
         <v>1</v>
       </c>
-      <c r="Q34" s="9"/>
+      <c r="Q34" s="17">
+        <v>150</v>
+      </c>
       <c r="R34" s="4">
         <f t="shared" si="0"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S34" s="3">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.2">
@@ -4538,14 +4602,16 @@
       <c r="P35" s="17">
         <v>1</v>
       </c>
-      <c r="Q35" s="9"/>
+      <c r="Q35" s="17">
+        <v>150</v>
+      </c>
       <c r="R35" s="4">
         <f t="shared" ref="R35:R64" si="2">(D35+F35+H35+J35+L35+N35+P35)/7</f>
         <v>0.8571428571428571</v>
       </c>
       <c r="S35" s="3">
         <f t="shared" ref="S35:S64" si="3">E35+G35+I35+K35+M35+O35+Q35</f>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.2">
@@ -4597,14 +4663,16 @@
       <c r="P36" s="17">
         <v>1</v>
       </c>
-      <c r="Q36" s="9"/>
+      <c r="Q36" s="17">
+        <v>150</v>
+      </c>
       <c r="R36" s="4">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S36" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.2">
@@ -4656,14 +4724,16 @@
       <c r="P37" s="17">
         <v>1</v>
       </c>
-      <c r="Q37" s="9"/>
+      <c r="Q37" s="17">
+        <v>150</v>
+      </c>
       <c r="R37" s="4">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S37" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.2">
@@ -4715,14 +4785,16 @@
       <c r="P38" s="17">
         <v>1</v>
       </c>
-      <c r="Q38" s="9"/>
+      <c r="Q38" s="17">
+        <v>150</v>
+      </c>
       <c r="R38" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S38" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.2">
@@ -4774,14 +4846,16 @@
       <c r="P39" s="17">
         <v>1</v>
       </c>
-      <c r="Q39" s="9"/>
+      <c r="Q39" s="17">
+        <v>150</v>
+      </c>
       <c r="R39" s="4">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S39" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.2">
@@ -4833,14 +4907,16 @@
       <c r="P40" s="17">
         <v>1</v>
       </c>
-      <c r="Q40" s="9"/>
+      <c r="Q40" s="17">
+        <v>150</v>
+      </c>
       <c r="R40" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S40" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.2">
@@ -4892,14 +4968,16 @@
       <c r="P41" s="17">
         <v>1</v>
       </c>
-      <c r="Q41" s="9"/>
+      <c r="Q41" s="17">
+        <v>150</v>
+      </c>
       <c r="R41" s="4">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S41" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.2">
@@ -4951,14 +5029,16 @@
       <c r="P42" s="17">
         <v>1</v>
       </c>
-      <c r="Q42" s="9"/>
+      <c r="Q42" s="17">
+        <v>150</v>
+      </c>
       <c r="R42" s="4">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S42" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.2">
@@ -5010,14 +5090,16 @@
       <c r="P43" s="17">
         <v>1</v>
       </c>
-      <c r="Q43" s="9"/>
+      <c r="Q43" s="17">
+        <v>150</v>
+      </c>
       <c r="R43" s="4">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S43" s="3">
         <f t="shared" si="3"/>
-        <v>130</v>
+        <v>280</v>
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.2">
@@ -5069,14 +5151,16 @@
       <c r="P44" s="17">
         <v>1</v>
       </c>
-      <c r="Q44" s="17"/>
+      <c r="Q44" s="17">
+        <v>150</v>
+      </c>
       <c r="R44" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S44" s="3">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.2">
@@ -5128,14 +5212,16 @@
       <c r="P45" s="17">
         <v>1</v>
       </c>
-      <c r="Q45" s="17"/>
+      <c r="Q45" s="17">
+        <v>150</v>
+      </c>
       <c r="R45" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S45" s="3">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>215</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.2">
@@ -5187,13 +5273,16 @@
       <c r="P46" s="17">
         <v>1</v>
       </c>
+      <c r="Q46" s="17">
+        <v>150</v>
+      </c>
       <c r="R46" s="4">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
       <c r="S46" s="12">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.2">
@@ -5245,13 +5334,16 @@
       <c r="P47" s="17">
         <v>1</v>
       </c>
+      <c r="Q47" s="17">
+        <v>150</v>
+      </c>
       <c r="R47" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S47" s="12">
         <f t="shared" si="3"/>
-        <v>65</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.2">
@@ -5303,14 +5395,16 @@
       <c r="P48" s="17">
         <v>1</v>
       </c>
-      <c r="Q48" s="13"/>
+      <c r="Q48" s="13">
+        <v>550</v>
+      </c>
       <c r="R48" s="4">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S48" s="12">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.2">
@@ -5362,14 +5456,16 @@
       <c r="P49" s="17">
         <v>1</v>
       </c>
-      <c r="Q49" s="13"/>
+      <c r="Q49" s="13">
+        <v>550</v>
+      </c>
       <c r="R49" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S49" s="12">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.2">
@@ -5421,14 +5517,16 @@
       <c r="P50" s="17">
         <v>1</v>
       </c>
-      <c r="Q50" s="13"/>
+      <c r="Q50" s="13">
+        <v>550</v>
+      </c>
       <c r="R50" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S50" s="12">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.2">
@@ -5480,14 +5578,16 @@
       <c r="P51" s="17">
         <v>1</v>
       </c>
-      <c r="Q51" s="13"/>
+      <c r="Q51" s="13">
+        <v>550</v>
+      </c>
       <c r="R51" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S51" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.2">
@@ -5539,14 +5639,16 @@
       <c r="P52" s="17">
         <v>1</v>
       </c>
-      <c r="Q52" s="13"/>
+      <c r="Q52" s="13">
+        <v>550</v>
+      </c>
       <c r="R52" s="4">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
       <c r="S52" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.2">
@@ -5598,14 +5700,16 @@
       <c r="P53" s="17">
         <v>1</v>
       </c>
-      <c r="Q53" s="13"/>
+      <c r="Q53" s="13">
+        <v>550</v>
+      </c>
       <c r="R53" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S53" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.2">
@@ -5657,14 +5761,16 @@
       <c r="P54" s="17">
         <v>1</v>
       </c>
-      <c r="Q54" s="13"/>
+      <c r="Q54" s="13">
+        <v>550</v>
+      </c>
       <c r="R54" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S54" s="14">
         <f t="shared" si="3"/>
-        <v>370</v>
+        <v>920</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.2">
@@ -5716,14 +5822,16 @@
       <c r="P55" s="17">
         <v>1</v>
       </c>
-      <c r="Q55" s="13"/>
+      <c r="Q55" s="13">
+        <v>150</v>
+      </c>
       <c r="R55" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S55" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -5775,14 +5883,16 @@
       <c r="P56" s="17">
         <v>1</v>
       </c>
-      <c r="Q56" s="13"/>
+      <c r="Q56" s="13">
+        <v>150</v>
+      </c>
       <c r="R56" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S56" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.2">
@@ -5834,14 +5944,16 @@
       <c r="P57" s="17">
         <v>1</v>
       </c>
-      <c r="Q57" s="13"/>
+      <c r="Q57" s="13">
+        <v>150</v>
+      </c>
       <c r="R57" s="4">
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S57" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.2">
@@ -5893,14 +6005,16 @@
       <c r="P58" s="17">
         <v>1</v>
       </c>
-      <c r="Q58" s="13"/>
+      <c r="Q58" s="13">
+        <v>150</v>
+      </c>
       <c r="R58" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="S58" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.2">
@@ -5952,14 +6066,16 @@
       <c r="P59" s="17">
         <v>1</v>
       </c>
-      <c r="Q59" s="13"/>
+      <c r="Q59" s="13">
+        <v>150</v>
+      </c>
       <c r="R59" s="4">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S59" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.2">
@@ -6011,14 +6127,16 @@
       <c r="P60" s="17">
         <v>1</v>
       </c>
-      <c r="Q60" s="13"/>
+      <c r="Q60" s="13">
+        <v>150</v>
+      </c>
       <c r="R60" s="16">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S60" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.2">
@@ -6070,14 +6188,16 @@
       <c r="P61" s="17">
         <v>1</v>
       </c>
-      <c r="Q61" s="13"/>
+      <c r="Q61" s="13">
+        <v>150</v>
+      </c>
       <c r="R61" s="16">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S61" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.2">
@@ -6129,14 +6249,16 @@
       <c r="P62" s="17">
         <v>1</v>
       </c>
-      <c r="Q62" s="13"/>
+      <c r="Q62" s="13">
+        <v>150</v>
+      </c>
       <c r="R62" s="16">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S62" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.2">
@@ -6188,14 +6310,16 @@
       <c r="P63" s="17">
         <v>1</v>
       </c>
-      <c r="Q63" s="13"/>
+      <c r="Q63" s="13">
+        <v>150</v>
+      </c>
       <c r="R63" s="16">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S63" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.2">
@@ -6247,14 +6371,16 @@
       <c r="P64" s="17">
         <v>1</v>
       </c>
-      <c r="Q64" s="13"/>
+      <c r="Q64" s="13">
+        <v>150</v>
+      </c>
       <c r="R64" s="16">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
       <c r="S64" s="14">
         <f t="shared" si="3"/>
-        <v>215</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6302,24 +6428,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="B4" s="26">
-        <v>395</v>
+        <v>920</v>
       </c>
       <c r="C4" s="7">
-        <v>0.875</v>
+        <v>0.91836734693877553</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="B5" s="26">
-        <v>370</v>
+        <v>845</v>
       </c>
       <c r="C5" s="7">
-        <v>0.91836734693877553</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -6327,7 +6453,7 @@
         <v>31</v>
       </c>
       <c r="B6" s="26">
-        <v>285</v>
+        <v>435</v>
       </c>
       <c r="C6" s="7">
         <v>0.9</v>
@@ -6338,7 +6464,7 @@
         <v>28</v>
       </c>
       <c r="B7" s="26">
-        <v>215</v>
+        <v>365</v>
       </c>
       <c r="C7" s="7">
         <v>0.82539682539682524</v>
@@ -6346,35 +6472,35 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B8" s="26">
-        <v>175</v>
+        <v>280</v>
       </c>
       <c r="C8" s="7">
-        <v>0.57142857142857129</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>36</v>
+        <v>149</v>
       </c>
       <c r="B9" s="26">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="C9" s="7">
-        <v>0.7</v>
+        <v>0.5357142857142857</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="B10" s="26">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="C10" s="7">
-        <v>0.5357142857142857</v>
+        <v>0.57142857142857129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -6393,7 +6519,7 @@
         <v>117</v>
       </c>
       <c r="B12" s="26">
-        <v>218.36065573770492</v>
+        <v>421.63934426229508</v>
       </c>
       <c r="C12" s="7">
         <v>0.75175644028103039</v>
